--- a/청첩장/Moment Edit · Letter System (개선).xlsx
+++ b/청첩장/Moment Edit · Letter System (개선).xlsx
@@ -1884,6 +1884,102 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lmh-cyj-0823</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이민호</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최유진</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lee Minho</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Choi Yujin</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-23</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">국민 333-111-222333</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신한 444-555-666777</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이재환 · 최미경</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정영석 · 박윤희</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저희 두 사람, 같은 곳을 바라보며 함께 걷기로 했습니다.</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
+        </is>
+      </c>
+      <c r="V5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
+        </is>
+      </c>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
       <c r="Y5" s="1">
         <f>IF($A5="","","https://momentedit.kr/i/cover-"&amp;$H5&amp;".html?e="&amp;$A5)</f>
       </c>

--- a/청첩장/Moment Edit · Letter System (개선).xlsx
+++ b/청첩장/Moment Edit · Letter System (개선).xlsx
@@ -1501,7 +1501,6 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1546,90 +1545,85 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">가족카드(Y)</t>
+          <t xml:space="preserve">신랑 계좌(은행 번호)</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신랑 계좌(은행 번호)</t>
+          <t xml:space="preserve">신부 계좌(은행 번호)</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신부 계좌(은행 번호)</t>
+          <t xml:space="preserve">신랑 혼주</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신랑 혼주</t>
+          <t xml:space="preserve">신부 혼주</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신부 혼주</t>
+          <t xml:space="preserve">인사글 직접작성(비우면 기본)</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">인사글 직접작성(비우면 기본)</t>
+          <t xml:space="preserve">인사글 부모표기(Y)</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">인사글 부모표기(Y)</t>
+          <t xml:space="preserve">계좌 부모표기(Y)</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">계좌 부모표기(Y)</t>
+          <t xml:space="preserve">신랑 아버지 계좌</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신랑 아버지 계좌</t>
+          <t xml:space="preserve">신랑 어머니 계좌</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신랑 어머니 계좌</t>
+          <t xml:space="preserve">신부 아버지 계좌</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신부 아버지 계좌</t>
+          <t xml:space="preserve">신부 어머니 계좌</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신부 어머니 계좌</t>
+          <t xml:space="preserve">신랑 이메일</t>
         </is>
       </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신랑 이메일</t>
+          <t xml:space="preserve">신부 이메일</t>
         </is>
       </c>
       <c r="V2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신부 이메일</t>
+          <t xml:space="preserve">영상ID</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">영상ID</t>
+          <t xml:space="preserve">영상Hash</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">영상Hash</t>
+          <t xml:space="preserve">라이브 링크(자동)</t>
         </is>
       </c>
       <c r="Y2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라이브 링크(자동)</t>
-        </is>
-      </c>
-      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">가족 링크(자동)</t>
         </is>
@@ -1678,90 +1672,85 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">familyActive</t>
+          <t xml:space="preserve">groomAccount</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">groomAccount</t>
+          <t xml:space="preserve">brideAccount</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">brideAccount</t>
+          <t xml:space="preserve">groomParents</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">groomParents</t>
+          <t xml:space="preserve">brideParents</t>
         </is>
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">brideParents</t>
+          <t xml:space="preserve">invitationText</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">invitationText</t>
+          <t xml:space="preserve">greetingShowParents</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">greetingShowParents</t>
+          <t xml:space="preserve">envelopeShowParents</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">envelopeShowParents</t>
+          <t xml:space="preserve">groomFatherAccount</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">groomFatherAccount</t>
+          <t xml:space="preserve">groomMotherAccount</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">groomMotherAccount</t>
+          <t xml:space="preserve">brideFatherAccount</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">brideFatherAccount</t>
+          <t xml:space="preserve">brideMotherAccount</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">brideMotherAccount</t>
+          <t xml:space="preserve">groomEmail</t>
         </is>
       </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">groomEmail</t>
+          <t xml:space="preserve">brideEmail</t>
         </is>
       </c>
       <c r="V3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">brideEmail</t>
+          <t xml:space="preserve">vimeoId</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">vimeoId</t>
+          <t xml:space="preserve">vimeoHash</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">vimeoHash</t>
+          <t xml:space="preserve">liveUrl</t>
         </is>
       </c>
       <c r="Y3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">liveUrl</t>
-        </is>
-      </c>
-      <c r="Z3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">familyUrl</t>
         </is>
@@ -1810,30 +1799,30 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">하나 222-456-789012</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리 333-456-789012</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박철수 · 이미경</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김영호 · 최선영</t>
+        </is>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하나 222-456-789012</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우리 333-456-789012</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박철수 · 이미경</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김영호 · 최선영</t>
-        </is>
-      </c>
-      <c r="N4" s="1"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
@@ -1841,27 +1830,27 @@
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">국민 110-123-456789</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">국민 110-123-456789</t>
+          <t xml:space="preserve">신한 220-456-123789</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신한 220-456-123789</t>
+          <t xml:space="preserve">농협 351-234-567890</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">농협 351-234-567890</t>
+          <t xml:space="preserve">카카오뱅크 3333-12-3456789</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크 3333-12-3456789</t>
+          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
         </is>
       </c>
       <c r="U4" s="1" t="inlineStr">
@@ -1869,18 +1858,13 @@
           <t xml:space="preserve">gtrddrt7706@gmail.com</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
-        </is>
-      </c>
+      <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
+      <c r="X4" s="1">
+        <f>IF($A4="","","https://momentedit.kr/i/cover-"&amp;$H4&amp;".html?e="&amp;$A4)</f>
+      </c>
       <c r="Y4" s="1">
-        <f>IF($A4="","","https://momentedit.kr/i/cover-"&amp;$H4&amp;".html?e="&amp;$A4)</f>
-      </c>
-      <c r="Z4" s="1">
-        <f>IF(AND($A4&lt;&gt;"",$I4="Y"),"https://momentedit.kr/i-family/family-"&amp;$H4&amp;".html?e="&amp;$A4,"")</f>
+        <f>IF($A4="","","https://momentedit.kr/i-family/family-"&amp;$H4&amp;".html?e="&amp;$A4)</f>
       </c>
     </row>
     <row r="5">
@@ -1926,32 +1910,32 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">국민 333-111-222333</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">국민 333-111-222333</t>
+          <t xml:space="preserve">신한 444-555-666777</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">신한 444-555-666777</t>
+          <t xml:space="preserve">이재환 · 최미경</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">이재환 · 최미경</t>
+          <t xml:space="preserve">정영석 · 박윤희</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">정영석 · 박윤희</t>
+          <t xml:space="preserve">저희 두 사람, 같은 곳을 바라보며 함께 걷기로 했습니다.</t>
         </is>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">저희 두 사람, 같은 곳을 바라보며 함께 걷기로 했습니다.</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -1959,1592 +1943,1587 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
+      <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
+      <c r="T5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
+        </is>
+      </c>
       <c r="U5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">gtrddrt7706@gmail.com</t>
         </is>
       </c>
-      <c r="V5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
-        </is>
-      </c>
+      <c r="V5" s="1"/>
       <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
+      <c r="X5" s="1">
+        <f>IF($A5="","","https://momentedit.kr/i/cover-"&amp;$H5&amp;".html?e="&amp;$A5)</f>
+      </c>
       <c r="Y5" s="1">
-        <f>IF($A5="","","https://momentedit.kr/i/cover-"&amp;$H5&amp;".html?e="&amp;$A5)</f>
-      </c>
-      <c r="Z5" s="1">
-        <f>IF(AND($A5&lt;&gt;"",$I5="Y"),"https://momentedit.kr/i-family/family-"&amp;$H5&amp;".html?e="&amp;$A5,"")</f>
+        <f>IF($A5="","","https://momentedit.kr/i-family/family-"&amp;$H5&amp;".html?e="&amp;$A5)</f>
       </c>
     </row>
     <row r="6">
+      <c r="X6" s="1">
+        <f>IF($A6="","","https://momentedit.kr/i/cover-"&amp;$H6&amp;".html?e="&amp;$A6)</f>
+      </c>
       <c r="Y6" s="1">
-        <f>IF($A6="","","https://momentedit.kr/i/cover-"&amp;$H6&amp;".html?e="&amp;$A6)</f>
-      </c>
-      <c r="Z6" s="1">
-        <f>IF(AND($A6&lt;&gt;"",$I6="Y"),"https://momentedit.kr/i-family/family-"&amp;$H6&amp;".html?e="&amp;$A6,"")</f>
+        <f>IF($A6="","","https://momentedit.kr/i-family/family-"&amp;$H6&amp;".html?e="&amp;$A6)</f>
       </c>
     </row>
     <row r="7">
+      <c r="X7" s="1">
+        <f>IF($A7="","","https://momentedit.kr/i/cover-"&amp;$H7&amp;".html?e="&amp;$A7)</f>
+      </c>
       <c r="Y7" s="1">
-        <f>IF($A7="","","https://momentedit.kr/i/cover-"&amp;$H7&amp;".html?e="&amp;$A7)</f>
-      </c>
-      <c r="Z7" s="1">
-        <f>IF(AND($A7&lt;&gt;"",$I7="Y"),"https://momentedit.kr/i-family/family-"&amp;$H7&amp;".html?e="&amp;$A7,"")</f>
+        <f>IF($A7="","","https://momentedit.kr/i-family/family-"&amp;$H7&amp;".html?e="&amp;$A7)</f>
       </c>
     </row>
     <row r="8">
+      <c r="X8" s="1">
+        <f>IF($A8="","","https://momentedit.kr/i/cover-"&amp;$H8&amp;".html?e="&amp;$A8)</f>
+      </c>
       <c r="Y8" s="1">
-        <f>IF($A8="","","https://momentedit.kr/i/cover-"&amp;$H8&amp;".html?e="&amp;$A8)</f>
-      </c>
-      <c r="Z8" s="1">
-        <f>IF(AND($A8&lt;&gt;"",$I8="Y"),"https://momentedit.kr/i-family/family-"&amp;$H8&amp;".html?e="&amp;$A8,"")</f>
+        <f>IF($A8="","","https://momentedit.kr/i-family/family-"&amp;$H8&amp;".html?e="&amp;$A8)</f>
       </c>
     </row>
     <row r="9">
+      <c r="X9" s="1">
+        <f>IF($A9="","","https://momentedit.kr/i/cover-"&amp;$H9&amp;".html?e="&amp;$A9)</f>
+      </c>
       <c r="Y9" s="1">
-        <f>IF($A9="","","https://momentedit.kr/i/cover-"&amp;$H9&amp;".html?e="&amp;$A9)</f>
-      </c>
-      <c r="Z9" s="1">
-        <f>IF(AND($A9&lt;&gt;"",$I9="Y"),"https://momentedit.kr/i-family/family-"&amp;$H9&amp;".html?e="&amp;$A9,"")</f>
+        <f>IF($A9="","","https://momentedit.kr/i-family/family-"&amp;$H9&amp;".html?e="&amp;$A9)</f>
       </c>
     </row>
     <row r="10">
+      <c r="X10" s="1">
+        <f>IF($A10="","","https://momentedit.kr/i/cover-"&amp;$H10&amp;".html?e="&amp;$A10)</f>
+      </c>
       <c r="Y10" s="1">
-        <f>IF($A10="","","https://momentedit.kr/i/cover-"&amp;$H10&amp;".html?e="&amp;$A10)</f>
-      </c>
-      <c r="Z10" s="1">
-        <f>IF(AND($A10&lt;&gt;"",$I10="Y"),"https://momentedit.kr/i-family/family-"&amp;$H10&amp;".html?e="&amp;$A10,"")</f>
+        <f>IF($A10="","","https://momentedit.kr/i-family/family-"&amp;$H10&amp;".html?e="&amp;$A10)</f>
       </c>
     </row>
     <row r="11">
+      <c r="X11" s="1">
+        <f>IF($A11="","","https://momentedit.kr/i/cover-"&amp;$H11&amp;".html?e="&amp;$A11)</f>
+      </c>
       <c r="Y11" s="1">
-        <f>IF($A11="","","https://momentedit.kr/i/cover-"&amp;$H11&amp;".html?e="&amp;$A11)</f>
-      </c>
-      <c r="Z11" s="1">
-        <f>IF(AND($A11&lt;&gt;"",$I11="Y"),"https://momentedit.kr/i-family/family-"&amp;$H11&amp;".html?e="&amp;$A11,"")</f>
+        <f>IF($A11="","","https://momentedit.kr/i-family/family-"&amp;$H11&amp;".html?e="&amp;$A11)</f>
       </c>
     </row>
     <row r="12">
+      <c r="X12" s="1">
+        <f>IF($A12="","","https://momentedit.kr/i/cover-"&amp;$H12&amp;".html?e="&amp;$A12)</f>
+      </c>
       <c r="Y12" s="1">
-        <f>IF($A12="","","https://momentedit.kr/i/cover-"&amp;$H12&amp;".html?e="&amp;$A12)</f>
-      </c>
-      <c r="Z12" s="1">
-        <f>IF(AND($A12&lt;&gt;"",$I12="Y"),"https://momentedit.kr/i-family/family-"&amp;$H12&amp;".html?e="&amp;$A12,"")</f>
+        <f>IF($A12="","","https://momentedit.kr/i-family/family-"&amp;$H12&amp;".html?e="&amp;$A12)</f>
       </c>
     </row>
     <row r="13">
+      <c r="X13" s="1">
+        <f>IF($A13="","","https://momentedit.kr/i/cover-"&amp;$H13&amp;".html?e="&amp;$A13)</f>
+      </c>
       <c r="Y13" s="1">
-        <f>IF($A13="","","https://momentedit.kr/i/cover-"&amp;$H13&amp;".html?e="&amp;$A13)</f>
-      </c>
-      <c r="Z13" s="1">
-        <f>IF(AND($A13&lt;&gt;"",$I13="Y"),"https://momentedit.kr/i-family/family-"&amp;$H13&amp;".html?e="&amp;$A13,"")</f>
+        <f>IF($A13="","","https://momentedit.kr/i-family/family-"&amp;$H13&amp;".html?e="&amp;$A13)</f>
       </c>
     </row>
     <row r="14">
+      <c r="X14" s="1">
+        <f>IF($A14="","","https://momentedit.kr/i/cover-"&amp;$H14&amp;".html?e="&amp;$A14)</f>
+      </c>
       <c r="Y14" s="1">
-        <f>IF($A14="","","https://momentedit.kr/i/cover-"&amp;$H14&amp;".html?e="&amp;$A14)</f>
-      </c>
-      <c r="Z14" s="1">
-        <f>IF(AND($A14&lt;&gt;"",$I14="Y"),"https://momentedit.kr/i-family/family-"&amp;$H14&amp;".html?e="&amp;$A14,"")</f>
+        <f>IF($A14="","","https://momentedit.kr/i-family/family-"&amp;$H14&amp;".html?e="&amp;$A14)</f>
       </c>
     </row>
     <row r="15">
+      <c r="X15" s="1">
+        <f>IF($A15="","","https://momentedit.kr/i/cover-"&amp;$H15&amp;".html?e="&amp;$A15)</f>
+      </c>
       <c r="Y15" s="1">
-        <f>IF($A15="","","https://momentedit.kr/i/cover-"&amp;$H15&amp;".html?e="&amp;$A15)</f>
-      </c>
-      <c r="Z15" s="1">
-        <f>IF(AND($A15&lt;&gt;"",$I15="Y"),"https://momentedit.kr/i-family/family-"&amp;$H15&amp;".html?e="&amp;$A15,"")</f>
+        <f>IF($A15="","","https://momentedit.kr/i-family/family-"&amp;$H15&amp;".html?e="&amp;$A15)</f>
       </c>
     </row>
     <row r="16">
+      <c r="X16" s="1">
+        <f>IF($A16="","","https://momentedit.kr/i/cover-"&amp;$H16&amp;".html?e="&amp;$A16)</f>
+      </c>
       <c r="Y16" s="1">
-        <f>IF($A16="","","https://momentedit.kr/i/cover-"&amp;$H16&amp;".html?e="&amp;$A16)</f>
-      </c>
-      <c r="Z16" s="1">
-        <f>IF(AND($A16&lt;&gt;"",$I16="Y"),"https://momentedit.kr/i-family/family-"&amp;$H16&amp;".html?e="&amp;$A16,"")</f>
+        <f>IF($A16="","","https://momentedit.kr/i-family/family-"&amp;$H16&amp;".html?e="&amp;$A16)</f>
       </c>
     </row>
     <row r="17">
+      <c r="X17" s="1">
+        <f>IF($A17="","","https://momentedit.kr/i/cover-"&amp;$H17&amp;".html?e="&amp;$A17)</f>
+      </c>
       <c r="Y17" s="1">
-        <f>IF($A17="","","https://momentedit.kr/i/cover-"&amp;$H17&amp;".html?e="&amp;$A17)</f>
-      </c>
-      <c r="Z17" s="1">
-        <f>IF(AND($A17&lt;&gt;"",$I17="Y"),"https://momentedit.kr/i-family/family-"&amp;$H17&amp;".html?e="&amp;$A17,"")</f>
+        <f>IF($A17="","","https://momentedit.kr/i-family/family-"&amp;$H17&amp;".html?e="&amp;$A17)</f>
       </c>
     </row>
     <row r="18">
+      <c r="X18" s="1">
+        <f>IF($A18="","","https://momentedit.kr/i/cover-"&amp;$H18&amp;".html?e="&amp;$A18)</f>
+      </c>
       <c r="Y18" s="1">
-        <f>IF($A18="","","https://momentedit.kr/i/cover-"&amp;$H18&amp;".html?e="&amp;$A18)</f>
-      </c>
-      <c r="Z18" s="1">
-        <f>IF(AND($A18&lt;&gt;"",$I18="Y"),"https://momentedit.kr/i-family/family-"&amp;$H18&amp;".html?e="&amp;$A18,"")</f>
+        <f>IF($A18="","","https://momentedit.kr/i-family/family-"&amp;$H18&amp;".html?e="&amp;$A18)</f>
       </c>
     </row>
     <row r="19">
+      <c r="X19" s="1">
+        <f>IF($A19="","","https://momentedit.kr/i/cover-"&amp;$H19&amp;".html?e="&amp;$A19)</f>
+      </c>
       <c r="Y19" s="1">
-        <f>IF($A19="","","https://momentedit.kr/i/cover-"&amp;$H19&amp;".html?e="&amp;$A19)</f>
-      </c>
-      <c r="Z19" s="1">
-        <f>IF(AND($A19&lt;&gt;"",$I19="Y"),"https://momentedit.kr/i-family/family-"&amp;$H19&amp;".html?e="&amp;$A19,"")</f>
+        <f>IF($A19="","","https://momentedit.kr/i-family/family-"&amp;$H19&amp;".html?e="&amp;$A19)</f>
       </c>
     </row>
     <row r="20">
+      <c r="X20" s="1">
+        <f>IF($A20="","","https://momentedit.kr/i/cover-"&amp;$H20&amp;".html?e="&amp;$A20)</f>
+      </c>
       <c r="Y20" s="1">
-        <f>IF($A20="","","https://momentedit.kr/i/cover-"&amp;$H20&amp;".html?e="&amp;$A20)</f>
-      </c>
-      <c r="Z20" s="1">
-        <f>IF(AND($A20&lt;&gt;"",$I20="Y"),"https://momentedit.kr/i-family/family-"&amp;$H20&amp;".html?e="&amp;$A20,"")</f>
+        <f>IF($A20="","","https://momentedit.kr/i-family/family-"&amp;$H20&amp;".html?e="&amp;$A20)</f>
       </c>
     </row>
     <row r="21">
+      <c r="X21" s="1">
+        <f>IF($A21="","","https://momentedit.kr/i/cover-"&amp;$H21&amp;".html?e="&amp;$A21)</f>
+      </c>
       <c r="Y21" s="1">
-        <f>IF($A21="","","https://momentedit.kr/i/cover-"&amp;$H21&amp;".html?e="&amp;$A21)</f>
-      </c>
-      <c r="Z21" s="1">
-        <f>IF(AND($A21&lt;&gt;"",$I21="Y"),"https://momentedit.kr/i-family/family-"&amp;$H21&amp;".html?e="&amp;$A21,"")</f>
+        <f>IF($A21="","","https://momentedit.kr/i-family/family-"&amp;$H21&amp;".html?e="&amp;$A21)</f>
       </c>
     </row>
     <row r="22">
+      <c r="X22" s="1">
+        <f>IF($A22="","","https://momentedit.kr/i/cover-"&amp;$H22&amp;".html?e="&amp;$A22)</f>
+      </c>
       <c r="Y22" s="1">
-        <f>IF($A22="","","https://momentedit.kr/i/cover-"&amp;$H22&amp;".html?e="&amp;$A22)</f>
-      </c>
-      <c r="Z22" s="1">
-        <f>IF(AND($A22&lt;&gt;"",$I22="Y"),"https://momentedit.kr/i-family/family-"&amp;$H22&amp;".html?e="&amp;$A22,"")</f>
+        <f>IF($A22="","","https://momentedit.kr/i-family/family-"&amp;$H22&amp;".html?e="&amp;$A22)</f>
       </c>
     </row>
     <row r="23">
+      <c r="X23" s="1">
+        <f>IF($A23="","","https://momentedit.kr/i/cover-"&amp;$H23&amp;".html?e="&amp;$A23)</f>
+      </c>
       <c r="Y23" s="1">
-        <f>IF($A23="","","https://momentedit.kr/i/cover-"&amp;$H23&amp;".html?e="&amp;$A23)</f>
-      </c>
-      <c r="Z23" s="1">
-        <f>IF(AND($A23&lt;&gt;"",$I23="Y"),"https://momentedit.kr/i-family/family-"&amp;$H23&amp;".html?e="&amp;$A23,"")</f>
+        <f>IF($A23="","","https://momentedit.kr/i-family/family-"&amp;$H23&amp;".html?e="&amp;$A23)</f>
       </c>
     </row>
     <row r="24">
+      <c r="X24" s="1">
+        <f>IF($A24="","","https://momentedit.kr/i/cover-"&amp;$H24&amp;".html?e="&amp;$A24)</f>
+      </c>
       <c r="Y24" s="1">
-        <f>IF($A24="","","https://momentedit.kr/i/cover-"&amp;$H24&amp;".html?e="&amp;$A24)</f>
-      </c>
-      <c r="Z24" s="1">
-        <f>IF(AND($A24&lt;&gt;"",$I24="Y"),"https://momentedit.kr/i-family/family-"&amp;$H24&amp;".html?e="&amp;$A24,"")</f>
+        <f>IF($A24="","","https://momentedit.kr/i-family/family-"&amp;$H24&amp;".html?e="&amp;$A24)</f>
       </c>
     </row>
     <row r="25">
+      <c r="X25" s="1">
+        <f>IF($A25="","","https://momentedit.kr/i/cover-"&amp;$H25&amp;".html?e="&amp;$A25)</f>
+      </c>
       <c r="Y25" s="1">
-        <f>IF($A25="","","https://momentedit.kr/i/cover-"&amp;$H25&amp;".html?e="&amp;$A25)</f>
-      </c>
-      <c r="Z25" s="1">
-        <f>IF(AND($A25&lt;&gt;"",$I25="Y"),"https://momentedit.kr/i-family/family-"&amp;$H25&amp;".html?e="&amp;$A25,"")</f>
+        <f>IF($A25="","","https://momentedit.kr/i-family/family-"&amp;$H25&amp;".html?e="&amp;$A25)</f>
       </c>
     </row>
     <row r="26">
+      <c r="X26" s="1">
+        <f>IF($A26="","","https://momentedit.kr/i/cover-"&amp;$H26&amp;".html?e="&amp;$A26)</f>
+      </c>
       <c r="Y26" s="1">
-        <f>IF($A26="","","https://momentedit.kr/i/cover-"&amp;$H26&amp;".html?e="&amp;$A26)</f>
-      </c>
-      <c r="Z26" s="1">
-        <f>IF(AND($A26&lt;&gt;"",$I26="Y"),"https://momentedit.kr/i-family/family-"&amp;$H26&amp;".html?e="&amp;$A26,"")</f>
+        <f>IF($A26="","","https://momentedit.kr/i-family/family-"&amp;$H26&amp;".html?e="&amp;$A26)</f>
       </c>
     </row>
     <row r="27">
+      <c r="X27" s="1">
+        <f>IF($A27="","","https://momentedit.kr/i/cover-"&amp;$H27&amp;".html?e="&amp;$A27)</f>
+      </c>
       <c r="Y27" s="1">
-        <f>IF($A27="","","https://momentedit.kr/i/cover-"&amp;$H27&amp;".html?e="&amp;$A27)</f>
-      </c>
-      <c r="Z27" s="1">
-        <f>IF(AND($A27&lt;&gt;"",$I27="Y"),"https://momentedit.kr/i-family/family-"&amp;$H27&amp;".html?e="&amp;$A27,"")</f>
+        <f>IF($A27="","","https://momentedit.kr/i-family/family-"&amp;$H27&amp;".html?e="&amp;$A27)</f>
       </c>
     </row>
     <row r="28">
+      <c r="X28" s="1">
+        <f>IF($A28="","","https://momentedit.kr/i/cover-"&amp;$H28&amp;".html?e="&amp;$A28)</f>
+      </c>
       <c r="Y28" s="1">
-        <f>IF($A28="","","https://momentedit.kr/i/cover-"&amp;$H28&amp;".html?e="&amp;$A28)</f>
-      </c>
-      <c r="Z28" s="1">
-        <f>IF(AND($A28&lt;&gt;"",$I28="Y"),"https://momentedit.kr/i-family/family-"&amp;$H28&amp;".html?e="&amp;$A28,"")</f>
+        <f>IF($A28="","","https://momentedit.kr/i-family/family-"&amp;$H28&amp;".html?e="&amp;$A28)</f>
       </c>
     </row>
     <row r="29">
+      <c r="X29" s="1">
+        <f>IF($A29="","","https://momentedit.kr/i/cover-"&amp;$H29&amp;".html?e="&amp;$A29)</f>
+      </c>
       <c r="Y29" s="1">
-        <f>IF($A29="","","https://momentedit.kr/i/cover-"&amp;$H29&amp;".html?e="&amp;$A29)</f>
-      </c>
-      <c r="Z29" s="1">
-        <f>IF(AND($A29&lt;&gt;"",$I29="Y"),"https://momentedit.kr/i-family/family-"&amp;$H29&amp;".html?e="&amp;$A29,"")</f>
+        <f>IF($A29="","","https://momentedit.kr/i-family/family-"&amp;$H29&amp;".html?e="&amp;$A29)</f>
       </c>
     </row>
     <row r="30">
+      <c r="X30" s="1">
+        <f>IF($A30="","","https://momentedit.kr/i/cover-"&amp;$H30&amp;".html?e="&amp;$A30)</f>
+      </c>
       <c r="Y30" s="1">
-        <f>IF($A30="","","https://momentedit.kr/i/cover-"&amp;$H30&amp;".html?e="&amp;$A30)</f>
-      </c>
-      <c r="Z30" s="1">
-        <f>IF(AND($A30&lt;&gt;"",$I30="Y"),"https://momentedit.kr/i-family/family-"&amp;$H30&amp;".html?e="&amp;$A30,"")</f>
+        <f>IF($A30="","","https://momentedit.kr/i-family/family-"&amp;$H30&amp;".html?e="&amp;$A30)</f>
       </c>
     </row>
     <row r="31">
+      <c r="X31" s="1">
+        <f>IF($A31="","","https://momentedit.kr/i/cover-"&amp;$H31&amp;".html?e="&amp;$A31)</f>
+      </c>
       <c r="Y31" s="1">
-        <f>IF($A31="","","https://momentedit.kr/i/cover-"&amp;$H31&amp;".html?e="&amp;$A31)</f>
-      </c>
-      <c r="Z31" s="1">
-        <f>IF(AND($A31&lt;&gt;"",$I31="Y"),"https://momentedit.kr/i-family/family-"&amp;$H31&amp;".html?e="&amp;$A31,"")</f>
+        <f>IF($A31="","","https://momentedit.kr/i-family/family-"&amp;$H31&amp;".html?e="&amp;$A31)</f>
       </c>
     </row>
     <row r="32">
+      <c r="X32" s="1">
+        <f>IF($A32="","","https://momentedit.kr/i/cover-"&amp;$H32&amp;".html?e="&amp;$A32)</f>
+      </c>
       <c r="Y32" s="1">
-        <f>IF($A32="","","https://momentedit.kr/i/cover-"&amp;$H32&amp;".html?e="&amp;$A32)</f>
-      </c>
-      <c r="Z32" s="1">
-        <f>IF(AND($A32&lt;&gt;"",$I32="Y"),"https://momentedit.kr/i-family/family-"&amp;$H32&amp;".html?e="&amp;$A32,"")</f>
+        <f>IF($A32="","","https://momentedit.kr/i-family/family-"&amp;$H32&amp;".html?e="&amp;$A32)</f>
       </c>
     </row>
     <row r="33">
+      <c r="X33" s="1">
+        <f>IF($A33="","","https://momentedit.kr/i/cover-"&amp;$H33&amp;".html?e="&amp;$A33)</f>
+      </c>
       <c r="Y33" s="1">
-        <f>IF($A33="","","https://momentedit.kr/i/cover-"&amp;$H33&amp;".html?e="&amp;$A33)</f>
-      </c>
-      <c r="Z33" s="1">
-        <f>IF(AND($A33&lt;&gt;"",$I33="Y"),"https://momentedit.kr/i-family/family-"&amp;$H33&amp;".html?e="&amp;$A33,"")</f>
+        <f>IF($A33="","","https://momentedit.kr/i-family/family-"&amp;$H33&amp;".html?e="&amp;$A33)</f>
       </c>
     </row>
     <row r="34">
+      <c r="X34" s="1">
+        <f>IF($A34="","","https://momentedit.kr/i/cover-"&amp;$H34&amp;".html?e="&amp;$A34)</f>
+      </c>
       <c r="Y34" s="1">
-        <f>IF($A34="","","https://momentedit.kr/i/cover-"&amp;$H34&amp;".html?e="&amp;$A34)</f>
-      </c>
-      <c r="Z34" s="1">
-        <f>IF(AND($A34&lt;&gt;"",$I34="Y"),"https://momentedit.kr/i-family/family-"&amp;$H34&amp;".html?e="&amp;$A34,"")</f>
+        <f>IF($A34="","","https://momentedit.kr/i-family/family-"&amp;$H34&amp;".html?e="&amp;$A34)</f>
       </c>
     </row>
     <row r="35">
+      <c r="X35" s="1">
+        <f>IF($A35="","","https://momentedit.kr/i/cover-"&amp;$H35&amp;".html?e="&amp;$A35)</f>
+      </c>
       <c r="Y35" s="1">
-        <f>IF($A35="","","https://momentedit.kr/i/cover-"&amp;$H35&amp;".html?e="&amp;$A35)</f>
-      </c>
-      <c r="Z35" s="1">
-        <f>IF(AND($A35&lt;&gt;"",$I35="Y"),"https://momentedit.kr/i-family/family-"&amp;$H35&amp;".html?e="&amp;$A35,"")</f>
+        <f>IF($A35="","","https://momentedit.kr/i-family/family-"&amp;$H35&amp;".html?e="&amp;$A35)</f>
       </c>
     </row>
     <row r="36">
+      <c r="X36" s="1">
+        <f>IF($A36="","","https://momentedit.kr/i/cover-"&amp;$H36&amp;".html?e="&amp;$A36)</f>
+      </c>
       <c r="Y36" s="1">
-        <f>IF($A36="","","https://momentedit.kr/i/cover-"&amp;$H36&amp;".html?e="&amp;$A36)</f>
-      </c>
-      <c r="Z36" s="1">
-        <f>IF(AND($A36&lt;&gt;"",$I36="Y"),"https://momentedit.kr/i-family/family-"&amp;$H36&amp;".html?e="&amp;$A36,"")</f>
+        <f>IF($A36="","","https://momentedit.kr/i-family/family-"&amp;$H36&amp;".html?e="&amp;$A36)</f>
       </c>
     </row>
     <row r="37">
+      <c r="X37" s="1">
+        <f>IF($A37="","","https://momentedit.kr/i/cover-"&amp;$H37&amp;".html?e="&amp;$A37)</f>
+      </c>
       <c r="Y37" s="1">
-        <f>IF($A37="","","https://momentedit.kr/i/cover-"&amp;$H37&amp;".html?e="&amp;$A37)</f>
-      </c>
-      <c r="Z37" s="1">
-        <f>IF(AND($A37&lt;&gt;"",$I37="Y"),"https://momentedit.kr/i-family/family-"&amp;$H37&amp;".html?e="&amp;$A37,"")</f>
+        <f>IF($A37="","","https://momentedit.kr/i-family/family-"&amp;$H37&amp;".html?e="&amp;$A37)</f>
       </c>
     </row>
     <row r="38">
+      <c r="X38" s="1">
+        <f>IF($A38="","","https://momentedit.kr/i/cover-"&amp;$H38&amp;".html?e="&amp;$A38)</f>
+      </c>
       <c r="Y38" s="1">
-        <f>IF($A38="","","https://momentedit.kr/i/cover-"&amp;$H38&amp;".html?e="&amp;$A38)</f>
-      </c>
-      <c r="Z38" s="1">
-        <f>IF(AND($A38&lt;&gt;"",$I38="Y"),"https://momentedit.kr/i-family/family-"&amp;$H38&amp;".html?e="&amp;$A38,"")</f>
+        <f>IF($A38="","","https://momentedit.kr/i-family/family-"&amp;$H38&amp;".html?e="&amp;$A38)</f>
       </c>
     </row>
     <row r="39">
+      <c r="X39" s="1">
+        <f>IF($A39="","","https://momentedit.kr/i/cover-"&amp;$H39&amp;".html?e="&amp;$A39)</f>
+      </c>
       <c r="Y39" s="1">
-        <f>IF($A39="","","https://momentedit.kr/i/cover-"&amp;$H39&amp;".html?e="&amp;$A39)</f>
-      </c>
-      <c r="Z39" s="1">
-        <f>IF(AND($A39&lt;&gt;"",$I39="Y"),"https://momentedit.kr/i-family/family-"&amp;$H39&amp;".html?e="&amp;$A39,"")</f>
+        <f>IF($A39="","","https://momentedit.kr/i-family/family-"&amp;$H39&amp;".html?e="&amp;$A39)</f>
       </c>
     </row>
     <row r="40">
+      <c r="X40" s="1">
+        <f>IF($A40="","","https://momentedit.kr/i/cover-"&amp;$H40&amp;".html?e="&amp;$A40)</f>
+      </c>
       <c r="Y40" s="1">
-        <f>IF($A40="","","https://momentedit.kr/i/cover-"&amp;$H40&amp;".html?e="&amp;$A40)</f>
-      </c>
-      <c r="Z40" s="1">
-        <f>IF(AND($A40&lt;&gt;"",$I40="Y"),"https://momentedit.kr/i-family/family-"&amp;$H40&amp;".html?e="&amp;$A40,"")</f>
+        <f>IF($A40="","","https://momentedit.kr/i-family/family-"&amp;$H40&amp;".html?e="&amp;$A40)</f>
       </c>
     </row>
     <row r="41">
+      <c r="X41" s="1">
+        <f>IF($A41="","","https://momentedit.kr/i/cover-"&amp;$H41&amp;".html?e="&amp;$A41)</f>
+      </c>
       <c r="Y41" s="1">
-        <f>IF($A41="","","https://momentedit.kr/i/cover-"&amp;$H41&amp;".html?e="&amp;$A41)</f>
-      </c>
-      <c r="Z41" s="1">
-        <f>IF(AND($A41&lt;&gt;"",$I41="Y"),"https://momentedit.kr/i-family/family-"&amp;$H41&amp;".html?e="&amp;$A41,"")</f>
+        <f>IF($A41="","","https://momentedit.kr/i-family/family-"&amp;$H41&amp;".html?e="&amp;$A41)</f>
       </c>
     </row>
     <row r="42">
+      <c r="X42" s="1">
+        <f>IF($A42="","","https://momentedit.kr/i/cover-"&amp;$H42&amp;".html?e="&amp;$A42)</f>
+      </c>
       <c r="Y42" s="1">
-        <f>IF($A42="","","https://momentedit.kr/i/cover-"&amp;$H42&amp;".html?e="&amp;$A42)</f>
-      </c>
-      <c r="Z42" s="1">
-        <f>IF(AND($A42&lt;&gt;"",$I42="Y"),"https://momentedit.kr/i-family/family-"&amp;$H42&amp;".html?e="&amp;$A42,"")</f>
+        <f>IF($A42="","","https://momentedit.kr/i-family/family-"&amp;$H42&amp;".html?e="&amp;$A42)</f>
       </c>
     </row>
     <row r="43">
+      <c r="X43" s="1">
+        <f>IF($A43="","","https://momentedit.kr/i/cover-"&amp;$H43&amp;".html?e="&amp;$A43)</f>
+      </c>
       <c r="Y43" s="1">
-        <f>IF($A43="","","https://momentedit.kr/i/cover-"&amp;$H43&amp;".html?e="&amp;$A43)</f>
-      </c>
-      <c r="Z43" s="1">
-        <f>IF(AND($A43&lt;&gt;"",$I43="Y"),"https://momentedit.kr/i-family/family-"&amp;$H43&amp;".html?e="&amp;$A43,"")</f>
+        <f>IF($A43="","","https://momentedit.kr/i-family/family-"&amp;$H43&amp;".html?e="&amp;$A43)</f>
       </c>
     </row>
     <row r="44">
+      <c r="X44" s="1">
+        <f>IF($A44="","","https://momentedit.kr/i/cover-"&amp;$H44&amp;".html?e="&amp;$A44)</f>
+      </c>
       <c r="Y44" s="1">
-        <f>IF($A44="","","https://momentedit.kr/i/cover-"&amp;$H44&amp;".html?e="&amp;$A44)</f>
-      </c>
-      <c r="Z44" s="1">
-        <f>IF(AND($A44&lt;&gt;"",$I44="Y"),"https://momentedit.kr/i-family/family-"&amp;$H44&amp;".html?e="&amp;$A44,"")</f>
+        <f>IF($A44="","","https://momentedit.kr/i-family/family-"&amp;$H44&amp;".html?e="&amp;$A44)</f>
       </c>
     </row>
     <row r="45">
+      <c r="X45" s="1">
+        <f>IF($A45="","","https://momentedit.kr/i/cover-"&amp;$H45&amp;".html?e="&amp;$A45)</f>
+      </c>
       <c r="Y45" s="1">
-        <f>IF($A45="","","https://momentedit.kr/i/cover-"&amp;$H45&amp;".html?e="&amp;$A45)</f>
-      </c>
-      <c r="Z45" s="1">
-        <f>IF(AND($A45&lt;&gt;"",$I45="Y"),"https://momentedit.kr/i-family/family-"&amp;$H45&amp;".html?e="&amp;$A45,"")</f>
+        <f>IF($A45="","","https://momentedit.kr/i-family/family-"&amp;$H45&amp;".html?e="&amp;$A45)</f>
       </c>
     </row>
     <row r="46">
+      <c r="X46" s="1">
+        <f>IF($A46="","","https://momentedit.kr/i/cover-"&amp;$H46&amp;".html?e="&amp;$A46)</f>
+      </c>
       <c r="Y46" s="1">
-        <f>IF($A46="","","https://momentedit.kr/i/cover-"&amp;$H46&amp;".html?e="&amp;$A46)</f>
-      </c>
-      <c r="Z46" s="1">
-        <f>IF(AND($A46&lt;&gt;"",$I46="Y"),"https://momentedit.kr/i-family/family-"&amp;$H46&amp;".html?e="&amp;$A46,"")</f>
+        <f>IF($A46="","","https://momentedit.kr/i-family/family-"&amp;$H46&amp;".html?e="&amp;$A46)</f>
       </c>
     </row>
     <row r="47">
+      <c r="X47" s="1">
+        <f>IF($A47="","","https://momentedit.kr/i/cover-"&amp;$H47&amp;".html?e="&amp;$A47)</f>
+      </c>
       <c r="Y47" s="1">
-        <f>IF($A47="","","https://momentedit.kr/i/cover-"&amp;$H47&amp;".html?e="&amp;$A47)</f>
-      </c>
-      <c r="Z47" s="1">
-        <f>IF(AND($A47&lt;&gt;"",$I47="Y"),"https://momentedit.kr/i-family/family-"&amp;$H47&amp;".html?e="&amp;$A47,"")</f>
+        <f>IF($A47="","","https://momentedit.kr/i-family/family-"&amp;$H47&amp;".html?e="&amp;$A47)</f>
       </c>
     </row>
     <row r="48">
+      <c r="X48" s="1">
+        <f>IF($A48="","","https://momentedit.kr/i/cover-"&amp;$H48&amp;".html?e="&amp;$A48)</f>
+      </c>
       <c r="Y48" s="1">
-        <f>IF($A48="","","https://momentedit.kr/i/cover-"&amp;$H48&amp;".html?e="&amp;$A48)</f>
-      </c>
-      <c r="Z48" s="1">
-        <f>IF(AND($A48&lt;&gt;"",$I48="Y"),"https://momentedit.kr/i-family/family-"&amp;$H48&amp;".html?e="&amp;$A48,"")</f>
+        <f>IF($A48="","","https://momentedit.kr/i-family/family-"&amp;$H48&amp;".html?e="&amp;$A48)</f>
       </c>
     </row>
     <row r="49">
+      <c r="X49" s="1">
+        <f>IF($A49="","","https://momentedit.kr/i/cover-"&amp;$H49&amp;".html?e="&amp;$A49)</f>
+      </c>
       <c r="Y49" s="1">
-        <f>IF($A49="","","https://momentedit.kr/i/cover-"&amp;$H49&amp;".html?e="&amp;$A49)</f>
-      </c>
-      <c r="Z49" s="1">
-        <f>IF(AND($A49&lt;&gt;"",$I49="Y"),"https://momentedit.kr/i-family/family-"&amp;$H49&amp;".html?e="&amp;$A49,"")</f>
+        <f>IF($A49="","","https://momentedit.kr/i-family/family-"&amp;$H49&amp;".html?e="&amp;$A49)</f>
       </c>
     </row>
     <row r="50">
+      <c r="X50" s="1">
+        <f>IF($A50="","","https://momentedit.kr/i/cover-"&amp;$H50&amp;".html?e="&amp;$A50)</f>
+      </c>
       <c r="Y50" s="1">
-        <f>IF($A50="","","https://momentedit.kr/i/cover-"&amp;$H50&amp;".html?e="&amp;$A50)</f>
-      </c>
-      <c r="Z50" s="1">
-        <f>IF(AND($A50&lt;&gt;"",$I50="Y"),"https://momentedit.kr/i-family/family-"&amp;$H50&amp;".html?e="&amp;$A50,"")</f>
+        <f>IF($A50="","","https://momentedit.kr/i-family/family-"&amp;$H50&amp;".html?e="&amp;$A50)</f>
       </c>
     </row>
     <row r="51">
+      <c r="X51" s="1">
+        <f>IF($A51="","","https://momentedit.kr/i/cover-"&amp;$H51&amp;".html?e="&amp;$A51)</f>
+      </c>
       <c r="Y51" s="1">
-        <f>IF($A51="","","https://momentedit.kr/i/cover-"&amp;$H51&amp;".html?e="&amp;$A51)</f>
-      </c>
-      <c r="Z51" s="1">
-        <f>IF(AND($A51&lt;&gt;"",$I51="Y"),"https://momentedit.kr/i-family/family-"&amp;$H51&amp;".html?e="&amp;$A51,"")</f>
+        <f>IF($A51="","","https://momentedit.kr/i-family/family-"&amp;$H51&amp;".html?e="&amp;$A51)</f>
       </c>
     </row>
     <row r="52">
+      <c r="X52" s="1">
+        <f>IF($A52="","","https://momentedit.kr/i/cover-"&amp;$H52&amp;".html?e="&amp;$A52)</f>
+      </c>
       <c r="Y52" s="1">
-        <f>IF($A52="","","https://momentedit.kr/i/cover-"&amp;$H52&amp;".html?e="&amp;$A52)</f>
-      </c>
-      <c r="Z52" s="1">
-        <f>IF(AND($A52&lt;&gt;"",$I52="Y"),"https://momentedit.kr/i-family/family-"&amp;$H52&amp;".html?e="&amp;$A52,"")</f>
+        <f>IF($A52="","","https://momentedit.kr/i-family/family-"&amp;$H52&amp;".html?e="&amp;$A52)</f>
       </c>
     </row>
     <row r="53">
+      <c r="X53" s="1">
+        <f>IF($A53="","","https://momentedit.kr/i/cover-"&amp;$H53&amp;".html?e="&amp;$A53)</f>
+      </c>
       <c r="Y53" s="1">
-        <f>IF($A53="","","https://momentedit.kr/i/cover-"&amp;$H53&amp;".html?e="&amp;$A53)</f>
-      </c>
-      <c r="Z53" s="1">
-        <f>IF(AND($A53&lt;&gt;"",$I53="Y"),"https://momentedit.kr/i-family/family-"&amp;$H53&amp;".html?e="&amp;$A53,"")</f>
+        <f>IF($A53="","","https://momentedit.kr/i-family/family-"&amp;$H53&amp;".html?e="&amp;$A53)</f>
       </c>
     </row>
     <row r="54">
+      <c r="X54" s="1">
+        <f>IF($A54="","","https://momentedit.kr/i/cover-"&amp;$H54&amp;".html?e="&amp;$A54)</f>
+      </c>
       <c r="Y54" s="1">
-        <f>IF($A54="","","https://momentedit.kr/i/cover-"&amp;$H54&amp;".html?e="&amp;$A54)</f>
-      </c>
-      <c r="Z54" s="1">
-        <f>IF(AND($A54&lt;&gt;"",$I54="Y"),"https://momentedit.kr/i-family/family-"&amp;$H54&amp;".html?e="&amp;$A54,"")</f>
+        <f>IF($A54="","","https://momentedit.kr/i-family/family-"&amp;$H54&amp;".html?e="&amp;$A54)</f>
       </c>
     </row>
     <row r="55">
+      <c r="X55" s="1">
+        <f>IF($A55="","","https://momentedit.kr/i/cover-"&amp;$H55&amp;".html?e="&amp;$A55)</f>
+      </c>
       <c r="Y55" s="1">
-        <f>IF($A55="","","https://momentedit.kr/i/cover-"&amp;$H55&amp;".html?e="&amp;$A55)</f>
-      </c>
-      <c r="Z55" s="1">
-        <f>IF(AND($A55&lt;&gt;"",$I55="Y"),"https://momentedit.kr/i-family/family-"&amp;$H55&amp;".html?e="&amp;$A55,"")</f>
+        <f>IF($A55="","","https://momentedit.kr/i-family/family-"&amp;$H55&amp;".html?e="&amp;$A55)</f>
       </c>
     </row>
     <row r="56">
+      <c r="X56" s="1">
+        <f>IF($A56="","","https://momentedit.kr/i/cover-"&amp;$H56&amp;".html?e="&amp;$A56)</f>
+      </c>
       <c r="Y56" s="1">
-        <f>IF($A56="","","https://momentedit.kr/i/cover-"&amp;$H56&amp;".html?e="&amp;$A56)</f>
-      </c>
-      <c r="Z56" s="1">
-        <f>IF(AND($A56&lt;&gt;"",$I56="Y"),"https://momentedit.kr/i-family/family-"&amp;$H56&amp;".html?e="&amp;$A56,"")</f>
+        <f>IF($A56="","","https://momentedit.kr/i-family/family-"&amp;$H56&amp;".html?e="&amp;$A56)</f>
       </c>
     </row>
     <row r="57">
+      <c r="X57" s="1">
+        <f>IF($A57="","","https://momentedit.kr/i/cover-"&amp;$H57&amp;".html?e="&amp;$A57)</f>
+      </c>
       <c r="Y57" s="1">
-        <f>IF($A57="","","https://momentedit.kr/i/cover-"&amp;$H57&amp;".html?e="&amp;$A57)</f>
-      </c>
-      <c r="Z57" s="1">
-        <f>IF(AND($A57&lt;&gt;"",$I57="Y"),"https://momentedit.kr/i-family/family-"&amp;$H57&amp;".html?e="&amp;$A57,"")</f>
+        <f>IF($A57="","","https://momentedit.kr/i-family/family-"&amp;$H57&amp;".html?e="&amp;$A57)</f>
       </c>
     </row>
     <row r="58">
+      <c r="X58" s="1">
+        <f>IF($A58="","","https://momentedit.kr/i/cover-"&amp;$H58&amp;".html?e="&amp;$A58)</f>
+      </c>
       <c r="Y58" s="1">
-        <f>IF($A58="","","https://momentedit.kr/i/cover-"&amp;$H58&amp;".html?e="&amp;$A58)</f>
-      </c>
-      <c r="Z58" s="1">
-        <f>IF(AND($A58&lt;&gt;"",$I58="Y"),"https://momentedit.kr/i-family/family-"&amp;$H58&amp;".html?e="&amp;$A58,"")</f>
+        <f>IF($A58="","","https://momentedit.kr/i-family/family-"&amp;$H58&amp;".html?e="&amp;$A58)</f>
       </c>
     </row>
     <row r="59">
+      <c r="X59" s="1">
+        <f>IF($A59="","","https://momentedit.kr/i/cover-"&amp;$H59&amp;".html?e="&amp;$A59)</f>
+      </c>
       <c r="Y59" s="1">
-        <f>IF($A59="","","https://momentedit.kr/i/cover-"&amp;$H59&amp;".html?e="&amp;$A59)</f>
-      </c>
-      <c r="Z59" s="1">
-        <f>IF(AND($A59&lt;&gt;"",$I59="Y"),"https://momentedit.kr/i-family/family-"&amp;$H59&amp;".html?e="&amp;$A59,"")</f>
+        <f>IF($A59="","","https://momentedit.kr/i-family/family-"&amp;$H59&amp;".html?e="&amp;$A59)</f>
       </c>
     </row>
     <row r="60">
+      <c r="X60" s="1">
+        <f>IF($A60="","","https://momentedit.kr/i/cover-"&amp;$H60&amp;".html?e="&amp;$A60)</f>
+      </c>
       <c r="Y60" s="1">
-        <f>IF($A60="","","https://momentedit.kr/i/cover-"&amp;$H60&amp;".html?e="&amp;$A60)</f>
-      </c>
-      <c r="Z60" s="1">
-        <f>IF(AND($A60&lt;&gt;"",$I60="Y"),"https://momentedit.kr/i-family/family-"&amp;$H60&amp;".html?e="&amp;$A60,"")</f>
+        <f>IF($A60="","","https://momentedit.kr/i-family/family-"&amp;$H60&amp;".html?e="&amp;$A60)</f>
       </c>
     </row>
     <row r="61">
+      <c r="X61" s="1">
+        <f>IF($A61="","","https://momentedit.kr/i/cover-"&amp;$H61&amp;".html?e="&amp;$A61)</f>
+      </c>
       <c r="Y61" s="1">
-        <f>IF($A61="","","https://momentedit.kr/i/cover-"&amp;$H61&amp;".html?e="&amp;$A61)</f>
-      </c>
-      <c r="Z61" s="1">
-        <f>IF(AND($A61&lt;&gt;"",$I61="Y"),"https://momentedit.kr/i-family/family-"&amp;$H61&amp;".html?e="&amp;$A61,"")</f>
+        <f>IF($A61="","","https://momentedit.kr/i-family/family-"&amp;$H61&amp;".html?e="&amp;$A61)</f>
       </c>
     </row>
     <row r="62">
+      <c r="X62" s="1">
+        <f>IF($A62="","","https://momentedit.kr/i/cover-"&amp;$H62&amp;".html?e="&amp;$A62)</f>
+      </c>
       <c r="Y62" s="1">
-        <f>IF($A62="","","https://momentedit.kr/i/cover-"&amp;$H62&amp;".html?e="&amp;$A62)</f>
-      </c>
-      <c r="Z62" s="1">
-        <f>IF(AND($A62&lt;&gt;"",$I62="Y"),"https://momentedit.kr/i-family/family-"&amp;$H62&amp;".html?e="&amp;$A62,"")</f>
+        <f>IF($A62="","","https://momentedit.kr/i-family/family-"&amp;$H62&amp;".html?e="&amp;$A62)</f>
       </c>
     </row>
     <row r="63">
+      <c r="X63" s="1">
+        <f>IF($A63="","","https://momentedit.kr/i/cover-"&amp;$H63&amp;".html?e="&amp;$A63)</f>
+      </c>
       <c r="Y63" s="1">
-        <f>IF($A63="","","https://momentedit.kr/i/cover-"&amp;$H63&amp;".html?e="&amp;$A63)</f>
-      </c>
-      <c r="Z63" s="1">
-        <f>IF(AND($A63&lt;&gt;"",$I63="Y"),"https://momentedit.kr/i-family/family-"&amp;$H63&amp;".html?e="&amp;$A63,"")</f>
+        <f>IF($A63="","","https://momentedit.kr/i-family/family-"&amp;$H63&amp;".html?e="&amp;$A63)</f>
       </c>
     </row>
     <row r="64">
+      <c r="X64" s="1">
+        <f>IF($A64="","","https://momentedit.kr/i/cover-"&amp;$H64&amp;".html?e="&amp;$A64)</f>
+      </c>
       <c r="Y64" s="1">
-        <f>IF($A64="","","https://momentedit.kr/i/cover-"&amp;$H64&amp;".html?e="&amp;$A64)</f>
-      </c>
-      <c r="Z64" s="1">
-        <f>IF(AND($A64&lt;&gt;"",$I64="Y"),"https://momentedit.kr/i-family/family-"&amp;$H64&amp;".html?e="&amp;$A64,"")</f>
+        <f>IF($A64="","","https://momentedit.kr/i-family/family-"&amp;$H64&amp;".html?e="&amp;$A64)</f>
       </c>
     </row>
     <row r="65">
+      <c r="X65" s="1">
+        <f>IF($A65="","","https://momentedit.kr/i/cover-"&amp;$H65&amp;".html?e="&amp;$A65)</f>
+      </c>
       <c r="Y65" s="1">
-        <f>IF($A65="","","https://momentedit.kr/i/cover-"&amp;$H65&amp;".html?e="&amp;$A65)</f>
-      </c>
-      <c r="Z65" s="1">
-        <f>IF(AND($A65&lt;&gt;"",$I65="Y"),"https://momentedit.kr/i-family/family-"&amp;$H65&amp;".html?e="&amp;$A65,"")</f>
+        <f>IF($A65="","","https://momentedit.kr/i-family/family-"&amp;$H65&amp;".html?e="&amp;$A65)</f>
       </c>
     </row>
     <row r="66">
+      <c r="X66" s="1">
+        <f>IF($A66="","","https://momentedit.kr/i/cover-"&amp;$H66&amp;".html?e="&amp;$A66)</f>
+      </c>
       <c r="Y66" s="1">
-        <f>IF($A66="","","https://momentedit.kr/i/cover-"&amp;$H66&amp;".html?e="&amp;$A66)</f>
-      </c>
-      <c r="Z66" s="1">
-        <f>IF(AND($A66&lt;&gt;"",$I66="Y"),"https://momentedit.kr/i-family/family-"&amp;$H66&amp;".html?e="&amp;$A66,"")</f>
+        <f>IF($A66="","","https://momentedit.kr/i-family/family-"&amp;$H66&amp;".html?e="&amp;$A66)</f>
       </c>
     </row>
     <row r="67">
+      <c r="X67" s="1">
+        <f>IF($A67="","","https://momentedit.kr/i/cover-"&amp;$H67&amp;".html?e="&amp;$A67)</f>
+      </c>
       <c r="Y67" s="1">
-        <f>IF($A67="","","https://momentedit.kr/i/cover-"&amp;$H67&amp;".html?e="&amp;$A67)</f>
-      </c>
-      <c r="Z67" s="1">
-        <f>IF(AND($A67&lt;&gt;"",$I67="Y"),"https://momentedit.kr/i-family/family-"&amp;$H67&amp;".html?e="&amp;$A67,"")</f>
+        <f>IF($A67="","","https://momentedit.kr/i-family/family-"&amp;$H67&amp;".html?e="&amp;$A67)</f>
       </c>
     </row>
     <row r="68">
+      <c r="X68" s="1">
+        <f>IF($A68="","","https://momentedit.kr/i/cover-"&amp;$H68&amp;".html?e="&amp;$A68)</f>
+      </c>
       <c r="Y68" s="1">
-        <f>IF($A68="","","https://momentedit.kr/i/cover-"&amp;$H68&amp;".html?e="&amp;$A68)</f>
-      </c>
-      <c r="Z68" s="1">
-        <f>IF(AND($A68&lt;&gt;"",$I68="Y"),"https://momentedit.kr/i-family/family-"&amp;$H68&amp;".html?e="&amp;$A68,"")</f>
+        <f>IF($A68="","","https://momentedit.kr/i-family/family-"&amp;$H68&amp;".html?e="&amp;$A68)</f>
       </c>
     </row>
     <row r="69">
+      <c r="X69" s="1">
+        <f>IF($A69="","","https://momentedit.kr/i/cover-"&amp;$H69&amp;".html?e="&amp;$A69)</f>
+      </c>
       <c r="Y69" s="1">
-        <f>IF($A69="","","https://momentedit.kr/i/cover-"&amp;$H69&amp;".html?e="&amp;$A69)</f>
-      </c>
-      <c r="Z69" s="1">
-        <f>IF(AND($A69&lt;&gt;"",$I69="Y"),"https://momentedit.kr/i-family/family-"&amp;$H69&amp;".html?e="&amp;$A69,"")</f>
+        <f>IF($A69="","","https://momentedit.kr/i-family/family-"&amp;$H69&amp;".html?e="&amp;$A69)</f>
       </c>
     </row>
     <row r="70">
+      <c r="X70" s="1">
+        <f>IF($A70="","","https://momentedit.kr/i/cover-"&amp;$H70&amp;".html?e="&amp;$A70)</f>
+      </c>
       <c r="Y70" s="1">
-        <f>IF($A70="","","https://momentedit.kr/i/cover-"&amp;$H70&amp;".html?e="&amp;$A70)</f>
-      </c>
-      <c r="Z70" s="1">
-        <f>IF(AND($A70&lt;&gt;"",$I70="Y"),"https://momentedit.kr/i-family/family-"&amp;$H70&amp;".html?e="&amp;$A70,"")</f>
+        <f>IF($A70="","","https://momentedit.kr/i-family/family-"&amp;$H70&amp;".html?e="&amp;$A70)</f>
       </c>
     </row>
     <row r="71">
+      <c r="X71" s="1">
+        <f>IF($A71="","","https://momentedit.kr/i/cover-"&amp;$H71&amp;".html?e="&amp;$A71)</f>
+      </c>
       <c r="Y71" s="1">
-        <f>IF($A71="","","https://momentedit.kr/i/cover-"&amp;$H71&amp;".html?e="&amp;$A71)</f>
-      </c>
-      <c r="Z71" s="1">
-        <f>IF(AND($A71&lt;&gt;"",$I71="Y"),"https://momentedit.kr/i-family/family-"&amp;$H71&amp;".html?e="&amp;$A71,"")</f>
+        <f>IF($A71="","","https://momentedit.kr/i-family/family-"&amp;$H71&amp;".html?e="&amp;$A71)</f>
       </c>
     </row>
     <row r="72">
+      <c r="X72" s="1">
+        <f>IF($A72="","","https://momentedit.kr/i/cover-"&amp;$H72&amp;".html?e="&amp;$A72)</f>
+      </c>
       <c r="Y72" s="1">
-        <f>IF($A72="","","https://momentedit.kr/i/cover-"&amp;$H72&amp;".html?e="&amp;$A72)</f>
-      </c>
-      <c r="Z72" s="1">
-        <f>IF(AND($A72&lt;&gt;"",$I72="Y"),"https://momentedit.kr/i-family/family-"&amp;$H72&amp;".html?e="&amp;$A72,"")</f>
+        <f>IF($A72="","","https://momentedit.kr/i-family/family-"&amp;$H72&amp;".html?e="&amp;$A72)</f>
       </c>
     </row>
     <row r="73">
+      <c r="X73" s="1">
+        <f>IF($A73="","","https://momentedit.kr/i/cover-"&amp;$H73&amp;".html?e="&amp;$A73)</f>
+      </c>
       <c r="Y73" s="1">
-        <f>IF($A73="","","https://momentedit.kr/i/cover-"&amp;$H73&amp;".html?e="&amp;$A73)</f>
-      </c>
-      <c r="Z73" s="1">
-        <f>IF(AND($A73&lt;&gt;"",$I73="Y"),"https://momentedit.kr/i-family/family-"&amp;$H73&amp;".html?e="&amp;$A73,"")</f>
+        <f>IF($A73="","","https://momentedit.kr/i-family/family-"&amp;$H73&amp;".html?e="&amp;$A73)</f>
       </c>
     </row>
     <row r="74">
+      <c r="X74" s="1">
+        <f>IF($A74="","","https://momentedit.kr/i/cover-"&amp;$H74&amp;".html?e="&amp;$A74)</f>
+      </c>
       <c r="Y74" s="1">
-        <f>IF($A74="","","https://momentedit.kr/i/cover-"&amp;$H74&amp;".html?e="&amp;$A74)</f>
-      </c>
-      <c r="Z74" s="1">
-        <f>IF(AND($A74&lt;&gt;"",$I74="Y"),"https://momentedit.kr/i-family/family-"&amp;$H74&amp;".html?e="&amp;$A74,"")</f>
+        <f>IF($A74="","","https://momentedit.kr/i-family/family-"&amp;$H74&amp;".html?e="&amp;$A74)</f>
       </c>
     </row>
     <row r="75">
+      <c r="X75" s="1">
+        <f>IF($A75="","","https://momentedit.kr/i/cover-"&amp;$H75&amp;".html?e="&amp;$A75)</f>
+      </c>
       <c r="Y75" s="1">
-        <f>IF($A75="","","https://momentedit.kr/i/cover-"&amp;$H75&amp;".html?e="&amp;$A75)</f>
-      </c>
-      <c r="Z75" s="1">
-        <f>IF(AND($A75&lt;&gt;"",$I75="Y"),"https://momentedit.kr/i-family/family-"&amp;$H75&amp;".html?e="&amp;$A75,"")</f>
+        <f>IF($A75="","","https://momentedit.kr/i-family/family-"&amp;$H75&amp;".html?e="&amp;$A75)</f>
       </c>
     </row>
     <row r="76">
+      <c r="X76" s="1">
+        <f>IF($A76="","","https://momentedit.kr/i/cover-"&amp;$H76&amp;".html?e="&amp;$A76)</f>
+      </c>
       <c r="Y76" s="1">
-        <f>IF($A76="","","https://momentedit.kr/i/cover-"&amp;$H76&amp;".html?e="&amp;$A76)</f>
-      </c>
-      <c r="Z76" s="1">
-        <f>IF(AND($A76&lt;&gt;"",$I76="Y"),"https://momentedit.kr/i-family/family-"&amp;$H76&amp;".html?e="&amp;$A76,"")</f>
+        <f>IF($A76="","","https://momentedit.kr/i-family/family-"&amp;$H76&amp;".html?e="&amp;$A76)</f>
       </c>
     </row>
     <row r="77">
+      <c r="X77" s="1">
+        <f>IF($A77="","","https://momentedit.kr/i/cover-"&amp;$H77&amp;".html?e="&amp;$A77)</f>
+      </c>
       <c r="Y77" s="1">
-        <f>IF($A77="","","https://momentedit.kr/i/cover-"&amp;$H77&amp;".html?e="&amp;$A77)</f>
-      </c>
-      <c r="Z77" s="1">
-        <f>IF(AND($A77&lt;&gt;"",$I77="Y"),"https://momentedit.kr/i-family/family-"&amp;$H77&amp;".html?e="&amp;$A77,"")</f>
+        <f>IF($A77="","","https://momentedit.kr/i-family/family-"&amp;$H77&amp;".html?e="&amp;$A77)</f>
       </c>
     </row>
     <row r="78">
+      <c r="X78" s="1">
+        <f>IF($A78="","","https://momentedit.kr/i/cover-"&amp;$H78&amp;".html?e="&amp;$A78)</f>
+      </c>
       <c r="Y78" s="1">
-        <f>IF($A78="","","https://momentedit.kr/i/cover-"&amp;$H78&amp;".html?e="&amp;$A78)</f>
-      </c>
-      <c r="Z78" s="1">
-        <f>IF(AND($A78&lt;&gt;"",$I78="Y"),"https://momentedit.kr/i-family/family-"&amp;$H78&amp;".html?e="&amp;$A78,"")</f>
+        <f>IF($A78="","","https://momentedit.kr/i-family/family-"&amp;$H78&amp;".html?e="&amp;$A78)</f>
       </c>
     </row>
     <row r="79">
+      <c r="X79" s="1">
+        <f>IF($A79="","","https://momentedit.kr/i/cover-"&amp;$H79&amp;".html?e="&amp;$A79)</f>
+      </c>
       <c r="Y79" s="1">
-        <f>IF($A79="","","https://momentedit.kr/i/cover-"&amp;$H79&amp;".html?e="&amp;$A79)</f>
-      </c>
-      <c r="Z79" s="1">
-        <f>IF(AND($A79&lt;&gt;"",$I79="Y"),"https://momentedit.kr/i-family/family-"&amp;$H79&amp;".html?e="&amp;$A79,"")</f>
+        <f>IF($A79="","","https://momentedit.kr/i-family/family-"&amp;$H79&amp;".html?e="&amp;$A79)</f>
       </c>
     </row>
     <row r="80">
+      <c r="X80" s="1">
+        <f>IF($A80="","","https://momentedit.kr/i/cover-"&amp;$H80&amp;".html?e="&amp;$A80)</f>
+      </c>
       <c r="Y80" s="1">
-        <f>IF($A80="","","https://momentedit.kr/i/cover-"&amp;$H80&amp;".html?e="&amp;$A80)</f>
-      </c>
-      <c r="Z80" s="1">
-        <f>IF(AND($A80&lt;&gt;"",$I80="Y"),"https://momentedit.kr/i-family/family-"&amp;$H80&amp;".html?e="&amp;$A80,"")</f>
+        <f>IF($A80="","","https://momentedit.kr/i-family/family-"&amp;$H80&amp;".html?e="&amp;$A80)</f>
       </c>
     </row>
     <row r="81">
+      <c r="X81" s="1">
+        <f>IF($A81="","","https://momentedit.kr/i/cover-"&amp;$H81&amp;".html?e="&amp;$A81)</f>
+      </c>
       <c r="Y81" s="1">
-        <f>IF($A81="","","https://momentedit.kr/i/cover-"&amp;$H81&amp;".html?e="&amp;$A81)</f>
-      </c>
-      <c r="Z81" s="1">
-        <f>IF(AND($A81&lt;&gt;"",$I81="Y"),"https://momentedit.kr/i-family/family-"&amp;$H81&amp;".html?e="&amp;$A81,"")</f>
+        <f>IF($A81="","","https://momentedit.kr/i-family/family-"&amp;$H81&amp;".html?e="&amp;$A81)</f>
       </c>
     </row>
     <row r="82">
+      <c r="X82" s="1">
+        <f>IF($A82="","","https://momentedit.kr/i/cover-"&amp;$H82&amp;".html?e="&amp;$A82)</f>
+      </c>
       <c r="Y82" s="1">
-        <f>IF($A82="","","https://momentedit.kr/i/cover-"&amp;$H82&amp;".html?e="&amp;$A82)</f>
-      </c>
-      <c r="Z82" s="1">
-        <f>IF(AND($A82&lt;&gt;"",$I82="Y"),"https://momentedit.kr/i-family/family-"&amp;$H82&amp;".html?e="&amp;$A82,"")</f>
+        <f>IF($A82="","","https://momentedit.kr/i-family/family-"&amp;$H82&amp;".html?e="&amp;$A82)</f>
       </c>
     </row>
     <row r="83">
+      <c r="X83" s="1">
+        <f>IF($A83="","","https://momentedit.kr/i/cover-"&amp;$H83&amp;".html?e="&amp;$A83)</f>
+      </c>
       <c r="Y83" s="1">
-        <f>IF($A83="","","https://momentedit.kr/i/cover-"&amp;$H83&amp;".html?e="&amp;$A83)</f>
-      </c>
-      <c r="Z83" s="1">
-        <f>IF(AND($A83&lt;&gt;"",$I83="Y"),"https://momentedit.kr/i-family/family-"&amp;$H83&amp;".html?e="&amp;$A83,"")</f>
+        <f>IF($A83="","","https://momentedit.kr/i-family/family-"&amp;$H83&amp;".html?e="&amp;$A83)</f>
       </c>
     </row>
     <row r="84">
+      <c r="X84" s="1">
+        <f>IF($A84="","","https://momentedit.kr/i/cover-"&amp;$H84&amp;".html?e="&amp;$A84)</f>
+      </c>
       <c r="Y84" s="1">
-        <f>IF($A84="","","https://momentedit.kr/i/cover-"&amp;$H84&amp;".html?e="&amp;$A84)</f>
-      </c>
-      <c r="Z84" s="1">
-        <f>IF(AND($A84&lt;&gt;"",$I84="Y"),"https://momentedit.kr/i-family/family-"&amp;$H84&amp;".html?e="&amp;$A84,"")</f>
+        <f>IF($A84="","","https://momentedit.kr/i-family/family-"&amp;$H84&amp;".html?e="&amp;$A84)</f>
       </c>
     </row>
     <row r="85">
+      <c r="X85" s="1">
+        <f>IF($A85="","","https://momentedit.kr/i/cover-"&amp;$H85&amp;".html?e="&amp;$A85)</f>
+      </c>
       <c r="Y85" s="1">
-        <f>IF($A85="","","https://momentedit.kr/i/cover-"&amp;$H85&amp;".html?e="&amp;$A85)</f>
-      </c>
-      <c r="Z85" s="1">
-        <f>IF(AND($A85&lt;&gt;"",$I85="Y"),"https://momentedit.kr/i-family/family-"&amp;$H85&amp;".html?e="&amp;$A85,"")</f>
+        <f>IF($A85="","","https://momentedit.kr/i-family/family-"&amp;$H85&amp;".html?e="&amp;$A85)</f>
       </c>
     </row>
     <row r="86">
+      <c r="X86" s="1">
+        <f>IF($A86="","","https://momentedit.kr/i/cover-"&amp;$H86&amp;".html?e="&amp;$A86)</f>
+      </c>
       <c r="Y86" s="1">
-        <f>IF($A86="","","https://momentedit.kr/i/cover-"&amp;$H86&amp;".html?e="&amp;$A86)</f>
-      </c>
-      <c r="Z86" s="1">
-        <f>IF(AND($A86&lt;&gt;"",$I86="Y"),"https://momentedit.kr/i-family/family-"&amp;$H86&amp;".html?e="&amp;$A86,"")</f>
+        <f>IF($A86="","","https://momentedit.kr/i-family/family-"&amp;$H86&amp;".html?e="&amp;$A86)</f>
       </c>
     </row>
     <row r="87">
+      <c r="X87" s="1">
+        <f>IF($A87="","","https://momentedit.kr/i/cover-"&amp;$H87&amp;".html?e="&amp;$A87)</f>
+      </c>
       <c r="Y87" s="1">
-        <f>IF($A87="","","https://momentedit.kr/i/cover-"&amp;$H87&amp;".html?e="&amp;$A87)</f>
-      </c>
-      <c r="Z87" s="1">
-        <f>IF(AND($A87&lt;&gt;"",$I87="Y"),"https://momentedit.kr/i-family/family-"&amp;$H87&amp;".html?e="&amp;$A87,"")</f>
+        <f>IF($A87="","","https://momentedit.kr/i-family/family-"&amp;$H87&amp;".html?e="&amp;$A87)</f>
       </c>
     </row>
     <row r="88">
+      <c r="X88" s="1">
+        <f>IF($A88="","","https://momentedit.kr/i/cover-"&amp;$H88&amp;".html?e="&amp;$A88)</f>
+      </c>
       <c r="Y88" s="1">
-        <f>IF($A88="","","https://momentedit.kr/i/cover-"&amp;$H88&amp;".html?e="&amp;$A88)</f>
-      </c>
-      <c r="Z88" s="1">
-        <f>IF(AND($A88&lt;&gt;"",$I88="Y"),"https://momentedit.kr/i-family/family-"&amp;$H88&amp;".html?e="&amp;$A88,"")</f>
+        <f>IF($A88="","","https://momentedit.kr/i-family/family-"&amp;$H88&amp;".html?e="&amp;$A88)</f>
       </c>
     </row>
     <row r="89">
+      <c r="X89" s="1">
+        <f>IF($A89="","","https://momentedit.kr/i/cover-"&amp;$H89&amp;".html?e="&amp;$A89)</f>
+      </c>
       <c r="Y89" s="1">
-        <f>IF($A89="","","https://momentedit.kr/i/cover-"&amp;$H89&amp;".html?e="&amp;$A89)</f>
-      </c>
-      <c r="Z89" s="1">
-        <f>IF(AND($A89&lt;&gt;"",$I89="Y"),"https://momentedit.kr/i-family/family-"&amp;$H89&amp;".html?e="&amp;$A89,"")</f>
+        <f>IF($A89="","","https://momentedit.kr/i-family/family-"&amp;$H89&amp;".html?e="&amp;$A89)</f>
       </c>
     </row>
     <row r="90">
+      <c r="X90" s="1">
+        <f>IF($A90="","","https://momentedit.kr/i/cover-"&amp;$H90&amp;".html?e="&amp;$A90)</f>
+      </c>
       <c r="Y90" s="1">
-        <f>IF($A90="","","https://momentedit.kr/i/cover-"&amp;$H90&amp;".html?e="&amp;$A90)</f>
-      </c>
-      <c r="Z90" s="1">
-        <f>IF(AND($A90&lt;&gt;"",$I90="Y"),"https://momentedit.kr/i-family/family-"&amp;$H90&amp;".html?e="&amp;$A90,"")</f>
+        <f>IF($A90="","","https://momentedit.kr/i-family/family-"&amp;$H90&amp;".html?e="&amp;$A90)</f>
       </c>
     </row>
     <row r="91">
+      <c r="X91" s="1">
+        <f>IF($A91="","","https://momentedit.kr/i/cover-"&amp;$H91&amp;".html?e="&amp;$A91)</f>
+      </c>
       <c r="Y91" s="1">
-        <f>IF($A91="","","https://momentedit.kr/i/cover-"&amp;$H91&amp;".html?e="&amp;$A91)</f>
-      </c>
-      <c r="Z91" s="1">
-        <f>IF(AND($A91&lt;&gt;"",$I91="Y"),"https://momentedit.kr/i-family/family-"&amp;$H91&amp;".html?e="&amp;$A91,"")</f>
+        <f>IF($A91="","","https://momentedit.kr/i-family/family-"&amp;$H91&amp;".html?e="&amp;$A91)</f>
       </c>
     </row>
     <row r="92">
+      <c r="X92" s="1">
+        <f>IF($A92="","","https://momentedit.kr/i/cover-"&amp;$H92&amp;".html?e="&amp;$A92)</f>
+      </c>
       <c r="Y92" s="1">
-        <f>IF($A92="","","https://momentedit.kr/i/cover-"&amp;$H92&amp;".html?e="&amp;$A92)</f>
-      </c>
-      <c r="Z92" s="1">
-        <f>IF(AND($A92&lt;&gt;"",$I92="Y"),"https://momentedit.kr/i-family/family-"&amp;$H92&amp;".html?e="&amp;$A92,"")</f>
+        <f>IF($A92="","","https://momentedit.kr/i-family/family-"&amp;$H92&amp;".html?e="&amp;$A92)</f>
       </c>
     </row>
     <row r="93">
+      <c r="X93" s="1">
+        <f>IF($A93="","","https://momentedit.kr/i/cover-"&amp;$H93&amp;".html?e="&amp;$A93)</f>
+      </c>
       <c r="Y93" s="1">
-        <f>IF($A93="","","https://momentedit.kr/i/cover-"&amp;$H93&amp;".html?e="&amp;$A93)</f>
-      </c>
-      <c r="Z93" s="1">
-        <f>IF(AND($A93&lt;&gt;"",$I93="Y"),"https://momentedit.kr/i-family/family-"&amp;$H93&amp;".html?e="&amp;$A93,"")</f>
+        <f>IF($A93="","","https://momentedit.kr/i-family/family-"&amp;$H93&amp;".html?e="&amp;$A93)</f>
       </c>
     </row>
     <row r="94">
+      <c r="X94" s="1">
+        <f>IF($A94="","","https://momentedit.kr/i/cover-"&amp;$H94&amp;".html?e="&amp;$A94)</f>
+      </c>
       <c r="Y94" s="1">
-        <f>IF($A94="","","https://momentedit.kr/i/cover-"&amp;$H94&amp;".html?e="&amp;$A94)</f>
-      </c>
-      <c r="Z94" s="1">
-        <f>IF(AND($A94&lt;&gt;"",$I94="Y"),"https://momentedit.kr/i-family/family-"&amp;$H94&amp;".html?e="&amp;$A94,"")</f>
+        <f>IF($A94="","","https://momentedit.kr/i-family/family-"&amp;$H94&amp;".html?e="&amp;$A94)</f>
       </c>
     </row>
     <row r="95">
+      <c r="X95" s="1">
+        <f>IF($A95="","","https://momentedit.kr/i/cover-"&amp;$H95&amp;".html?e="&amp;$A95)</f>
+      </c>
       <c r="Y95" s="1">
-        <f>IF($A95="","","https://momentedit.kr/i/cover-"&amp;$H95&amp;".html?e="&amp;$A95)</f>
-      </c>
-      <c r="Z95" s="1">
-        <f>IF(AND($A95&lt;&gt;"",$I95="Y"),"https://momentedit.kr/i-family/family-"&amp;$H95&amp;".html?e="&amp;$A95,"")</f>
+        <f>IF($A95="","","https://momentedit.kr/i-family/family-"&amp;$H95&amp;".html?e="&amp;$A95)</f>
       </c>
     </row>
     <row r="96">
+      <c r="X96" s="1">
+        <f>IF($A96="","","https://momentedit.kr/i/cover-"&amp;$H96&amp;".html?e="&amp;$A96)</f>
+      </c>
       <c r="Y96" s="1">
-        <f>IF($A96="","","https://momentedit.kr/i/cover-"&amp;$H96&amp;".html?e="&amp;$A96)</f>
-      </c>
-      <c r="Z96" s="1">
-        <f>IF(AND($A96&lt;&gt;"",$I96="Y"),"https://momentedit.kr/i-family/family-"&amp;$H96&amp;".html?e="&amp;$A96,"")</f>
+        <f>IF($A96="","","https://momentedit.kr/i-family/family-"&amp;$H96&amp;".html?e="&amp;$A96)</f>
       </c>
     </row>
     <row r="97">
+      <c r="X97" s="1">
+        <f>IF($A97="","","https://momentedit.kr/i/cover-"&amp;$H97&amp;".html?e="&amp;$A97)</f>
+      </c>
       <c r="Y97" s="1">
-        <f>IF($A97="","","https://momentedit.kr/i/cover-"&amp;$H97&amp;".html?e="&amp;$A97)</f>
-      </c>
-      <c r="Z97" s="1">
-        <f>IF(AND($A97&lt;&gt;"",$I97="Y"),"https://momentedit.kr/i-family/family-"&amp;$H97&amp;".html?e="&amp;$A97,"")</f>
+        <f>IF($A97="","","https://momentedit.kr/i-family/family-"&amp;$H97&amp;".html?e="&amp;$A97)</f>
       </c>
     </row>
     <row r="98">
+      <c r="X98" s="1">
+        <f>IF($A98="","","https://momentedit.kr/i/cover-"&amp;$H98&amp;".html?e="&amp;$A98)</f>
+      </c>
       <c r="Y98" s="1">
-        <f>IF($A98="","","https://momentedit.kr/i/cover-"&amp;$H98&amp;".html?e="&amp;$A98)</f>
-      </c>
-      <c r="Z98" s="1">
-        <f>IF(AND($A98&lt;&gt;"",$I98="Y"),"https://momentedit.kr/i-family/family-"&amp;$H98&amp;".html?e="&amp;$A98,"")</f>
+        <f>IF($A98="","","https://momentedit.kr/i-family/family-"&amp;$H98&amp;".html?e="&amp;$A98)</f>
       </c>
     </row>
     <row r="99">
+      <c r="X99" s="1">
+        <f>IF($A99="","","https://momentedit.kr/i/cover-"&amp;$H99&amp;".html?e="&amp;$A99)</f>
+      </c>
       <c r="Y99" s="1">
-        <f>IF($A99="","","https://momentedit.kr/i/cover-"&amp;$H99&amp;".html?e="&amp;$A99)</f>
-      </c>
-      <c r="Z99" s="1">
-        <f>IF(AND($A99&lt;&gt;"",$I99="Y"),"https://momentedit.kr/i-family/family-"&amp;$H99&amp;".html?e="&amp;$A99,"")</f>
+        <f>IF($A99="","","https://momentedit.kr/i-family/family-"&amp;$H99&amp;".html?e="&amp;$A99)</f>
       </c>
     </row>
     <row r="100">
+      <c r="X100" s="1">
+        <f>IF($A100="","","https://momentedit.kr/i/cover-"&amp;$H100&amp;".html?e="&amp;$A100)</f>
+      </c>
       <c r="Y100" s="1">
-        <f>IF($A100="","","https://momentedit.kr/i/cover-"&amp;$H100&amp;".html?e="&amp;$A100)</f>
-      </c>
-      <c r="Z100" s="1">
-        <f>IF(AND($A100&lt;&gt;"",$I100="Y"),"https://momentedit.kr/i-family/family-"&amp;$H100&amp;".html?e="&amp;$A100,"")</f>
+        <f>IF($A100="","","https://momentedit.kr/i-family/family-"&amp;$H100&amp;".html?e="&amp;$A100)</f>
       </c>
     </row>
     <row r="101">
+      <c r="X101" s="1">
+        <f>IF($A101="","","https://momentedit.kr/i/cover-"&amp;$H101&amp;".html?e="&amp;$A101)</f>
+      </c>
       <c r="Y101" s="1">
-        <f>IF($A101="","","https://momentedit.kr/i/cover-"&amp;$H101&amp;".html?e="&amp;$A101)</f>
-      </c>
-      <c r="Z101" s="1">
-        <f>IF(AND($A101&lt;&gt;"",$I101="Y"),"https://momentedit.kr/i-family/family-"&amp;$H101&amp;".html?e="&amp;$A101,"")</f>
+        <f>IF($A101="","","https://momentedit.kr/i-family/family-"&amp;$H101&amp;".html?e="&amp;$A101)</f>
       </c>
     </row>
     <row r="102">
+      <c r="X102" s="1">
+        <f>IF($A102="","","https://momentedit.kr/i/cover-"&amp;$H102&amp;".html?e="&amp;$A102)</f>
+      </c>
       <c r="Y102" s="1">
-        <f>IF($A102="","","https://momentedit.kr/i/cover-"&amp;$H102&amp;".html?e="&amp;$A102)</f>
-      </c>
-      <c r="Z102" s="1">
-        <f>IF(AND($A102&lt;&gt;"",$I102="Y"),"https://momentedit.kr/i-family/family-"&amp;$H102&amp;".html?e="&amp;$A102,"")</f>
+        <f>IF($A102="","","https://momentedit.kr/i-family/family-"&amp;$H102&amp;".html?e="&amp;$A102)</f>
       </c>
     </row>
     <row r="103">
+      <c r="X103" s="1">
+        <f>IF($A103="","","https://momentedit.kr/i/cover-"&amp;$H103&amp;".html?e="&amp;$A103)</f>
+      </c>
       <c r="Y103" s="1">
-        <f>IF($A103="","","https://momentedit.kr/i/cover-"&amp;$H103&amp;".html?e="&amp;$A103)</f>
-      </c>
-      <c r="Z103" s="1">
-        <f>IF(AND($A103&lt;&gt;"",$I103="Y"),"https://momentedit.kr/i-family/family-"&amp;$H103&amp;".html?e="&amp;$A103,"")</f>
+        <f>IF($A103="","","https://momentedit.kr/i-family/family-"&amp;$H103&amp;".html?e="&amp;$A103)</f>
       </c>
     </row>
     <row r="104">
+      <c r="X104" s="1">
+        <f>IF($A104="","","https://momentedit.kr/i/cover-"&amp;$H104&amp;".html?e="&amp;$A104)</f>
+      </c>
       <c r="Y104" s="1">
-        <f>IF($A104="","","https://momentedit.kr/i/cover-"&amp;$H104&amp;".html?e="&amp;$A104)</f>
-      </c>
-      <c r="Z104" s="1">
-        <f>IF(AND($A104&lt;&gt;"",$I104="Y"),"https://momentedit.kr/i-family/family-"&amp;$H104&amp;".html?e="&amp;$A104,"")</f>
+        <f>IF($A104="","","https://momentedit.kr/i-family/family-"&amp;$H104&amp;".html?e="&amp;$A104)</f>
       </c>
     </row>
     <row r="105">
+      <c r="X105" s="1">
+        <f>IF($A105="","","https://momentedit.kr/i/cover-"&amp;$H105&amp;".html?e="&amp;$A105)</f>
+      </c>
       <c r="Y105" s="1">
-        <f>IF($A105="","","https://momentedit.kr/i/cover-"&amp;$H105&amp;".html?e="&amp;$A105)</f>
-      </c>
-      <c r="Z105" s="1">
-        <f>IF(AND($A105&lt;&gt;"",$I105="Y"),"https://momentedit.kr/i-family/family-"&amp;$H105&amp;".html?e="&amp;$A105,"")</f>
+        <f>IF($A105="","","https://momentedit.kr/i-family/family-"&amp;$H105&amp;".html?e="&amp;$A105)</f>
       </c>
     </row>
     <row r="106">
+      <c r="X106" s="1">
+        <f>IF($A106="","","https://momentedit.kr/i/cover-"&amp;$H106&amp;".html?e="&amp;$A106)</f>
+      </c>
       <c r="Y106" s="1">
-        <f>IF($A106="","","https://momentedit.kr/i/cover-"&amp;$H106&amp;".html?e="&amp;$A106)</f>
-      </c>
-      <c r="Z106" s="1">
-        <f>IF(AND($A106&lt;&gt;"",$I106="Y"),"https://momentedit.kr/i-family/family-"&amp;$H106&amp;".html?e="&amp;$A106,"")</f>
+        <f>IF($A106="","","https://momentedit.kr/i-family/family-"&amp;$H106&amp;".html?e="&amp;$A106)</f>
       </c>
     </row>
     <row r="107">
+      <c r="X107" s="1">
+        <f>IF($A107="","","https://momentedit.kr/i/cover-"&amp;$H107&amp;".html?e="&amp;$A107)</f>
+      </c>
       <c r="Y107" s="1">
-        <f>IF($A107="","","https://momentedit.kr/i/cover-"&amp;$H107&amp;".html?e="&amp;$A107)</f>
-      </c>
-      <c r="Z107" s="1">
-        <f>IF(AND($A107&lt;&gt;"",$I107="Y"),"https://momentedit.kr/i-family/family-"&amp;$H107&amp;".html?e="&amp;$A107,"")</f>
+        <f>IF($A107="","","https://momentedit.kr/i-family/family-"&amp;$H107&amp;".html?e="&amp;$A107)</f>
       </c>
     </row>
     <row r="108">
+      <c r="X108" s="1">
+        <f>IF($A108="","","https://momentedit.kr/i/cover-"&amp;$H108&amp;".html?e="&amp;$A108)</f>
+      </c>
       <c r="Y108" s="1">
-        <f>IF($A108="","","https://momentedit.kr/i/cover-"&amp;$H108&amp;".html?e="&amp;$A108)</f>
-      </c>
-      <c r="Z108" s="1">
-        <f>IF(AND($A108&lt;&gt;"",$I108="Y"),"https://momentedit.kr/i-family/family-"&amp;$H108&amp;".html?e="&amp;$A108,"")</f>
+        <f>IF($A108="","","https://momentedit.kr/i-family/family-"&amp;$H108&amp;".html?e="&amp;$A108)</f>
       </c>
     </row>
     <row r="109">
+      <c r="X109" s="1">
+        <f>IF($A109="","","https://momentedit.kr/i/cover-"&amp;$H109&amp;".html?e="&amp;$A109)</f>
+      </c>
       <c r="Y109" s="1">
-        <f>IF($A109="","","https://momentedit.kr/i/cover-"&amp;$H109&amp;".html?e="&amp;$A109)</f>
-      </c>
-      <c r="Z109" s="1">
-        <f>IF(AND($A109&lt;&gt;"",$I109="Y"),"https://momentedit.kr/i-family/family-"&amp;$H109&amp;".html?e="&amp;$A109,"")</f>
+        <f>IF($A109="","","https://momentedit.kr/i-family/family-"&amp;$H109&amp;".html?e="&amp;$A109)</f>
       </c>
     </row>
     <row r="110">
+      <c r="X110" s="1">
+        <f>IF($A110="","","https://momentedit.kr/i/cover-"&amp;$H110&amp;".html?e="&amp;$A110)</f>
+      </c>
       <c r="Y110" s="1">
-        <f>IF($A110="","","https://momentedit.kr/i/cover-"&amp;$H110&amp;".html?e="&amp;$A110)</f>
-      </c>
-      <c r="Z110" s="1">
-        <f>IF(AND($A110&lt;&gt;"",$I110="Y"),"https://momentedit.kr/i-family/family-"&amp;$H110&amp;".html?e="&amp;$A110,"")</f>
+        <f>IF($A110="","","https://momentedit.kr/i-family/family-"&amp;$H110&amp;".html?e="&amp;$A110)</f>
       </c>
     </row>
     <row r="111">
+      <c r="X111" s="1">
+        <f>IF($A111="","","https://momentedit.kr/i/cover-"&amp;$H111&amp;".html?e="&amp;$A111)</f>
+      </c>
       <c r="Y111" s="1">
-        <f>IF($A111="","","https://momentedit.kr/i/cover-"&amp;$H111&amp;".html?e="&amp;$A111)</f>
-      </c>
-      <c r="Z111" s="1">
-        <f>IF(AND($A111&lt;&gt;"",$I111="Y"),"https://momentedit.kr/i-family/family-"&amp;$H111&amp;".html?e="&amp;$A111,"")</f>
+        <f>IF($A111="","","https://momentedit.kr/i-family/family-"&amp;$H111&amp;".html?e="&amp;$A111)</f>
       </c>
     </row>
     <row r="112">
+      <c r="X112" s="1">
+        <f>IF($A112="","","https://momentedit.kr/i/cover-"&amp;$H112&amp;".html?e="&amp;$A112)</f>
+      </c>
       <c r="Y112" s="1">
-        <f>IF($A112="","","https://momentedit.kr/i/cover-"&amp;$H112&amp;".html?e="&amp;$A112)</f>
-      </c>
-      <c r="Z112" s="1">
-        <f>IF(AND($A112&lt;&gt;"",$I112="Y"),"https://momentedit.kr/i-family/family-"&amp;$H112&amp;".html?e="&amp;$A112,"")</f>
+        <f>IF($A112="","","https://momentedit.kr/i-family/family-"&amp;$H112&amp;".html?e="&amp;$A112)</f>
       </c>
     </row>
     <row r="113">
+      <c r="X113" s="1">
+        <f>IF($A113="","","https://momentedit.kr/i/cover-"&amp;$H113&amp;".html?e="&amp;$A113)</f>
+      </c>
       <c r="Y113" s="1">
-        <f>IF($A113="","","https://momentedit.kr/i/cover-"&amp;$H113&amp;".html?e="&amp;$A113)</f>
-      </c>
-      <c r="Z113" s="1">
-        <f>IF(AND($A113&lt;&gt;"",$I113="Y"),"https://momentedit.kr/i-family/family-"&amp;$H113&amp;".html?e="&amp;$A113,"")</f>
+        <f>IF($A113="","","https://momentedit.kr/i-family/family-"&amp;$H113&amp;".html?e="&amp;$A113)</f>
       </c>
     </row>
     <row r="114">
+      <c r="X114" s="1">
+        <f>IF($A114="","","https://momentedit.kr/i/cover-"&amp;$H114&amp;".html?e="&amp;$A114)</f>
+      </c>
       <c r="Y114" s="1">
-        <f>IF($A114="","","https://momentedit.kr/i/cover-"&amp;$H114&amp;".html?e="&amp;$A114)</f>
-      </c>
-      <c r="Z114" s="1">
-        <f>IF(AND($A114&lt;&gt;"",$I114="Y"),"https://momentedit.kr/i-family/family-"&amp;$H114&amp;".html?e="&amp;$A114,"")</f>
+        <f>IF($A114="","","https://momentedit.kr/i-family/family-"&amp;$H114&amp;".html?e="&amp;$A114)</f>
       </c>
     </row>
     <row r="115">
+      <c r="X115" s="1">
+        <f>IF($A115="","","https://momentedit.kr/i/cover-"&amp;$H115&amp;".html?e="&amp;$A115)</f>
+      </c>
       <c r="Y115" s="1">
-        <f>IF($A115="","","https://momentedit.kr/i/cover-"&amp;$H115&amp;".html?e="&amp;$A115)</f>
-      </c>
-      <c r="Z115" s="1">
-        <f>IF(AND($A115&lt;&gt;"",$I115="Y"),"https://momentedit.kr/i-family/family-"&amp;$H115&amp;".html?e="&amp;$A115,"")</f>
+        <f>IF($A115="","","https://momentedit.kr/i-family/family-"&amp;$H115&amp;".html?e="&amp;$A115)</f>
       </c>
     </row>
     <row r="116">
+      <c r="X116" s="1">
+        <f>IF($A116="","","https://momentedit.kr/i/cover-"&amp;$H116&amp;".html?e="&amp;$A116)</f>
+      </c>
       <c r="Y116" s="1">
-        <f>IF($A116="","","https://momentedit.kr/i/cover-"&amp;$H116&amp;".html?e="&amp;$A116)</f>
-      </c>
-      <c r="Z116" s="1">
-        <f>IF(AND($A116&lt;&gt;"",$I116="Y"),"https://momentedit.kr/i-family/family-"&amp;$H116&amp;".html?e="&amp;$A116,"")</f>
+        <f>IF($A116="","","https://momentedit.kr/i-family/family-"&amp;$H116&amp;".html?e="&amp;$A116)</f>
       </c>
     </row>
     <row r="117">
+      <c r="X117" s="1">
+        <f>IF($A117="","","https://momentedit.kr/i/cover-"&amp;$H117&amp;".html?e="&amp;$A117)</f>
+      </c>
       <c r="Y117" s="1">
-        <f>IF($A117="","","https://momentedit.kr/i/cover-"&amp;$H117&amp;".html?e="&amp;$A117)</f>
-      </c>
-      <c r="Z117" s="1">
-        <f>IF(AND($A117&lt;&gt;"",$I117="Y"),"https://momentedit.kr/i-family/family-"&amp;$H117&amp;".html?e="&amp;$A117,"")</f>
+        <f>IF($A117="","","https://momentedit.kr/i-family/family-"&amp;$H117&amp;".html?e="&amp;$A117)</f>
       </c>
     </row>
     <row r="118">
+      <c r="X118" s="1">
+        <f>IF($A118="","","https://momentedit.kr/i/cover-"&amp;$H118&amp;".html?e="&amp;$A118)</f>
+      </c>
       <c r="Y118" s="1">
-        <f>IF($A118="","","https://momentedit.kr/i/cover-"&amp;$H118&amp;".html?e="&amp;$A118)</f>
-      </c>
-      <c r="Z118" s="1">
-        <f>IF(AND($A118&lt;&gt;"",$I118="Y"),"https://momentedit.kr/i-family/family-"&amp;$H118&amp;".html?e="&amp;$A118,"")</f>
+        <f>IF($A118="","","https://momentedit.kr/i-family/family-"&amp;$H118&amp;".html?e="&amp;$A118)</f>
       </c>
     </row>
     <row r="119">
+      <c r="X119" s="1">
+        <f>IF($A119="","","https://momentedit.kr/i/cover-"&amp;$H119&amp;".html?e="&amp;$A119)</f>
+      </c>
       <c r="Y119" s="1">
-        <f>IF($A119="","","https://momentedit.kr/i/cover-"&amp;$H119&amp;".html?e="&amp;$A119)</f>
-      </c>
-      <c r="Z119" s="1">
-        <f>IF(AND($A119&lt;&gt;"",$I119="Y"),"https://momentedit.kr/i-family/family-"&amp;$H119&amp;".html?e="&amp;$A119,"")</f>
+        <f>IF($A119="","","https://momentedit.kr/i-family/family-"&amp;$H119&amp;".html?e="&amp;$A119)</f>
       </c>
     </row>
     <row r="120">
+      <c r="X120" s="1">
+        <f>IF($A120="","","https://momentedit.kr/i/cover-"&amp;$H120&amp;".html?e="&amp;$A120)</f>
+      </c>
       <c r="Y120" s="1">
-        <f>IF($A120="","","https://momentedit.kr/i/cover-"&amp;$H120&amp;".html?e="&amp;$A120)</f>
-      </c>
-      <c r="Z120" s="1">
-        <f>IF(AND($A120&lt;&gt;"",$I120="Y"),"https://momentedit.kr/i-family/family-"&amp;$H120&amp;".html?e="&amp;$A120,"")</f>
+        <f>IF($A120="","","https://momentedit.kr/i-family/family-"&amp;$H120&amp;".html?e="&amp;$A120)</f>
       </c>
     </row>
     <row r="121">
+      <c r="X121" s="1">
+        <f>IF($A121="","","https://momentedit.kr/i/cover-"&amp;$H121&amp;".html?e="&amp;$A121)</f>
+      </c>
       <c r="Y121" s="1">
-        <f>IF($A121="","","https://momentedit.kr/i/cover-"&amp;$H121&amp;".html?e="&amp;$A121)</f>
-      </c>
-      <c r="Z121" s="1">
-        <f>IF(AND($A121&lt;&gt;"",$I121="Y"),"https://momentedit.kr/i-family/family-"&amp;$H121&amp;".html?e="&amp;$A121,"")</f>
+        <f>IF($A121="","","https://momentedit.kr/i-family/family-"&amp;$H121&amp;".html?e="&amp;$A121)</f>
       </c>
     </row>
     <row r="122">
+      <c r="X122" s="1">
+        <f>IF($A122="","","https://momentedit.kr/i/cover-"&amp;$H122&amp;".html?e="&amp;$A122)</f>
+      </c>
       <c r="Y122" s="1">
-        <f>IF($A122="","","https://momentedit.kr/i/cover-"&amp;$H122&amp;".html?e="&amp;$A122)</f>
-      </c>
-      <c r="Z122" s="1">
-        <f>IF(AND($A122&lt;&gt;"",$I122="Y"),"https://momentedit.kr/i-family/family-"&amp;$H122&amp;".html?e="&amp;$A122,"")</f>
+        <f>IF($A122="","","https://momentedit.kr/i-family/family-"&amp;$H122&amp;".html?e="&amp;$A122)</f>
       </c>
     </row>
     <row r="123">
+      <c r="X123" s="1">
+        <f>IF($A123="","","https://momentedit.kr/i/cover-"&amp;$H123&amp;".html?e="&amp;$A123)</f>
+      </c>
       <c r="Y123" s="1">
-        <f>IF($A123="","","https://momentedit.kr/i/cover-"&amp;$H123&amp;".html?e="&amp;$A123)</f>
-      </c>
-      <c r="Z123" s="1">
-        <f>IF(AND($A123&lt;&gt;"",$I123="Y"),"https://momentedit.kr/i-family/family-"&amp;$H123&amp;".html?e="&amp;$A123,"")</f>
+        <f>IF($A123="","","https://momentedit.kr/i-family/family-"&amp;$H123&amp;".html?e="&amp;$A123)</f>
       </c>
     </row>
     <row r="124">
+      <c r="X124" s="1">
+        <f>IF($A124="","","https://momentedit.kr/i/cover-"&amp;$H124&amp;".html?e="&amp;$A124)</f>
+      </c>
       <c r="Y124" s="1">
-        <f>IF($A124="","","https://momentedit.kr/i/cover-"&amp;$H124&amp;".html?e="&amp;$A124)</f>
-      </c>
-      <c r="Z124" s="1">
-        <f>IF(AND($A124&lt;&gt;"",$I124="Y"),"https://momentedit.kr/i-family/family-"&amp;$H124&amp;".html?e="&amp;$A124,"")</f>
+        <f>IF($A124="","","https://momentedit.kr/i-family/family-"&amp;$H124&amp;".html?e="&amp;$A124)</f>
       </c>
     </row>
     <row r="125">
+      <c r="X125" s="1">
+        <f>IF($A125="","","https://momentedit.kr/i/cover-"&amp;$H125&amp;".html?e="&amp;$A125)</f>
+      </c>
       <c r="Y125" s="1">
-        <f>IF($A125="","","https://momentedit.kr/i/cover-"&amp;$H125&amp;".html?e="&amp;$A125)</f>
-      </c>
-      <c r="Z125" s="1">
-        <f>IF(AND($A125&lt;&gt;"",$I125="Y"),"https://momentedit.kr/i-family/family-"&amp;$H125&amp;".html?e="&amp;$A125,"")</f>
+        <f>IF($A125="","","https://momentedit.kr/i-family/family-"&amp;$H125&amp;".html?e="&amp;$A125)</f>
       </c>
     </row>
     <row r="126">
+      <c r="X126" s="1">
+        <f>IF($A126="","","https://momentedit.kr/i/cover-"&amp;$H126&amp;".html?e="&amp;$A126)</f>
+      </c>
       <c r="Y126" s="1">
-        <f>IF($A126="","","https://momentedit.kr/i/cover-"&amp;$H126&amp;".html?e="&amp;$A126)</f>
-      </c>
-      <c r="Z126" s="1">
-        <f>IF(AND($A126&lt;&gt;"",$I126="Y"),"https://momentedit.kr/i-family/family-"&amp;$H126&amp;".html?e="&amp;$A126,"")</f>
+        <f>IF($A126="","","https://momentedit.kr/i-family/family-"&amp;$H126&amp;".html?e="&amp;$A126)</f>
       </c>
     </row>
     <row r="127">
+      <c r="X127" s="1">
+        <f>IF($A127="","","https://momentedit.kr/i/cover-"&amp;$H127&amp;".html?e="&amp;$A127)</f>
+      </c>
       <c r="Y127" s="1">
-        <f>IF($A127="","","https://momentedit.kr/i/cover-"&amp;$H127&amp;".html?e="&amp;$A127)</f>
-      </c>
-      <c r="Z127" s="1">
-        <f>IF(AND($A127&lt;&gt;"",$I127="Y"),"https://momentedit.kr/i-family/family-"&amp;$H127&amp;".html?e="&amp;$A127,"")</f>
+        <f>IF($A127="","","https://momentedit.kr/i-family/family-"&amp;$H127&amp;".html?e="&amp;$A127)</f>
       </c>
     </row>
     <row r="128">
+      <c r="X128" s="1">
+        <f>IF($A128="","","https://momentedit.kr/i/cover-"&amp;$H128&amp;".html?e="&amp;$A128)</f>
+      </c>
       <c r="Y128" s="1">
-        <f>IF($A128="","","https://momentedit.kr/i/cover-"&amp;$H128&amp;".html?e="&amp;$A128)</f>
-      </c>
-      <c r="Z128" s="1">
-        <f>IF(AND($A128&lt;&gt;"",$I128="Y"),"https://momentedit.kr/i-family/family-"&amp;$H128&amp;".html?e="&amp;$A128,"")</f>
+        <f>IF($A128="","","https://momentedit.kr/i-family/family-"&amp;$H128&amp;".html?e="&amp;$A128)</f>
       </c>
     </row>
     <row r="129">
+      <c r="X129" s="1">
+        <f>IF($A129="","","https://momentedit.kr/i/cover-"&amp;$H129&amp;".html?e="&amp;$A129)</f>
+      </c>
       <c r="Y129" s="1">
-        <f>IF($A129="","","https://momentedit.kr/i/cover-"&amp;$H129&amp;".html?e="&amp;$A129)</f>
-      </c>
-      <c r="Z129" s="1">
-        <f>IF(AND($A129&lt;&gt;"",$I129="Y"),"https://momentedit.kr/i-family/family-"&amp;$H129&amp;".html?e="&amp;$A129,"")</f>
+        <f>IF($A129="","","https://momentedit.kr/i-family/family-"&amp;$H129&amp;".html?e="&amp;$A129)</f>
       </c>
     </row>
     <row r="130">
+      <c r="X130" s="1">
+        <f>IF($A130="","","https://momentedit.kr/i/cover-"&amp;$H130&amp;".html?e="&amp;$A130)</f>
+      </c>
       <c r="Y130" s="1">
-        <f>IF($A130="","","https://momentedit.kr/i/cover-"&amp;$H130&amp;".html?e="&amp;$A130)</f>
-      </c>
-      <c r="Z130" s="1">
-        <f>IF(AND($A130&lt;&gt;"",$I130="Y"),"https://momentedit.kr/i-family/family-"&amp;$H130&amp;".html?e="&amp;$A130,"")</f>
+        <f>IF($A130="","","https://momentedit.kr/i-family/family-"&amp;$H130&amp;".html?e="&amp;$A130)</f>
       </c>
     </row>
     <row r="131">
+      <c r="X131" s="1">
+        <f>IF($A131="","","https://momentedit.kr/i/cover-"&amp;$H131&amp;".html?e="&amp;$A131)</f>
+      </c>
       <c r="Y131" s="1">
-        <f>IF($A131="","","https://momentedit.kr/i/cover-"&amp;$H131&amp;".html?e="&amp;$A131)</f>
-      </c>
-      <c r="Z131" s="1">
-        <f>IF(AND($A131&lt;&gt;"",$I131="Y"),"https://momentedit.kr/i-family/family-"&amp;$H131&amp;".html?e="&amp;$A131,"")</f>
+        <f>IF($A131="","","https://momentedit.kr/i-family/family-"&amp;$H131&amp;".html?e="&amp;$A131)</f>
       </c>
     </row>
     <row r="132">
+      <c r="X132" s="1">
+        <f>IF($A132="","","https://momentedit.kr/i/cover-"&amp;$H132&amp;".html?e="&amp;$A132)</f>
+      </c>
       <c r="Y132" s="1">
-        <f>IF($A132="","","https://momentedit.kr/i/cover-"&amp;$H132&amp;".html?e="&amp;$A132)</f>
-      </c>
-      <c r="Z132" s="1">
-        <f>IF(AND($A132&lt;&gt;"",$I132="Y"),"https://momentedit.kr/i-family/family-"&amp;$H132&amp;".html?e="&amp;$A132,"")</f>
+        <f>IF($A132="","","https://momentedit.kr/i-family/family-"&amp;$H132&amp;".html?e="&amp;$A132)</f>
       </c>
     </row>
     <row r="133">
+      <c r="X133" s="1">
+        <f>IF($A133="","","https://momentedit.kr/i/cover-"&amp;$H133&amp;".html?e="&amp;$A133)</f>
+      </c>
       <c r="Y133" s="1">
-        <f>IF($A133="","","https://momentedit.kr/i/cover-"&amp;$H133&amp;".html?e="&amp;$A133)</f>
-      </c>
-      <c r="Z133" s="1">
-        <f>IF(AND($A133&lt;&gt;"",$I133="Y"),"https://momentedit.kr/i-family/family-"&amp;$H133&amp;".html?e="&amp;$A133,"")</f>
+        <f>IF($A133="","","https://momentedit.kr/i-family/family-"&amp;$H133&amp;".html?e="&amp;$A133)</f>
       </c>
     </row>
     <row r="134">
+      <c r="X134" s="1">
+        <f>IF($A134="","","https://momentedit.kr/i/cover-"&amp;$H134&amp;".html?e="&amp;$A134)</f>
+      </c>
       <c r="Y134" s="1">
-        <f>IF($A134="","","https://momentedit.kr/i/cover-"&amp;$H134&amp;".html?e="&amp;$A134)</f>
-      </c>
-      <c r="Z134" s="1">
-        <f>IF(AND($A134&lt;&gt;"",$I134="Y"),"https://momentedit.kr/i-family/family-"&amp;$H134&amp;".html?e="&amp;$A134,"")</f>
+        <f>IF($A134="","","https://momentedit.kr/i-family/family-"&amp;$H134&amp;".html?e="&amp;$A134)</f>
       </c>
     </row>
     <row r="135">
+      <c r="X135" s="1">
+        <f>IF($A135="","","https://momentedit.kr/i/cover-"&amp;$H135&amp;".html?e="&amp;$A135)</f>
+      </c>
       <c r="Y135" s="1">
-        <f>IF($A135="","","https://momentedit.kr/i/cover-"&amp;$H135&amp;".html?e="&amp;$A135)</f>
-      </c>
-      <c r="Z135" s="1">
-        <f>IF(AND($A135&lt;&gt;"",$I135="Y"),"https://momentedit.kr/i-family/family-"&amp;$H135&amp;".html?e="&amp;$A135,"")</f>
+        <f>IF($A135="","","https://momentedit.kr/i-family/family-"&amp;$H135&amp;".html?e="&amp;$A135)</f>
       </c>
     </row>
     <row r="136">
+      <c r="X136" s="1">
+        <f>IF($A136="","","https://momentedit.kr/i/cover-"&amp;$H136&amp;".html?e="&amp;$A136)</f>
+      </c>
       <c r="Y136" s="1">
-        <f>IF($A136="","","https://momentedit.kr/i/cover-"&amp;$H136&amp;".html?e="&amp;$A136)</f>
-      </c>
-      <c r="Z136" s="1">
-        <f>IF(AND($A136&lt;&gt;"",$I136="Y"),"https://momentedit.kr/i-family/family-"&amp;$H136&amp;".html?e="&amp;$A136,"")</f>
+        <f>IF($A136="","","https://momentedit.kr/i-family/family-"&amp;$H136&amp;".html?e="&amp;$A136)</f>
       </c>
     </row>
     <row r="137">
+      <c r="X137" s="1">
+        <f>IF($A137="","","https://momentedit.kr/i/cover-"&amp;$H137&amp;".html?e="&amp;$A137)</f>
+      </c>
       <c r="Y137" s="1">
-        <f>IF($A137="","","https://momentedit.kr/i/cover-"&amp;$H137&amp;".html?e="&amp;$A137)</f>
-      </c>
-      <c r="Z137" s="1">
-        <f>IF(AND($A137&lt;&gt;"",$I137="Y"),"https://momentedit.kr/i-family/family-"&amp;$H137&amp;".html?e="&amp;$A137,"")</f>
+        <f>IF($A137="","","https://momentedit.kr/i-family/family-"&amp;$H137&amp;".html?e="&amp;$A137)</f>
       </c>
     </row>
     <row r="138">
+      <c r="X138" s="1">
+        <f>IF($A138="","","https://momentedit.kr/i/cover-"&amp;$H138&amp;".html?e="&amp;$A138)</f>
+      </c>
       <c r="Y138" s="1">
-        <f>IF($A138="","","https://momentedit.kr/i/cover-"&amp;$H138&amp;".html?e="&amp;$A138)</f>
-      </c>
-      <c r="Z138" s="1">
-        <f>IF(AND($A138&lt;&gt;"",$I138="Y"),"https://momentedit.kr/i-family/family-"&amp;$H138&amp;".html?e="&amp;$A138,"")</f>
+        <f>IF($A138="","","https://momentedit.kr/i-family/family-"&amp;$H138&amp;".html?e="&amp;$A138)</f>
       </c>
     </row>
     <row r="139">
+      <c r="X139" s="1">
+        <f>IF($A139="","","https://momentedit.kr/i/cover-"&amp;$H139&amp;".html?e="&amp;$A139)</f>
+      </c>
       <c r="Y139" s="1">
-        <f>IF($A139="","","https://momentedit.kr/i/cover-"&amp;$H139&amp;".html?e="&amp;$A139)</f>
-      </c>
-      <c r="Z139" s="1">
-        <f>IF(AND($A139&lt;&gt;"",$I139="Y"),"https://momentedit.kr/i-family/family-"&amp;$H139&amp;".html?e="&amp;$A139,"")</f>
+        <f>IF($A139="","","https://momentedit.kr/i-family/family-"&amp;$H139&amp;".html?e="&amp;$A139)</f>
       </c>
     </row>
     <row r="140">
+      <c r="X140" s="1">
+        <f>IF($A140="","","https://momentedit.kr/i/cover-"&amp;$H140&amp;".html?e="&amp;$A140)</f>
+      </c>
       <c r="Y140" s="1">
-        <f>IF($A140="","","https://momentedit.kr/i/cover-"&amp;$H140&amp;".html?e="&amp;$A140)</f>
-      </c>
-      <c r="Z140" s="1">
-        <f>IF(AND($A140&lt;&gt;"",$I140="Y"),"https://momentedit.kr/i-family/family-"&amp;$H140&amp;".html?e="&amp;$A140,"")</f>
+        <f>IF($A140="","","https://momentedit.kr/i-family/family-"&amp;$H140&amp;".html?e="&amp;$A140)</f>
       </c>
     </row>
     <row r="141">
+      <c r="X141" s="1">
+        <f>IF($A141="","","https://momentedit.kr/i/cover-"&amp;$H141&amp;".html?e="&amp;$A141)</f>
+      </c>
       <c r="Y141" s="1">
-        <f>IF($A141="","","https://momentedit.kr/i/cover-"&amp;$H141&amp;".html?e="&amp;$A141)</f>
-      </c>
-      <c r="Z141" s="1">
-        <f>IF(AND($A141&lt;&gt;"",$I141="Y"),"https://momentedit.kr/i-family/family-"&amp;$H141&amp;".html?e="&amp;$A141,"")</f>
+        <f>IF($A141="","","https://momentedit.kr/i-family/family-"&amp;$H141&amp;".html?e="&amp;$A141)</f>
       </c>
     </row>
     <row r="142">
+      <c r="X142" s="1">
+        <f>IF($A142="","","https://momentedit.kr/i/cover-"&amp;$H142&amp;".html?e="&amp;$A142)</f>
+      </c>
       <c r="Y142" s="1">
-        <f>IF($A142="","","https://momentedit.kr/i/cover-"&amp;$H142&amp;".html?e="&amp;$A142)</f>
-      </c>
-      <c r="Z142" s="1">
-        <f>IF(AND($A142&lt;&gt;"",$I142="Y"),"https://momentedit.kr/i-family/family-"&amp;$H142&amp;".html?e="&amp;$A142,"")</f>
+        <f>IF($A142="","","https://momentedit.kr/i-family/family-"&amp;$H142&amp;".html?e="&amp;$A142)</f>
       </c>
     </row>
     <row r="143">
+      <c r="X143" s="1">
+        <f>IF($A143="","","https://momentedit.kr/i/cover-"&amp;$H143&amp;".html?e="&amp;$A143)</f>
+      </c>
       <c r="Y143" s="1">
-        <f>IF($A143="","","https://momentedit.kr/i/cover-"&amp;$H143&amp;".html?e="&amp;$A143)</f>
-      </c>
-      <c r="Z143" s="1">
-        <f>IF(AND($A143&lt;&gt;"",$I143="Y"),"https://momentedit.kr/i-family/family-"&amp;$H143&amp;".html?e="&amp;$A143,"")</f>
+        <f>IF($A143="","","https://momentedit.kr/i-family/family-"&amp;$H143&amp;".html?e="&amp;$A143)</f>
       </c>
     </row>
     <row r="144">
+      <c r="X144" s="1">
+        <f>IF($A144="","","https://momentedit.kr/i/cover-"&amp;$H144&amp;".html?e="&amp;$A144)</f>
+      </c>
       <c r="Y144" s="1">
-        <f>IF($A144="","","https://momentedit.kr/i/cover-"&amp;$H144&amp;".html?e="&amp;$A144)</f>
-      </c>
-      <c r="Z144" s="1">
-        <f>IF(AND($A144&lt;&gt;"",$I144="Y"),"https://momentedit.kr/i-family/family-"&amp;$H144&amp;".html?e="&amp;$A144,"")</f>
+        <f>IF($A144="","","https://momentedit.kr/i-family/family-"&amp;$H144&amp;".html?e="&amp;$A144)</f>
       </c>
     </row>
     <row r="145">
+      <c r="X145" s="1">
+        <f>IF($A145="","","https://momentedit.kr/i/cover-"&amp;$H145&amp;".html?e="&amp;$A145)</f>
+      </c>
       <c r="Y145" s="1">
-        <f>IF($A145="","","https://momentedit.kr/i/cover-"&amp;$H145&amp;".html?e="&amp;$A145)</f>
-      </c>
-      <c r="Z145" s="1">
-        <f>IF(AND($A145&lt;&gt;"",$I145="Y"),"https://momentedit.kr/i-family/family-"&amp;$H145&amp;".html?e="&amp;$A145,"")</f>
+        <f>IF($A145="","","https://momentedit.kr/i-family/family-"&amp;$H145&amp;".html?e="&amp;$A145)</f>
       </c>
     </row>
     <row r="146">
+      <c r="X146" s="1">
+        <f>IF($A146="","","https://momentedit.kr/i/cover-"&amp;$H146&amp;".html?e="&amp;$A146)</f>
+      </c>
       <c r="Y146" s="1">
-        <f>IF($A146="","","https://momentedit.kr/i/cover-"&amp;$H146&amp;".html?e="&amp;$A146)</f>
-      </c>
-      <c r="Z146" s="1">
-        <f>IF(AND($A146&lt;&gt;"",$I146="Y"),"https://momentedit.kr/i-family/family-"&amp;$H146&amp;".html?e="&amp;$A146,"")</f>
+        <f>IF($A146="","","https://momentedit.kr/i-family/family-"&amp;$H146&amp;".html?e="&amp;$A146)</f>
       </c>
     </row>
     <row r="147">
+      <c r="X147" s="1">
+        <f>IF($A147="","","https://momentedit.kr/i/cover-"&amp;$H147&amp;".html?e="&amp;$A147)</f>
+      </c>
       <c r="Y147" s="1">
-        <f>IF($A147="","","https://momentedit.kr/i/cover-"&amp;$H147&amp;".html?e="&amp;$A147)</f>
-      </c>
-      <c r="Z147" s="1">
-        <f>IF(AND($A147&lt;&gt;"",$I147="Y"),"https://momentedit.kr/i-family/family-"&amp;$H147&amp;".html?e="&amp;$A147,"")</f>
+        <f>IF($A147="","","https://momentedit.kr/i-family/family-"&amp;$H147&amp;".html?e="&amp;$A147)</f>
       </c>
     </row>
     <row r="148">
+      <c r="X148" s="1">
+        <f>IF($A148="","","https://momentedit.kr/i/cover-"&amp;$H148&amp;".html?e="&amp;$A148)</f>
+      </c>
       <c r="Y148" s="1">
-        <f>IF($A148="","","https://momentedit.kr/i/cover-"&amp;$H148&amp;".html?e="&amp;$A148)</f>
-      </c>
-      <c r="Z148" s="1">
-        <f>IF(AND($A148&lt;&gt;"",$I148="Y"),"https://momentedit.kr/i-family/family-"&amp;$H148&amp;".html?e="&amp;$A148,"")</f>
+        <f>IF($A148="","","https://momentedit.kr/i-family/family-"&amp;$H148&amp;".html?e="&amp;$A148)</f>
       </c>
     </row>
     <row r="149">
+      <c r="X149" s="1">
+        <f>IF($A149="","","https://momentedit.kr/i/cover-"&amp;$H149&amp;".html?e="&amp;$A149)</f>
+      </c>
       <c r="Y149" s="1">
-        <f>IF($A149="","","https://momentedit.kr/i/cover-"&amp;$H149&amp;".html?e="&amp;$A149)</f>
-      </c>
-      <c r="Z149" s="1">
-        <f>IF(AND($A149&lt;&gt;"",$I149="Y"),"https://momentedit.kr/i-family/family-"&amp;$H149&amp;".html?e="&amp;$A149,"")</f>
+        <f>IF($A149="","","https://momentedit.kr/i-family/family-"&amp;$H149&amp;".html?e="&amp;$A149)</f>
       </c>
     </row>
     <row r="150">
+      <c r="X150" s="1">
+        <f>IF($A150="","","https://momentedit.kr/i/cover-"&amp;$H150&amp;".html?e="&amp;$A150)</f>
+      </c>
       <c r="Y150" s="1">
-        <f>IF($A150="","","https://momentedit.kr/i/cover-"&amp;$H150&amp;".html?e="&amp;$A150)</f>
-      </c>
-      <c r="Z150" s="1">
-        <f>IF(AND($A150&lt;&gt;"",$I150="Y"),"https://momentedit.kr/i-family/family-"&amp;$H150&amp;".html?e="&amp;$A150,"")</f>
+        <f>IF($A150="","","https://momentedit.kr/i-family/family-"&amp;$H150&amp;".html?e="&amp;$A150)</f>
       </c>
     </row>
     <row r="151">
+      <c r="X151" s="1">
+        <f>IF($A151="","","https://momentedit.kr/i/cover-"&amp;$H151&amp;".html?e="&amp;$A151)</f>
+      </c>
       <c r="Y151" s="1">
-        <f>IF($A151="","","https://momentedit.kr/i/cover-"&amp;$H151&amp;".html?e="&amp;$A151)</f>
-      </c>
-      <c r="Z151" s="1">
-        <f>IF(AND($A151&lt;&gt;"",$I151="Y"),"https://momentedit.kr/i-family/family-"&amp;$H151&amp;".html?e="&amp;$A151,"")</f>
+        <f>IF($A151="","","https://momentedit.kr/i-family/family-"&amp;$H151&amp;".html?e="&amp;$A151)</f>
       </c>
     </row>
     <row r="152">
+      <c r="X152" s="1">
+        <f>IF($A152="","","https://momentedit.kr/i/cover-"&amp;$H152&amp;".html?e="&amp;$A152)</f>
+      </c>
       <c r="Y152" s="1">
-        <f>IF($A152="","","https://momentedit.kr/i/cover-"&amp;$H152&amp;".html?e="&amp;$A152)</f>
-      </c>
-      <c r="Z152" s="1">
-        <f>IF(AND($A152&lt;&gt;"",$I152="Y"),"https://momentedit.kr/i-family/family-"&amp;$H152&amp;".html?e="&amp;$A152,"")</f>
+        <f>IF($A152="","","https://momentedit.kr/i-family/family-"&amp;$H152&amp;".html?e="&amp;$A152)</f>
       </c>
     </row>
     <row r="153">
+      <c r="X153" s="1">
+        <f>IF($A153="","","https://momentedit.kr/i/cover-"&amp;$H153&amp;".html?e="&amp;$A153)</f>
+      </c>
       <c r="Y153" s="1">
-        <f>IF($A153="","","https://momentedit.kr/i/cover-"&amp;$H153&amp;".html?e="&amp;$A153)</f>
-      </c>
-      <c r="Z153" s="1">
-        <f>IF(AND($A153&lt;&gt;"",$I153="Y"),"https://momentedit.kr/i-family/family-"&amp;$H153&amp;".html?e="&amp;$A153,"")</f>
+        <f>IF($A153="","","https://momentedit.kr/i-family/family-"&amp;$H153&amp;".html?e="&amp;$A153)</f>
       </c>
     </row>
     <row r="154">
+      <c r="X154" s="1">
+        <f>IF($A154="","","https://momentedit.kr/i/cover-"&amp;$H154&amp;".html?e="&amp;$A154)</f>
+      </c>
       <c r="Y154" s="1">
-        <f>IF($A154="","","https://momentedit.kr/i/cover-"&amp;$H154&amp;".html?e="&amp;$A154)</f>
-      </c>
-      <c r="Z154" s="1">
-        <f>IF(AND($A154&lt;&gt;"",$I154="Y"),"https://momentedit.kr/i-family/family-"&amp;$H154&amp;".html?e="&amp;$A154,"")</f>
+        <f>IF($A154="","","https://momentedit.kr/i-family/family-"&amp;$H154&amp;".html?e="&amp;$A154)</f>
       </c>
     </row>
     <row r="155">
+      <c r="X155" s="1">
+        <f>IF($A155="","","https://momentedit.kr/i/cover-"&amp;$H155&amp;".html?e="&amp;$A155)</f>
+      </c>
       <c r="Y155" s="1">
-        <f>IF($A155="","","https://momentedit.kr/i/cover-"&amp;$H155&amp;".html?e="&amp;$A155)</f>
-      </c>
-      <c r="Z155" s="1">
-        <f>IF(AND($A155&lt;&gt;"",$I155="Y"),"https://momentedit.kr/i-family/family-"&amp;$H155&amp;".html?e="&amp;$A155,"")</f>
+        <f>IF($A155="","","https://momentedit.kr/i-family/family-"&amp;$H155&amp;".html?e="&amp;$A155)</f>
       </c>
     </row>
     <row r="156">
+      <c r="X156" s="1">
+        <f>IF($A156="","","https://momentedit.kr/i/cover-"&amp;$H156&amp;".html?e="&amp;$A156)</f>
+      </c>
       <c r="Y156" s="1">
-        <f>IF($A156="","","https://momentedit.kr/i/cover-"&amp;$H156&amp;".html?e="&amp;$A156)</f>
-      </c>
-      <c r="Z156" s="1">
-        <f>IF(AND($A156&lt;&gt;"",$I156="Y"),"https://momentedit.kr/i-family/family-"&amp;$H156&amp;".html?e="&amp;$A156,"")</f>
+        <f>IF($A156="","","https://momentedit.kr/i-family/family-"&amp;$H156&amp;".html?e="&amp;$A156)</f>
       </c>
     </row>
     <row r="157">
+      <c r="X157" s="1">
+        <f>IF($A157="","","https://momentedit.kr/i/cover-"&amp;$H157&amp;".html?e="&amp;$A157)</f>
+      </c>
       <c r="Y157" s="1">
-        <f>IF($A157="","","https://momentedit.kr/i/cover-"&amp;$H157&amp;".html?e="&amp;$A157)</f>
-      </c>
-      <c r="Z157" s="1">
-        <f>IF(AND($A157&lt;&gt;"",$I157="Y"),"https://momentedit.kr/i-family/family-"&amp;$H157&amp;".html?e="&amp;$A157,"")</f>
+        <f>IF($A157="","","https://momentedit.kr/i-family/family-"&amp;$H157&amp;".html?e="&amp;$A157)</f>
       </c>
     </row>
     <row r="158">
+      <c r="X158" s="1">
+        <f>IF($A158="","","https://momentedit.kr/i/cover-"&amp;$H158&amp;".html?e="&amp;$A158)</f>
+      </c>
       <c r="Y158" s="1">
-        <f>IF($A158="","","https://momentedit.kr/i/cover-"&amp;$H158&amp;".html?e="&amp;$A158)</f>
-      </c>
-      <c r="Z158" s="1">
-        <f>IF(AND($A158&lt;&gt;"",$I158="Y"),"https://momentedit.kr/i-family/family-"&amp;$H158&amp;".html?e="&amp;$A158,"")</f>
+        <f>IF($A158="","","https://momentedit.kr/i-family/family-"&amp;$H158&amp;".html?e="&amp;$A158)</f>
       </c>
     </row>
     <row r="159">
+      <c r="X159" s="1">
+        <f>IF($A159="","","https://momentedit.kr/i/cover-"&amp;$H159&amp;".html?e="&amp;$A159)</f>
+      </c>
       <c r="Y159" s="1">
-        <f>IF($A159="","","https://momentedit.kr/i/cover-"&amp;$H159&amp;".html?e="&amp;$A159)</f>
-      </c>
-      <c r="Z159" s="1">
-        <f>IF(AND($A159&lt;&gt;"",$I159="Y"),"https://momentedit.kr/i-family/family-"&amp;$H159&amp;".html?e="&amp;$A159,"")</f>
+        <f>IF($A159="","","https://momentedit.kr/i-family/family-"&amp;$H159&amp;".html?e="&amp;$A159)</f>
       </c>
     </row>
     <row r="160">
+      <c r="X160" s="1">
+        <f>IF($A160="","","https://momentedit.kr/i/cover-"&amp;$H160&amp;".html?e="&amp;$A160)</f>
+      </c>
       <c r="Y160" s="1">
-        <f>IF($A160="","","https://momentedit.kr/i/cover-"&amp;$H160&amp;".html?e="&amp;$A160)</f>
-      </c>
-      <c r="Z160" s="1">
-        <f>IF(AND($A160&lt;&gt;"",$I160="Y"),"https://momentedit.kr/i-family/family-"&amp;$H160&amp;".html?e="&amp;$A160,"")</f>
+        <f>IF($A160="","","https://momentedit.kr/i-family/family-"&amp;$H160&amp;".html?e="&amp;$A160)</f>
       </c>
     </row>
     <row r="161">
+      <c r="X161" s="1">
+        <f>IF($A161="","","https://momentedit.kr/i/cover-"&amp;$H161&amp;".html?e="&amp;$A161)</f>
+      </c>
       <c r="Y161" s="1">
-        <f>IF($A161="","","https://momentedit.kr/i/cover-"&amp;$H161&amp;".html?e="&amp;$A161)</f>
-      </c>
-      <c r="Z161" s="1">
-        <f>IF(AND($A161&lt;&gt;"",$I161="Y"),"https://momentedit.kr/i-family/family-"&amp;$H161&amp;".html?e="&amp;$A161,"")</f>
+        <f>IF($A161="","","https://momentedit.kr/i-family/family-"&amp;$H161&amp;".html?e="&amp;$A161)</f>
       </c>
     </row>
     <row r="162">
+      <c r="X162" s="1">
+        <f>IF($A162="","","https://momentedit.kr/i/cover-"&amp;$H162&amp;".html?e="&amp;$A162)</f>
+      </c>
       <c r="Y162" s="1">
-        <f>IF($A162="","","https://momentedit.kr/i/cover-"&amp;$H162&amp;".html?e="&amp;$A162)</f>
-      </c>
-      <c r="Z162" s="1">
-        <f>IF(AND($A162&lt;&gt;"",$I162="Y"),"https://momentedit.kr/i-family/family-"&amp;$H162&amp;".html?e="&amp;$A162,"")</f>
+        <f>IF($A162="","","https://momentedit.kr/i-family/family-"&amp;$H162&amp;".html?e="&amp;$A162)</f>
       </c>
     </row>
     <row r="163">
+      <c r="X163" s="1">
+        <f>IF($A163="","","https://momentedit.kr/i/cover-"&amp;$H163&amp;".html?e="&amp;$A163)</f>
+      </c>
       <c r="Y163" s="1">
-        <f>IF($A163="","","https://momentedit.kr/i/cover-"&amp;$H163&amp;".html?e="&amp;$A163)</f>
-      </c>
-      <c r="Z163" s="1">
-        <f>IF(AND($A163&lt;&gt;"",$I163="Y"),"https://momentedit.kr/i-family/family-"&amp;$H163&amp;".html?e="&amp;$A163,"")</f>
+        <f>IF($A163="","","https://momentedit.kr/i-family/family-"&amp;$H163&amp;".html?e="&amp;$A163)</f>
       </c>
     </row>
     <row r="164">
+      <c r="X164" s="1">
+        <f>IF($A164="","","https://momentedit.kr/i/cover-"&amp;$H164&amp;".html?e="&amp;$A164)</f>
+      </c>
       <c r="Y164" s="1">
-        <f>IF($A164="","","https://momentedit.kr/i/cover-"&amp;$H164&amp;".html?e="&amp;$A164)</f>
-      </c>
-      <c r="Z164" s="1">
-        <f>IF(AND($A164&lt;&gt;"",$I164="Y"),"https://momentedit.kr/i-family/family-"&amp;$H164&amp;".html?e="&amp;$A164,"")</f>
+        <f>IF($A164="","","https://momentedit.kr/i-family/family-"&amp;$H164&amp;".html?e="&amp;$A164)</f>
       </c>
     </row>
     <row r="165">
+      <c r="X165" s="1">
+        <f>IF($A165="","","https://momentedit.kr/i/cover-"&amp;$H165&amp;".html?e="&amp;$A165)</f>
+      </c>
       <c r="Y165" s="1">
-        <f>IF($A165="","","https://momentedit.kr/i/cover-"&amp;$H165&amp;".html?e="&amp;$A165)</f>
-      </c>
-      <c r="Z165" s="1">
-        <f>IF(AND($A165&lt;&gt;"",$I165="Y"),"https://momentedit.kr/i-family/family-"&amp;$H165&amp;".html?e="&amp;$A165,"")</f>
+        <f>IF($A165="","","https://momentedit.kr/i-family/family-"&amp;$H165&amp;".html?e="&amp;$A165)</f>
       </c>
     </row>
     <row r="166">
+      <c r="X166" s="1">
+        <f>IF($A166="","","https://momentedit.kr/i/cover-"&amp;$H166&amp;".html?e="&amp;$A166)</f>
+      </c>
       <c r="Y166" s="1">
-        <f>IF($A166="","","https://momentedit.kr/i/cover-"&amp;$H166&amp;".html?e="&amp;$A166)</f>
-      </c>
-      <c r="Z166" s="1">
-        <f>IF(AND($A166&lt;&gt;"",$I166="Y"),"https://momentedit.kr/i-family/family-"&amp;$H166&amp;".html?e="&amp;$A166,"")</f>
+        <f>IF($A166="","","https://momentedit.kr/i-family/family-"&amp;$H166&amp;".html?e="&amp;$A166)</f>
       </c>
     </row>
     <row r="167">
+      <c r="X167" s="1">
+        <f>IF($A167="","","https://momentedit.kr/i/cover-"&amp;$H167&amp;".html?e="&amp;$A167)</f>
+      </c>
       <c r="Y167" s="1">
-        <f>IF($A167="","","https://momentedit.kr/i/cover-"&amp;$H167&amp;".html?e="&amp;$A167)</f>
-      </c>
-      <c r="Z167" s="1">
-        <f>IF(AND($A167&lt;&gt;"",$I167="Y"),"https://momentedit.kr/i-family/family-"&amp;$H167&amp;".html?e="&amp;$A167,"")</f>
+        <f>IF($A167="","","https://momentedit.kr/i-family/family-"&amp;$H167&amp;".html?e="&amp;$A167)</f>
       </c>
     </row>
     <row r="168">
+      <c r="X168" s="1">
+        <f>IF($A168="","","https://momentedit.kr/i/cover-"&amp;$H168&amp;".html?e="&amp;$A168)</f>
+      </c>
       <c r="Y168" s="1">
-        <f>IF($A168="","","https://momentedit.kr/i/cover-"&amp;$H168&amp;".html?e="&amp;$A168)</f>
-      </c>
-      <c r="Z168" s="1">
-        <f>IF(AND($A168&lt;&gt;"",$I168="Y"),"https://momentedit.kr/i-family/family-"&amp;$H168&amp;".html?e="&amp;$A168,"")</f>
+        <f>IF($A168="","","https://momentedit.kr/i-family/family-"&amp;$H168&amp;".html?e="&amp;$A168)</f>
       </c>
     </row>
     <row r="169">
+      <c r="X169" s="1">
+        <f>IF($A169="","","https://momentedit.kr/i/cover-"&amp;$H169&amp;".html?e="&amp;$A169)</f>
+      </c>
       <c r="Y169" s="1">
-        <f>IF($A169="","","https://momentedit.kr/i/cover-"&amp;$H169&amp;".html?e="&amp;$A169)</f>
-      </c>
-      <c r="Z169" s="1">
-        <f>IF(AND($A169&lt;&gt;"",$I169="Y"),"https://momentedit.kr/i-family/family-"&amp;$H169&amp;".html?e="&amp;$A169,"")</f>
+        <f>IF($A169="","","https://momentedit.kr/i-family/family-"&amp;$H169&amp;".html?e="&amp;$A169)</f>
       </c>
     </row>
     <row r="170">
+      <c r="X170" s="1">
+        <f>IF($A170="","","https://momentedit.kr/i/cover-"&amp;$H170&amp;".html?e="&amp;$A170)</f>
+      </c>
       <c r="Y170" s="1">
-        <f>IF($A170="","","https://momentedit.kr/i/cover-"&amp;$H170&amp;".html?e="&amp;$A170)</f>
-      </c>
-      <c r="Z170" s="1">
-        <f>IF(AND($A170&lt;&gt;"",$I170="Y"),"https://momentedit.kr/i-family/family-"&amp;$H170&amp;".html?e="&amp;$A170,"")</f>
+        <f>IF($A170="","","https://momentedit.kr/i-family/family-"&amp;$H170&amp;".html?e="&amp;$A170)</f>
       </c>
     </row>
     <row r="171">
+      <c r="X171" s="1">
+        <f>IF($A171="","","https://momentedit.kr/i/cover-"&amp;$H171&amp;".html?e="&amp;$A171)</f>
+      </c>
       <c r="Y171" s="1">
-        <f>IF($A171="","","https://momentedit.kr/i/cover-"&amp;$H171&amp;".html?e="&amp;$A171)</f>
-      </c>
-      <c r="Z171" s="1">
-        <f>IF(AND($A171&lt;&gt;"",$I171="Y"),"https://momentedit.kr/i-family/family-"&amp;$H171&amp;".html?e="&amp;$A171,"")</f>
+        <f>IF($A171="","","https://momentedit.kr/i-family/family-"&amp;$H171&amp;".html?e="&amp;$A171)</f>
       </c>
     </row>
     <row r="172">
+      <c r="X172" s="1">
+        <f>IF($A172="","","https://momentedit.kr/i/cover-"&amp;$H172&amp;".html?e="&amp;$A172)</f>
+      </c>
       <c r="Y172" s="1">
-        <f>IF($A172="","","https://momentedit.kr/i/cover-"&amp;$H172&amp;".html?e="&amp;$A172)</f>
-      </c>
-      <c r="Z172" s="1">
-        <f>IF(AND($A172&lt;&gt;"",$I172="Y"),"https://momentedit.kr/i-family/family-"&amp;$H172&amp;".html?e="&amp;$A172,"")</f>
+        <f>IF($A172="","","https://momentedit.kr/i-family/family-"&amp;$H172&amp;".html?e="&amp;$A172)</f>
       </c>
     </row>
     <row r="173">
+      <c r="X173" s="1">
+        <f>IF($A173="","","https://momentedit.kr/i/cover-"&amp;$H173&amp;".html?e="&amp;$A173)</f>
+      </c>
       <c r="Y173" s="1">
-        <f>IF($A173="","","https://momentedit.kr/i/cover-"&amp;$H173&amp;".html?e="&amp;$A173)</f>
-      </c>
-      <c r="Z173" s="1">
-        <f>IF(AND($A173&lt;&gt;"",$I173="Y"),"https://momentedit.kr/i-family/family-"&amp;$H173&amp;".html?e="&amp;$A173,"")</f>
+        <f>IF($A173="","","https://momentedit.kr/i-family/family-"&amp;$H173&amp;".html?e="&amp;$A173)</f>
       </c>
     </row>
     <row r="174">
+      <c r="X174" s="1">
+        <f>IF($A174="","","https://momentedit.kr/i/cover-"&amp;$H174&amp;".html?e="&amp;$A174)</f>
+      </c>
       <c r="Y174" s="1">
-        <f>IF($A174="","","https://momentedit.kr/i/cover-"&amp;$H174&amp;".html?e="&amp;$A174)</f>
-      </c>
-      <c r="Z174" s="1">
-        <f>IF(AND($A174&lt;&gt;"",$I174="Y"),"https://momentedit.kr/i-family/family-"&amp;$H174&amp;".html?e="&amp;$A174,"")</f>
+        <f>IF($A174="","","https://momentedit.kr/i-family/family-"&amp;$H174&amp;".html?e="&amp;$A174)</f>
       </c>
     </row>
     <row r="175">
+      <c r="X175" s="1">
+        <f>IF($A175="","","https://momentedit.kr/i/cover-"&amp;$H175&amp;".html?e="&amp;$A175)</f>
+      </c>
       <c r="Y175" s="1">
-        <f>IF($A175="","","https://momentedit.kr/i/cover-"&amp;$H175&amp;".html?e="&amp;$A175)</f>
-      </c>
-      <c r="Z175" s="1">
-        <f>IF(AND($A175&lt;&gt;"",$I175="Y"),"https://momentedit.kr/i-family/family-"&amp;$H175&amp;".html?e="&amp;$A175,"")</f>
+        <f>IF($A175="","","https://momentedit.kr/i-family/family-"&amp;$H175&amp;".html?e="&amp;$A175)</f>
       </c>
     </row>
     <row r="176">
+      <c r="X176" s="1">
+        <f>IF($A176="","","https://momentedit.kr/i/cover-"&amp;$H176&amp;".html?e="&amp;$A176)</f>
+      </c>
       <c r="Y176" s="1">
-        <f>IF($A176="","","https://momentedit.kr/i/cover-"&amp;$H176&amp;".html?e="&amp;$A176)</f>
-      </c>
-      <c r="Z176" s="1">
-        <f>IF(AND($A176&lt;&gt;"",$I176="Y"),"https://momentedit.kr/i-family/family-"&amp;$H176&amp;".html?e="&amp;$A176,"")</f>
+        <f>IF($A176="","","https://momentedit.kr/i-family/family-"&amp;$H176&amp;".html?e="&amp;$A176)</f>
       </c>
     </row>
     <row r="177">
+      <c r="X177" s="1">
+        <f>IF($A177="","","https://momentedit.kr/i/cover-"&amp;$H177&amp;".html?e="&amp;$A177)</f>
+      </c>
       <c r="Y177" s="1">
-        <f>IF($A177="","","https://momentedit.kr/i/cover-"&amp;$H177&amp;".html?e="&amp;$A177)</f>
-      </c>
-      <c r="Z177" s="1">
-        <f>IF(AND($A177&lt;&gt;"",$I177="Y"),"https://momentedit.kr/i-family/family-"&amp;$H177&amp;".html?e="&amp;$A177,"")</f>
+        <f>IF($A177="","","https://momentedit.kr/i-family/family-"&amp;$H177&amp;".html?e="&amp;$A177)</f>
       </c>
     </row>
     <row r="178">
+      <c r="X178" s="1">
+        <f>IF($A178="","","https://momentedit.kr/i/cover-"&amp;$H178&amp;".html?e="&amp;$A178)</f>
+      </c>
       <c r="Y178" s="1">
-        <f>IF($A178="","","https://momentedit.kr/i/cover-"&amp;$H178&amp;".html?e="&amp;$A178)</f>
-      </c>
-      <c r="Z178" s="1">
-        <f>IF(AND($A178&lt;&gt;"",$I178="Y"),"https://momentedit.kr/i-family/family-"&amp;$H178&amp;".html?e="&amp;$A178,"")</f>
+        <f>IF($A178="","","https://momentedit.kr/i-family/family-"&amp;$H178&amp;".html?e="&amp;$A178)</f>
       </c>
     </row>
     <row r="179">
+      <c r="X179" s="1">
+        <f>IF($A179="","","https://momentedit.kr/i/cover-"&amp;$H179&amp;".html?e="&amp;$A179)</f>
+      </c>
       <c r="Y179" s="1">
-        <f>IF($A179="","","https://momentedit.kr/i/cover-"&amp;$H179&amp;".html?e="&amp;$A179)</f>
-      </c>
-      <c r="Z179" s="1">
-        <f>IF(AND($A179&lt;&gt;"",$I179="Y"),"https://momentedit.kr/i-family/family-"&amp;$H179&amp;".html?e="&amp;$A179,"")</f>
+        <f>IF($A179="","","https://momentedit.kr/i-family/family-"&amp;$H179&amp;".html?e="&amp;$A179)</f>
       </c>
     </row>
     <row r="180">
+      <c r="X180" s="1">
+        <f>IF($A180="","","https://momentedit.kr/i/cover-"&amp;$H180&amp;".html?e="&amp;$A180)</f>
+      </c>
       <c r="Y180" s="1">
-        <f>IF($A180="","","https://momentedit.kr/i/cover-"&amp;$H180&amp;".html?e="&amp;$A180)</f>
-      </c>
-      <c r="Z180" s="1">
-        <f>IF(AND($A180&lt;&gt;"",$I180="Y"),"https://momentedit.kr/i-family/family-"&amp;$H180&amp;".html?e="&amp;$A180,"")</f>
+        <f>IF($A180="","","https://momentedit.kr/i-family/family-"&amp;$H180&amp;".html?e="&amp;$A180)</f>
       </c>
     </row>
     <row r="181">
+      <c r="X181" s="1">
+        <f>IF($A181="","","https://momentedit.kr/i/cover-"&amp;$H181&amp;".html?e="&amp;$A181)</f>
+      </c>
       <c r="Y181" s="1">
-        <f>IF($A181="","","https://momentedit.kr/i/cover-"&amp;$H181&amp;".html?e="&amp;$A181)</f>
-      </c>
-      <c r="Z181" s="1">
-        <f>IF(AND($A181&lt;&gt;"",$I181="Y"),"https://momentedit.kr/i-family/family-"&amp;$H181&amp;".html?e="&amp;$A181,"")</f>
+        <f>IF($A181="","","https://momentedit.kr/i-family/family-"&amp;$H181&amp;".html?e="&amp;$A181)</f>
       </c>
     </row>
     <row r="182">
+      <c r="X182" s="1">
+        <f>IF($A182="","","https://momentedit.kr/i/cover-"&amp;$H182&amp;".html?e="&amp;$A182)</f>
+      </c>
       <c r="Y182" s="1">
-        <f>IF($A182="","","https://momentedit.kr/i/cover-"&amp;$H182&amp;".html?e="&amp;$A182)</f>
-      </c>
-      <c r="Z182" s="1">
-        <f>IF(AND($A182&lt;&gt;"",$I182="Y"),"https://momentedit.kr/i-family/family-"&amp;$H182&amp;".html?e="&amp;$A182,"")</f>
+        <f>IF($A182="","","https://momentedit.kr/i-family/family-"&amp;$H182&amp;".html?e="&amp;$A182)</f>
       </c>
     </row>
     <row r="183">
+      <c r="X183" s="1">
+        <f>IF($A183="","","https://momentedit.kr/i/cover-"&amp;$H183&amp;".html?e="&amp;$A183)</f>
+      </c>
       <c r="Y183" s="1">
-        <f>IF($A183="","","https://momentedit.kr/i/cover-"&amp;$H183&amp;".html?e="&amp;$A183)</f>
-      </c>
-      <c r="Z183" s="1">
-        <f>IF(AND($A183&lt;&gt;"",$I183="Y"),"https://momentedit.kr/i-family/family-"&amp;$H183&amp;".html?e="&amp;$A183,"")</f>
+        <f>IF($A183="","","https://momentedit.kr/i-family/family-"&amp;$H183&amp;".html?e="&amp;$A183)</f>
       </c>
     </row>
     <row r="184">
+      <c r="X184" s="1">
+        <f>IF($A184="","","https://momentedit.kr/i/cover-"&amp;$H184&amp;".html?e="&amp;$A184)</f>
+      </c>
       <c r="Y184" s="1">
-        <f>IF($A184="","","https://momentedit.kr/i/cover-"&amp;$H184&amp;".html?e="&amp;$A184)</f>
-      </c>
-      <c r="Z184" s="1">
-        <f>IF(AND($A184&lt;&gt;"",$I184="Y"),"https://momentedit.kr/i-family/family-"&amp;$H184&amp;".html?e="&amp;$A184,"")</f>
+        <f>IF($A184="","","https://momentedit.kr/i-family/family-"&amp;$H184&amp;".html?e="&amp;$A184)</f>
       </c>
     </row>
     <row r="185">
+      <c r="X185" s="1">
+        <f>IF($A185="","","https://momentedit.kr/i/cover-"&amp;$H185&amp;".html?e="&amp;$A185)</f>
+      </c>
       <c r="Y185" s="1">
-        <f>IF($A185="","","https://momentedit.kr/i/cover-"&amp;$H185&amp;".html?e="&amp;$A185)</f>
-      </c>
-      <c r="Z185" s="1">
-        <f>IF(AND($A185&lt;&gt;"",$I185="Y"),"https://momentedit.kr/i-family/family-"&amp;$H185&amp;".html?e="&amp;$A185,"")</f>
+        <f>IF($A185="","","https://momentedit.kr/i-family/family-"&amp;$H185&amp;".html?e="&amp;$A185)</f>
       </c>
     </row>
     <row r="186">
+      <c r="X186" s="1">
+        <f>IF($A186="","","https://momentedit.kr/i/cover-"&amp;$H186&amp;".html?e="&amp;$A186)</f>
+      </c>
       <c r="Y186" s="1">
-        <f>IF($A186="","","https://momentedit.kr/i/cover-"&amp;$H186&amp;".html?e="&amp;$A186)</f>
-      </c>
-      <c r="Z186" s="1">
-        <f>IF(AND($A186&lt;&gt;"",$I186="Y"),"https://momentedit.kr/i-family/family-"&amp;$H186&amp;".html?e="&amp;$A186,"")</f>
+        <f>IF($A186="","","https://momentedit.kr/i-family/family-"&amp;$H186&amp;".html?e="&amp;$A186)</f>
       </c>
     </row>
     <row r="187">
+      <c r="X187" s="1">
+        <f>IF($A187="","","https://momentedit.kr/i/cover-"&amp;$H187&amp;".html?e="&amp;$A187)</f>
+      </c>
       <c r="Y187" s="1">
-        <f>IF($A187="","","https://momentedit.kr/i/cover-"&amp;$H187&amp;".html?e="&amp;$A187)</f>
-      </c>
-      <c r="Z187" s="1">
-        <f>IF(AND($A187&lt;&gt;"",$I187="Y"),"https://momentedit.kr/i-family/family-"&amp;$H187&amp;".html?e="&amp;$A187,"")</f>
+        <f>IF($A187="","","https://momentedit.kr/i-family/family-"&amp;$H187&amp;".html?e="&amp;$A187)</f>
       </c>
     </row>
     <row r="188">
+      <c r="X188" s="1">
+        <f>IF($A188="","","https://momentedit.kr/i/cover-"&amp;$H188&amp;".html?e="&amp;$A188)</f>
+      </c>
       <c r="Y188" s="1">
-        <f>IF($A188="","","https://momentedit.kr/i/cover-"&amp;$H188&amp;".html?e="&amp;$A188)</f>
-      </c>
-      <c r="Z188" s="1">
-        <f>IF(AND($A188&lt;&gt;"",$I188="Y"),"https://momentedit.kr/i-family/family-"&amp;$H188&amp;".html?e="&amp;$A188,"")</f>
+        <f>IF($A188="","","https://momentedit.kr/i-family/family-"&amp;$H188&amp;".html?e="&amp;$A188)</f>
       </c>
     </row>
     <row r="189">
+      <c r="X189" s="1">
+        <f>IF($A189="","","https://momentedit.kr/i/cover-"&amp;$H189&amp;".html?e="&amp;$A189)</f>
+      </c>
       <c r="Y189" s="1">
-        <f>IF($A189="","","https://momentedit.kr/i/cover-"&amp;$H189&amp;".html?e="&amp;$A189)</f>
-      </c>
-      <c r="Z189" s="1">
-        <f>IF(AND($A189&lt;&gt;"",$I189="Y"),"https://momentedit.kr/i-family/family-"&amp;$H189&amp;".html?e="&amp;$A189,"")</f>
+        <f>IF($A189="","","https://momentedit.kr/i-family/family-"&amp;$H189&amp;".html?e="&amp;$A189)</f>
       </c>
     </row>
     <row r="190">
+      <c r="X190" s="1">
+        <f>IF($A190="","","https://momentedit.kr/i/cover-"&amp;$H190&amp;".html?e="&amp;$A190)</f>
+      </c>
       <c r="Y190" s="1">
-        <f>IF($A190="","","https://momentedit.kr/i/cover-"&amp;$H190&amp;".html?e="&amp;$A190)</f>
-      </c>
-      <c r="Z190" s="1">
-        <f>IF(AND($A190&lt;&gt;"",$I190="Y"),"https://momentedit.kr/i-family/family-"&amp;$H190&amp;".html?e="&amp;$A190,"")</f>
+        <f>IF($A190="","","https://momentedit.kr/i-family/family-"&amp;$H190&amp;".html?e="&amp;$A190)</f>
       </c>
     </row>
     <row r="191">
+      <c r="X191" s="1">
+        <f>IF($A191="","","https://momentedit.kr/i/cover-"&amp;$H191&amp;".html?e="&amp;$A191)</f>
+      </c>
       <c r="Y191" s="1">
-        <f>IF($A191="","","https://momentedit.kr/i/cover-"&amp;$H191&amp;".html?e="&amp;$A191)</f>
-      </c>
-      <c r="Z191" s="1">
-        <f>IF(AND($A191&lt;&gt;"",$I191="Y"),"https://momentedit.kr/i-family/family-"&amp;$H191&amp;".html?e="&amp;$A191,"")</f>
+        <f>IF($A191="","","https://momentedit.kr/i-family/family-"&amp;$H191&amp;".html?e="&amp;$A191)</f>
       </c>
     </row>
     <row r="192">
+      <c r="X192" s="1">
+        <f>IF($A192="","","https://momentedit.kr/i/cover-"&amp;$H192&amp;".html?e="&amp;$A192)</f>
+      </c>
       <c r="Y192" s="1">
-        <f>IF($A192="","","https://momentedit.kr/i/cover-"&amp;$H192&amp;".html?e="&amp;$A192)</f>
-      </c>
-      <c r="Z192" s="1">
-        <f>IF(AND($A192&lt;&gt;"",$I192="Y"),"https://momentedit.kr/i-family/family-"&amp;$H192&amp;".html?e="&amp;$A192,"")</f>
+        <f>IF($A192="","","https://momentedit.kr/i-family/family-"&amp;$H192&amp;".html?e="&amp;$A192)</f>
       </c>
     </row>
     <row r="193">
+      <c r="X193" s="1">
+        <f>IF($A193="","","https://momentedit.kr/i/cover-"&amp;$H193&amp;".html?e="&amp;$A193)</f>
+      </c>
       <c r="Y193" s="1">
-        <f>IF($A193="","","https://momentedit.kr/i/cover-"&amp;$H193&amp;".html?e="&amp;$A193)</f>
-      </c>
-      <c r="Z193" s="1">
-        <f>IF(AND($A193&lt;&gt;"",$I193="Y"),"https://momentedit.kr/i-family/family-"&amp;$H193&amp;".html?e="&amp;$A193,"")</f>
+        <f>IF($A193="","","https://momentedit.kr/i-family/family-"&amp;$H193&amp;".html?e="&amp;$A193)</f>
       </c>
     </row>
     <row r="194">
+      <c r="X194" s="1">
+        <f>IF($A194="","","https://momentedit.kr/i/cover-"&amp;$H194&amp;".html?e="&amp;$A194)</f>
+      </c>
       <c r="Y194" s="1">
-        <f>IF($A194="","","https://momentedit.kr/i/cover-"&amp;$H194&amp;".html?e="&amp;$A194)</f>
-      </c>
-      <c r="Z194" s="1">
-        <f>IF(AND($A194&lt;&gt;"",$I194="Y"),"https://momentedit.kr/i-family/family-"&amp;$H194&amp;".html?e="&amp;$A194,"")</f>
+        <f>IF($A194="","","https://momentedit.kr/i-family/family-"&amp;$H194&amp;".html?e="&amp;$A194)</f>
       </c>
     </row>
     <row r="195">
+      <c r="X195" s="1">
+        <f>IF($A195="","","https://momentedit.kr/i/cover-"&amp;$H195&amp;".html?e="&amp;$A195)</f>
+      </c>
       <c r="Y195" s="1">
-        <f>IF($A195="","","https://momentedit.kr/i/cover-"&amp;$H195&amp;".html?e="&amp;$A195)</f>
-      </c>
-      <c r="Z195" s="1">
-        <f>IF(AND($A195&lt;&gt;"",$I195="Y"),"https://momentedit.kr/i-family/family-"&amp;$H195&amp;".html?e="&amp;$A195,"")</f>
+        <f>IF($A195="","","https://momentedit.kr/i-family/family-"&amp;$H195&amp;".html?e="&amp;$A195)</f>
       </c>
     </row>
     <row r="196">
+      <c r="X196" s="1">
+        <f>IF($A196="","","https://momentedit.kr/i/cover-"&amp;$H196&amp;".html?e="&amp;$A196)</f>
+      </c>
       <c r="Y196" s="1">
-        <f>IF($A196="","","https://momentedit.kr/i/cover-"&amp;$H196&amp;".html?e="&amp;$A196)</f>
-      </c>
-      <c r="Z196" s="1">
-        <f>IF(AND($A196&lt;&gt;"",$I196="Y"),"https://momentedit.kr/i-family/family-"&amp;$H196&amp;".html?e="&amp;$A196,"")</f>
+        <f>IF($A196="","","https://momentedit.kr/i-family/family-"&amp;$H196&amp;".html?e="&amp;$A196)</f>
       </c>
     </row>
     <row r="197">
+      <c r="X197" s="1">
+        <f>IF($A197="","","https://momentedit.kr/i/cover-"&amp;$H197&amp;".html?e="&amp;$A197)</f>
+      </c>
       <c r="Y197" s="1">
-        <f>IF($A197="","","https://momentedit.kr/i/cover-"&amp;$H197&amp;".html?e="&amp;$A197)</f>
-      </c>
-      <c r="Z197" s="1">
-        <f>IF(AND($A197&lt;&gt;"",$I197="Y"),"https://momentedit.kr/i-family/family-"&amp;$H197&amp;".html?e="&amp;$A197,"")</f>
+        <f>IF($A197="","","https://momentedit.kr/i-family/family-"&amp;$H197&amp;".html?e="&amp;$A197)</f>
       </c>
     </row>
     <row r="198">
+      <c r="X198" s="1">
+        <f>IF($A198="","","https://momentedit.kr/i/cover-"&amp;$H198&amp;".html?e="&amp;$A198)</f>
+      </c>
       <c r="Y198" s="1">
-        <f>IF($A198="","","https://momentedit.kr/i/cover-"&amp;$H198&amp;".html?e="&amp;$A198)</f>
-      </c>
-      <c r="Z198" s="1">
-        <f>IF(AND($A198&lt;&gt;"",$I198="Y"),"https://momentedit.kr/i-family/family-"&amp;$H198&amp;".html?e="&amp;$A198,"")</f>
+        <f>IF($A198="","","https://momentedit.kr/i-family/family-"&amp;$H198&amp;".html?e="&amp;$A198)</f>
       </c>
     </row>
     <row r="199">
+      <c r="X199" s="1">
+        <f>IF($A199="","","https://momentedit.kr/i/cover-"&amp;$H199&amp;".html?e="&amp;$A199)</f>
+      </c>
       <c r="Y199" s="1">
-        <f>IF($A199="","","https://momentedit.kr/i/cover-"&amp;$H199&amp;".html?e="&amp;$A199)</f>
-      </c>
-      <c r="Z199" s="1">
-        <f>IF(AND($A199&lt;&gt;"",$I199="Y"),"https://momentedit.kr/i-family/family-"&amp;$H199&amp;".html?e="&amp;$A199,"")</f>
+        <f>IF($A199="","","https://momentedit.kr/i-family/family-"&amp;$H199&amp;".html?e="&amp;$A199)</f>
       </c>
     </row>
     <row r="200">
+      <c r="X200" s="1">
+        <f>IF($A200="","","https://momentedit.kr/i/cover-"&amp;$H200&amp;".html?e="&amp;$A200)</f>
+      </c>
       <c r="Y200" s="1">
-        <f>IF($A200="","","https://momentedit.kr/i/cover-"&amp;$H200&amp;".html?e="&amp;$A200)</f>
-      </c>
-      <c r="Z200" s="1">
-        <f>IF(AND($A200&lt;&gt;"",$I200="Y"),"https://momentedit.kr/i-family/family-"&amp;$H200&amp;".html?e="&amp;$A200,"")</f>
+        <f>IF($A200="","","https://momentedit.kr/i-family/family-"&amp;$H200&amp;".html?e="&amp;$A200)</f>
       </c>
     </row>
   </sheetData>

--- a/청첩장/Moment Edit · Letter System (개선).xlsx
+++ b/청첩장/Moment Edit · Letter System (개선).xlsx
@@ -1501,6 +1501,9 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1570,60 +1573,75 @@
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">대표문구(02 전용)</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신랑 자기소개(08 전용)</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신부 자기소개(08 전용)</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">인사글 부모표기(Y)</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">계좌 부모표기(Y)</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">신랑 아버지 계좌</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">신랑 어머니 계좌</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">신부 아버지 계좌</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">신부 어머니 계좌</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">신랑 이메일</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">신부 이메일</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">영상ID</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">영상Hash</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">라이브 링크(자동)</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">가족 링크(자동)</t>
         </is>
@@ -1697,60 +1715,75 @@
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">pullQuote</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">groomBio</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brideBio</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">greetingShowParents</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">envelopeShowParents</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">groomFatherAccount</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">groomMotherAccount</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brideFatherAccount</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brideMotherAccount</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">groomEmail</t>
         </is>
       </c>
-      <c r="U3" s="1" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brideEmail</t>
         </is>
       </c>
-      <c r="V3" s="1" t="inlineStr">
+      <c r="Y3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">vimeoId</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="Z3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">vimeoHash</t>
         </is>
       </c>
-      <c r="X3" s="1" t="inlineStr">
+      <c r="AA3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">liveUrl</t>
         </is>
       </c>
-      <c r="Y3" s="1" t="inlineStr">
+      <c r="AB3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">familyUrl</t>
         </is>
@@ -1818,53 +1851,56 @@
         </is>
       </c>
       <c r="M4" s="1"/>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">국민 110-123-456789</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="T4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">신한 220-456-123789</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">농협 351-234-567890</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="V4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">카카오뱅크 3333-12-3456789</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="W4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">gtrddrt7706@gmail.com</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">gtrddrt7706@gmail.com</t>
         </is>
       </c>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1">
-        <f>IF($A4="","","https://momentedit.kr/i/cover-"&amp;$H4&amp;".html?e="&amp;$A4)</f>
-      </c>
-      <c r="Y4" s="1">
-        <f>IF($A4="","","https://momentedit.kr/i-family/family-"&amp;$H4&amp;".html?e="&amp;$A4)</f>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1">
+        <f>IF($A4="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H4,2)&amp;".html?e="&amp;$A4)</f>
+      </c>
+      <c r="AB4" s="1">
+        <f>IF($A4="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H4,2)&amp;".html?e="&amp;$A4)</f>
       </c>
     </row>
     <row r="5">
@@ -1935,1595 +1971,1716 @@
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">한 장면, 한 약속, 하나의 시작.</t>
+        </is>
+      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="R5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="1" t="inlineStr">
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">gtrddrt7706@gmail.com</t>
         </is>
       </c>
-      <c r="U5" s="1" t="inlineStr">
+      <c r="X5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">gtrddrt7706@gmail.com</t>
         </is>
       </c>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1">
-        <f>IF($A5="","","https://momentedit.kr/i/cover-"&amp;$H5&amp;".html?e="&amp;$A5)</f>
-      </c>
-      <c r="Y5" s="1">
-        <f>IF($A5="","","https://momentedit.kr/i-family/family-"&amp;$H5&amp;".html?e="&amp;$A5)</f>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1">
+        <f>IF($A5="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H5,2)&amp;".html?e="&amp;$A5)</f>
+      </c>
+      <c r="AB5" s="1">
+        <f>IF($A5="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H5,2)&amp;".html?e="&amp;$A5)</f>
       </c>
     </row>
     <row r="6">
-      <c r="X6" s="1">
-        <f>IF($A6="","","https://momentedit.kr/i/cover-"&amp;$H6&amp;".html?e="&amp;$A6)</f>
-      </c>
-      <c r="Y6" s="1">
-        <f>IF($A6="","","https://momentedit.kr/i-family/family-"&amp;$H6&amp;".html?e="&amp;$A6)</f>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jws-hjm-1115</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정우성</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한지민</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jung Woosung</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Han Jimin</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-15</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토스뱅크 100-200-300400</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">케이뱅크 500-600-700800</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정해성 · 김미라</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한동훈 · 이수진</t>
+        </is>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍경 사진을 좋아하고, 조용한 카페에서 책 읽는 시간을 좋아합니다.</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오래된 영화와 손편지를 좋아하고, 매일 작은 기록을 남기며 살아갑니다.</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신한 111-222-333444</t>
+        </is>
+      </c>
+      <c r="T6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">국민 222-333-444555</t>
+        </is>
+      </c>
+      <c r="U6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리 333-444-555666</t>
+        </is>
+      </c>
+      <c r="V6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하나 444-555-666777</t>
+        </is>
+      </c>
+      <c r="W6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gtrddrt7706@gmail.com</t>
+        </is>
+      </c>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1">
+        <f>IF($A6="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H6,2)&amp;".html?e="&amp;$A6)</f>
+      </c>
+      <c r="AB6" s="1">
+        <f>IF($A6="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H6,2)&amp;".html?e="&amp;$A6)</f>
       </c>
     </row>
     <row r="7">
-      <c r="X7" s="1">
-        <f>IF($A7="","","https://momentedit.kr/i/cover-"&amp;$H7&amp;".html?e="&amp;$A7)</f>
-      </c>
-      <c r="Y7" s="1">
-        <f>IF($A7="","","https://momentedit.kr/i-family/family-"&amp;$H7&amp;".html?e="&amp;$A7)</f>
+      <c r="AA7" s="1">
+        <f>IF($A7="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H7,2)&amp;".html?e="&amp;$A7)</f>
+      </c>
+      <c r="AB7" s="1">
+        <f>IF($A7="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H7,2)&amp;".html?e="&amp;$A7)</f>
       </c>
     </row>
     <row r="8">
-      <c r="X8" s="1">
-        <f>IF($A8="","","https://momentedit.kr/i/cover-"&amp;$H8&amp;".html?e="&amp;$A8)</f>
-      </c>
-      <c r="Y8" s="1">
-        <f>IF($A8="","","https://momentedit.kr/i-family/family-"&amp;$H8&amp;".html?e="&amp;$A8)</f>
+      <c r="AA8" s="1">
+        <f>IF($A8="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H8,2)&amp;".html?e="&amp;$A8)</f>
+      </c>
+      <c r="AB8" s="1">
+        <f>IF($A8="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H8,2)&amp;".html?e="&amp;$A8)</f>
       </c>
     </row>
     <row r="9">
-      <c r="X9" s="1">
-        <f>IF($A9="","","https://momentedit.kr/i/cover-"&amp;$H9&amp;".html?e="&amp;$A9)</f>
-      </c>
-      <c r="Y9" s="1">
-        <f>IF($A9="","","https://momentedit.kr/i-family/family-"&amp;$H9&amp;".html?e="&amp;$A9)</f>
+      <c r="AA9" s="1">
+        <f>IF($A9="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H9,2)&amp;".html?e="&amp;$A9)</f>
+      </c>
+      <c r="AB9" s="1">
+        <f>IF($A9="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H9,2)&amp;".html?e="&amp;$A9)</f>
       </c>
     </row>
     <row r="10">
-      <c r="X10" s="1">
-        <f>IF($A10="","","https://momentedit.kr/i/cover-"&amp;$H10&amp;".html?e="&amp;$A10)</f>
-      </c>
-      <c r="Y10" s="1">
-        <f>IF($A10="","","https://momentedit.kr/i-family/family-"&amp;$H10&amp;".html?e="&amp;$A10)</f>
+      <c r="AA10" s="1">
+        <f>IF($A10="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H10,2)&amp;".html?e="&amp;$A10)</f>
+      </c>
+      <c r="AB10" s="1">
+        <f>IF($A10="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H10,2)&amp;".html?e="&amp;$A10)</f>
       </c>
     </row>
     <row r="11">
-      <c r="X11" s="1">
-        <f>IF($A11="","","https://momentedit.kr/i/cover-"&amp;$H11&amp;".html?e="&amp;$A11)</f>
-      </c>
-      <c r="Y11" s="1">
-        <f>IF($A11="","","https://momentedit.kr/i-family/family-"&amp;$H11&amp;".html?e="&amp;$A11)</f>
+      <c r="AA11" s="1">
+        <f>IF($A11="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H11,2)&amp;".html?e="&amp;$A11)</f>
+      </c>
+      <c r="AB11" s="1">
+        <f>IF($A11="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H11,2)&amp;".html?e="&amp;$A11)</f>
       </c>
     </row>
     <row r="12">
-      <c r="X12" s="1">
-        <f>IF($A12="","","https://momentedit.kr/i/cover-"&amp;$H12&amp;".html?e="&amp;$A12)</f>
-      </c>
-      <c r="Y12" s="1">
-        <f>IF($A12="","","https://momentedit.kr/i-family/family-"&amp;$H12&amp;".html?e="&amp;$A12)</f>
+      <c r="AA12" s="1">
+        <f>IF($A12="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H12,2)&amp;".html?e="&amp;$A12)</f>
+      </c>
+      <c r="AB12" s="1">
+        <f>IF($A12="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H12,2)&amp;".html?e="&amp;$A12)</f>
       </c>
     </row>
     <row r="13">
-      <c r="X13" s="1">
-        <f>IF($A13="","","https://momentedit.kr/i/cover-"&amp;$H13&amp;".html?e="&amp;$A13)</f>
-      </c>
-      <c r="Y13" s="1">
-        <f>IF($A13="","","https://momentedit.kr/i-family/family-"&amp;$H13&amp;".html?e="&amp;$A13)</f>
+      <c r="AA13" s="1">
+        <f>IF($A13="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H13,2)&amp;".html?e="&amp;$A13)</f>
+      </c>
+      <c r="AB13" s="1">
+        <f>IF($A13="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H13,2)&amp;".html?e="&amp;$A13)</f>
       </c>
     </row>
     <row r="14">
-      <c r="X14" s="1">
-        <f>IF($A14="","","https://momentedit.kr/i/cover-"&amp;$H14&amp;".html?e="&amp;$A14)</f>
-      </c>
-      <c r="Y14" s="1">
-        <f>IF($A14="","","https://momentedit.kr/i-family/family-"&amp;$H14&amp;".html?e="&amp;$A14)</f>
+      <c r="AA14" s="1">
+        <f>IF($A14="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H14,2)&amp;".html?e="&amp;$A14)</f>
+      </c>
+      <c r="AB14" s="1">
+        <f>IF($A14="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H14,2)&amp;".html?e="&amp;$A14)</f>
       </c>
     </row>
     <row r="15">
-      <c r="X15" s="1">
-        <f>IF($A15="","","https://momentedit.kr/i/cover-"&amp;$H15&amp;".html?e="&amp;$A15)</f>
-      </c>
-      <c r="Y15" s="1">
-        <f>IF($A15="","","https://momentedit.kr/i-family/family-"&amp;$H15&amp;".html?e="&amp;$A15)</f>
+      <c r="AA15" s="1">
+        <f>IF($A15="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H15,2)&amp;".html?e="&amp;$A15)</f>
+      </c>
+      <c r="AB15" s="1">
+        <f>IF($A15="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H15,2)&amp;".html?e="&amp;$A15)</f>
       </c>
     </row>
     <row r="16">
-      <c r="X16" s="1">
-        <f>IF($A16="","","https://momentedit.kr/i/cover-"&amp;$H16&amp;".html?e="&amp;$A16)</f>
-      </c>
-      <c r="Y16" s="1">
-        <f>IF($A16="","","https://momentedit.kr/i-family/family-"&amp;$H16&amp;".html?e="&amp;$A16)</f>
+      <c r="AA16" s="1">
+        <f>IF($A16="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H16,2)&amp;".html?e="&amp;$A16)</f>
+      </c>
+      <c r="AB16" s="1">
+        <f>IF($A16="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H16,2)&amp;".html?e="&amp;$A16)</f>
       </c>
     </row>
     <row r="17">
-      <c r="X17" s="1">
-        <f>IF($A17="","","https://momentedit.kr/i/cover-"&amp;$H17&amp;".html?e="&amp;$A17)</f>
-      </c>
-      <c r="Y17" s="1">
-        <f>IF($A17="","","https://momentedit.kr/i-family/family-"&amp;$H17&amp;".html?e="&amp;$A17)</f>
+      <c r="AA17" s="1">
+        <f>IF($A17="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H17,2)&amp;".html?e="&amp;$A17)</f>
+      </c>
+      <c r="AB17" s="1">
+        <f>IF($A17="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H17,2)&amp;".html?e="&amp;$A17)</f>
       </c>
     </row>
     <row r="18">
-      <c r="X18" s="1">
-        <f>IF($A18="","","https://momentedit.kr/i/cover-"&amp;$H18&amp;".html?e="&amp;$A18)</f>
-      </c>
-      <c r="Y18" s="1">
-        <f>IF($A18="","","https://momentedit.kr/i-family/family-"&amp;$H18&amp;".html?e="&amp;$A18)</f>
+      <c r="AA18" s="1">
+        <f>IF($A18="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H18,2)&amp;".html?e="&amp;$A18)</f>
+      </c>
+      <c r="AB18" s="1">
+        <f>IF($A18="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H18,2)&amp;".html?e="&amp;$A18)</f>
       </c>
     </row>
     <row r="19">
-      <c r="X19" s="1">
-        <f>IF($A19="","","https://momentedit.kr/i/cover-"&amp;$H19&amp;".html?e="&amp;$A19)</f>
-      </c>
-      <c r="Y19" s="1">
-        <f>IF($A19="","","https://momentedit.kr/i-family/family-"&amp;$H19&amp;".html?e="&amp;$A19)</f>
+      <c r="AA19" s="1">
+        <f>IF($A19="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H19,2)&amp;".html?e="&amp;$A19)</f>
+      </c>
+      <c r="AB19" s="1">
+        <f>IF($A19="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H19,2)&amp;".html?e="&amp;$A19)</f>
       </c>
     </row>
     <row r="20">
-      <c r="X20" s="1">
-        <f>IF($A20="","","https://momentedit.kr/i/cover-"&amp;$H20&amp;".html?e="&amp;$A20)</f>
-      </c>
-      <c r="Y20" s="1">
-        <f>IF($A20="","","https://momentedit.kr/i-family/family-"&amp;$H20&amp;".html?e="&amp;$A20)</f>
+      <c r="AA20" s="1">
+        <f>IF($A20="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H20,2)&amp;".html?e="&amp;$A20)</f>
+      </c>
+      <c r="AB20" s="1">
+        <f>IF($A20="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H20,2)&amp;".html?e="&amp;$A20)</f>
       </c>
     </row>
     <row r="21">
-      <c r="X21" s="1">
-        <f>IF($A21="","","https://momentedit.kr/i/cover-"&amp;$H21&amp;".html?e="&amp;$A21)</f>
-      </c>
-      <c r="Y21" s="1">
-        <f>IF($A21="","","https://momentedit.kr/i-family/family-"&amp;$H21&amp;".html?e="&amp;$A21)</f>
+      <c r="AA21" s="1">
+        <f>IF($A21="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H21,2)&amp;".html?e="&amp;$A21)</f>
+      </c>
+      <c r="AB21" s="1">
+        <f>IF($A21="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H21,2)&amp;".html?e="&amp;$A21)</f>
       </c>
     </row>
     <row r="22">
-      <c r="X22" s="1">
-        <f>IF($A22="","","https://momentedit.kr/i/cover-"&amp;$H22&amp;".html?e="&amp;$A22)</f>
-      </c>
-      <c r="Y22" s="1">
-        <f>IF($A22="","","https://momentedit.kr/i-family/family-"&amp;$H22&amp;".html?e="&amp;$A22)</f>
+      <c r="AA22" s="1">
+        <f>IF($A22="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H22,2)&amp;".html?e="&amp;$A22)</f>
+      </c>
+      <c r="AB22" s="1">
+        <f>IF($A22="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H22,2)&amp;".html?e="&amp;$A22)</f>
       </c>
     </row>
     <row r="23">
-      <c r="X23" s="1">
-        <f>IF($A23="","","https://momentedit.kr/i/cover-"&amp;$H23&amp;".html?e="&amp;$A23)</f>
-      </c>
-      <c r="Y23" s="1">
-        <f>IF($A23="","","https://momentedit.kr/i-family/family-"&amp;$H23&amp;".html?e="&amp;$A23)</f>
+      <c r="AA23" s="1">
+        <f>IF($A23="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H23,2)&amp;".html?e="&amp;$A23)</f>
+      </c>
+      <c r="AB23" s="1">
+        <f>IF($A23="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H23,2)&amp;".html?e="&amp;$A23)</f>
       </c>
     </row>
     <row r="24">
-      <c r="X24" s="1">
-        <f>IF($A24="","","https://momentedit.kr/i/cover-"&amp;$H24&amp;".html?e="&amp;$A24)</f>
-      </c>
-      <c r="Y24" s="1">
-        <f>IF($A24="","","https://momentedit.kr/i-family/family-"&amp;$H24&amp;".html?e="&amp;$A24)</f>
+      <c r="AA24" s="1">
+        <f>IF($A24="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H24,2)&amp;".html?e="&amp;$A24)</f>
+      </c>
+      <c r="AB24" s="1">
+        <f>IF($A24="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H24,2)&amp;".html?e="&amp;$A24)</f>
       </c>
     </row>
     <row r="25">
-      <c r="X25" s="1">
-        <f>IF($A25="","","https://momentedit.kr/i/cover-"&amp;$H25&amp;".html?e="&amp;$A25)</f>
-      </c>
-      <c r="Y25" s="1">
-        <f>IF($A25="","","https://momentedit.kr/i-family/family-"&amp;$H25&amp;".html?e="&amp;$A25)</f>
+      <c r="AA25" s="1">
+        <f>IF($A25="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H25,2)&amp;".html?e="&amp;$A25)</f>
+      </c>
+      <c r="AB25" s="1">
+        <f>IF($A25="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H25,2)&amp;".html?e="&amp;$A25)</f>
       </c>
     </row>
     <row r="26">
-      <c r="X26" s="1">
-        <f>IF($A26="","","https://momentedit.kr/i/cover-"&amp;$H26&amp;".html?e="&amp;$A26)</f>
-      </c>
-      <c r="Y26" s="1">
-        <f>IF($A26="","","https://momentedit.kr/i-family/family-"&amp;$H26&amp;".html?e="&amp;$A26)</f>
+      <c r="AA26" s="1">
+        <f>IF($A26="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H26,2)&amp;".html?e="&amp;$A26)</f>
+      </c>
+      <c r="AB26" s="1">
+        <f>IF($A26="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H26,2)&amp;".html?e="&amp;$A26)</f>
       </c>
     </row>
     <row r="27">
-      <c r="X27" s="1">
-        <f>IF($A27="","","https://momentedit.kr/i/cover-"&amp;$H27&amp;".html?e="&amp;$A27)</f>
-      </c>
-      <c r="Y27" s="1">
-        <f>IF($A27="","","https://momentedit.kr/i-family/family-"&amp;$H27&amp;".html?e="&amp;$A27)</f>
+      <c r="AA27" s="1">
+        <f>IF($A27="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H27,2)&amp;".html?e="&amp;$A27)</f>
+      </c>
+      <c r="AB27" s="1">
+        <f>IF($A27="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H27,2)&amp;".html?e="&amp;$A27)</f>
       </c>
     </row>
     <row r="28">
-      <c r="X28" s="1">
-        <f>IF($A28="","","https://momentedit.kr/i/cover-"&amp;$H28&amp;".html?e="&amp;$A28)</f>
-      </c>
-      <c r="Y28" s="1">
-        <f>IF($A28="","","https://momentedit.kr/i-family/family-"&amp;$H28&amp;".html?e="&amp;$A28)</f>
+      <c r="AA28" s="1">
+        <f>IF($A28="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H28,2)&amp;".html?e="&amp;$A28)</f>
+      </c>
+      <c r="AB28" s="1">
+        <f>IF($A28="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H28,2)&amp;".html?e="&amp;$A28)</f>
       </c>
     </row>
     <row r="29">
-      <c r="X29" s="1">
-        <f>IF($A29="","","https://momentedit.kr/i/cover-"&amp;$H29&amp;".html?e="&amp;$A29)</f>
-      </c>
-      <c r="Y29" s="1">
-        <f>IF($A29="","","https://momentedit.kr/i-family/family-"&amp;$H29&amp;".html?e="&amp;$A29)</f>
+      <c r="AA29" s="1">
+        <f>IF($A29="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H29,2)&amp;".html?e="&amp;$A29)</f>
+      </c>
+      <c r="AB29" s="1">
+        <f>IF($A29="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H29,2)&amp;".html?e="&amp;$A29)</f>
       </c>
     </row>
     <row r="30">
-      <c r="X30" s="1">
-        <f>IF($A30="","","https://momentedit.kr/i/cover-"&amp;$H30&amp;".html?e="&amp;$A30)</f>
-      </c>
-      <c r="Y30" s="1">
-        <f>IF($A30="","","https://momentedit.kr/i-family/family-"&amp;$H30&amp;".html?e="&amp;$A30)</f>
+      <c r="AA30" s="1">
+        <f>IF($A30="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H30,2)&amp;".html?e="&amp;$A30)</f>
+      </c>
+      <c r="AB30" s="1">
+        <f>IF($A30="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H30,2)&amp;".html?e="&amp;$A30)</f>
       </c>
     </row>
     <row r="31">
-      <c r="X31" s="1">
-        <f>IF($A31="","","https://momentedit.kr/i/cover-"&amp;$H31&amp;".html?e="&amp;$A31)</f>
-      </c>
-      <c r="Y31" s="1">
-        <f>IF($A31="","","https://momentedit.kr/i-family/family-"&amp;$H31&amp;".html?e="&amp;$A31)</f>
+      <c r="AA31" s="1">
+        <f>IF($A31="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H31,2)&amp;".html?e="&amp;$A31)</f>
+      </c>
+      <c r="AB31" s="1">
+        <f>IF($A31="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H31,2)&amp;".html?e="&amp;$A31)</f>
       </c>
     </row>
     <row r="32">
-      <c r="X32" s="1">
-        <f>IF($A32="","","https://momentedit.kr/i/cover-"&amp;$H32&amp;".html?e="&amp;$A32)</f>
-      </c>
-      <c r="Y32" s="1">
-        <f>IF($A32="","","https://momentedit.kr/i-family/family-"&amp;$H32&amp;".html?e="&amp;$A32)</f>
+      <c r="AA32" s="1">
+        <f>IF($A32="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H32,2)&amp;".html?e="&amp;$A32)</f>
+      </c>
+      <c r="AB32" s="1">
+        <f>IF($A32="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H32,2)&amp;".html?e="&amp;$A32)</f>
       </c>
     </row>
     <row r="33">
-      <c r="X33" s="1">
-        <f>IF($A33="","","https://momentedit.kr/i/cover-"&amp;$H33&amp;".html?e="&amp;$A33)</f>
-      </c>
-      <c r="Y33" s="1">
-        <f>IF($A33="","","https://momentedit.kr/i-family/family-"&amp;$H33&amp;".html?e="&amp;$A33)</f>
+      <c r="AA33" s="1">
+        <f>IF($A33="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H33,2)&amp;".html?e="&amp;$A33)</f>
+      </c>
+      <c r="AB33" s="1">
+        <f>IF($A33="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H33,2)&amp;".html?e="&amp;$A33)</f>
       </c>
     </row>
     <row r="34">
-      <c r="X34" s="1">
-        <f>IF($A34="","","https://momentedit.kr/i/cover-"&amp;$H34&amp;".html?e="&amp;$A34)</f>
-      </c>
-      <c r="Y34" s="1">
-        <f>IF($A34="","","https://momentedit.kr/i-family/family-"&amp;$H34&amp;".html?e="&amp;$A34)</f>
+      <c r="AA34" s="1">
+        <f>IF($A34="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H34,2)&amp;".html?e="&amp;$A34)</f>
+      </c>
+      <c r="AB34" s="1">
+        <f>IF($A34="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H34,2)&amp;".html?e="&amp;$A34)</f>
       </c>
     </row>
     <row r="35">
-      <c r="X35" s="1">
-        <f>IF($A35="","","https://momentedit.kr/i/cover-"&amp;$H35&amp;".html?e="&amp;$A35)</f>
-      </c>
-      <c r="Y35" s="1">
-        <f>IF($A35="","","https://momentedit.kr/i-family/family-"&amp;$H35&amp;".html?e="&amp;$A35)</f>
+      <c r="AA35" s="1">
+        <f>IF($A35="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H35,2)&amp;".html?e="&amp;$A35)</f>
+      </c>
+      <c r="AB35" s="1">
+        <f>IF($A35="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H35,2)&amp;".html?e="&amp;$A35)</f>
       </c>
     </row>
     <row r="36">
-      <c r="X36" s="1">
-        <f>IF($A36="","","https://momentedit.kr/i/cover-"&amp;$H36&amp;".html?e="&amp;$A36)</f>
-      </c>
-      <c r="Y36" s="1">
-        <f>IF($A36="","","https://momentedit.kr/i-family/family-"&amp;$H36&amp;".html?e="&amp;$A36)</f>
+      <c r="AA36" s="1">
+        <f>IF($A36="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H36,2)&amp;".html?e="&amp;$A36)</f>
+      </c>
+      <c r="AB36" s="1">
+        <f>IF($A36="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H36,2)&amp;".html?e="&amp;$A36)</f>
       </c>
     </row>
     <row r="37">
-      <c r="X37" s="1">
-        <f>IF($A37="","","https://momentedit.kr/i/cover-"&amp;$H37&amp;".html?e="&amp;$A37)</f>
-      </c>
-      <c r="Y37" s="1">
-        <f>IF($A37="","","https://momentedit.kr/i-family/family-"&amp;$H37&amp;".html?e="&amp;$A37)</f>
+      <c r="AA37" s="1">
+        <f>IF($A37="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H37,2)&amp;".html?e="&amp;$A37)</f>
+      </c>
+      <c r="AB37" s="1">
+        <f>IF($A37="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H37,2)&amp;".html?e="&amp;$A37)</f>
       </c>
     </row>
     <row r="38">
-      <c r="X38" s="1">
-        <f>IF($A38="","","https://momentedit.kr/i/cover-"&amp;$H38&amp;".html?e="&amp;$A38)</f>
-      </c>
-      <c r="Y38" s="1">
-        <f>IF($A38="","","https://momentedit.kr/i-family/family-"&amp;$H38&amp;".html?e="&amp;$A38)</f>
+      <c r="AA38" s="1">
+        <f>IF($A38="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H38,2)&amp;".html?e="&amp;$A38)</f>
+      </c>
+      <c r="AB38" s="1">
+        <f>IF($A38="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H38,2)&amp;".html?e="&amp;$A38)</f>
       </c>
     </row>
     <row r="39">
-      <c r="X39" s="1">
-        <f>IF($A39="","","https://momentedit.kr/i/cover-"&amp;$H39&amp;".html?e="&amp;$A39)</f>
-      </c>
-      <c r="Y39" s="1">
-        <f>IF($A39="","","https://momentedit.kr/i-family/family-"&amp;$H39&amp;".html?e="&amp;$A39)</f>
+      <c r="AA39" s="1">
+        <f>IF($A39="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H39,2)&amp;".html?e="&amp;$A39)</f>
+      </c>
+      <c r="AB39" s="1">
+        <f>IF($A39="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H39,2)&amp;".html?e="&amp;$A39)</f>
       </c>
     </row>
     <row r="40">
-      <c r="X40" s="1">
-        <f>IF($A40="","","https://momentedit.kr/i/cover-"&amp;$H40&amp;".html?e="&amp;$A40)</f>
-      </c>
-      <c r="Y40" s="1">
-        <f>IF($A40="","","https://momentedit.kr/i-family/family-"&amp;$H40&amp;".html?e="&amp;$A40)</f>
+      <c r="AA40" s="1">
+        <f>IF($A40="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H40,2)&amp;".html?e="&amp;$A40)</f>
+      </c>
+      <c r="AB40" s="1">
+        <f>IF($A40="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H40,2)&amp;".html?e="&amp;$A40)</f>
       </c>
     </row>
     <row r="41">
-      <c r="X41" s="1">
-        <f>IF($A41="","","https://momentedit.kr/i/cover-"&amp;$H41&amp;".html?e="&amp;$A41)</f>
-      </c>
-      <c r="Y41" s="1">
-        <f>IF($A41="","","https://momentedit.kr/i-family/family-"&amp;$H41&amp;".html?e="&amp;$A41)</f>
+      <c r="AA41" s="1">
+        <f>IF($A41="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H41,2)&amp;".html?e="&amp;$A41)</f>
+      </c>
+      <c r="AB41" s="1">
+        <f>IF($A41="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H41,2)&amp;".html?e="&amp;$A41)</f>
       </c>
     </row>
     <row r="42">
-      <c r="X42" s="1">
-        <f>IF($A42="","","https://momentedit.kr/i/cover-"&amp;$H42&amp;".html?e="&amp;$A42)</f>
-      </c>
-      <c r="Y42" s="1">
-        <f>IF($A42="","","https://momentedit.kr/i-family/family-"&amp;$H42&amp;".html?e="&amp;$A42)</f>
+      <c r="AA42" s="1">
+        <f>IF($A42="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H42,2)&amp;".html?e="&amp;$A42)</f>
+      </c>
+      <c r="AB42" s="1">
+        <f>IF($A42="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H42,2)&amp;".html?e="&amp;$A42)</f>
       </c>
     </row>
     <row r="43">
-      <c r="X43" s="1">
-        <f>IF($A43="","","https://momentedit.kr/i/cover-"&amp;$H43&amp;".html?e="&amp;$A43)</f>
-      </c>
-      <c r="Y43" s="1">
-        <f>IF($A43="","","https://momentedit.kr/i-family/family-"&amp;$H43&amp;".html?e="&amp;$A43)</f>
+      <c r="AA43" s="1">
+        <f>IF($A43="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H43,2)&amp;".html?e="&amp;$A43)</f>
+      </c>
+      <c r="AB43" s="1">
+        <f>IF($A43="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H43,2)&amp;".html?e="&amp;$A43)</f>
       </c>
     </row>
     <row r="44">
-      <c r="X44" s="1">
-        <f>IF($A44="","","https://momentedit.kr/i/cover-"&amp;$H44&amp;".html?e="&amp;$A44)</f>
-      </c>
-      <c r="Y44" s="1">
-        <f>IF($A44="","","https://momentedit.kr/i-family/family-"&amp;$H44&amp;".html?e="&amp;$A44)</f>
+      <c r="AA44" s="1">
+        <f>IF($A44="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H44,2)&amp;".html?e="&amp;$A44)</f>
+      </c>
+      <c r="AB44" s="1">
+        <f>IF($A44="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H44,2)&amp;".html?e="&amp;$A44)</f>
       </c>
     </row>
     <row r="45">
-      <c r="X45" s="1">
-        <f>IF($A45="","","https://momentedit.kr/i/cover-"&amp;$H45&amp;".html?e="&amp;$A45)</f>
-      </c>
-      <c r="Y45" s="1">
-        <f>IF($A45="","","https://momentedit.kr/i-family/family-"&amp;$H45&amp;".html?e="&amp;$A45)</f>
+      <c r="AA45" s="1">
+        <f>IF($A45="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H45,2)&amp;".html?e="&amp;$A45)</f>
+      </c>
+      <c r="AB45" s="1">
+        <f>IF($A45="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H45,2)&amp;".html?e="&amp;$A45)</f>
       </c>
     </row>
     <row r="46">
-      <c r="X46" s="1">
-        <f>IF($A46="","","https://momentedit.kr/i/cover-"&amp;$H46&amp;".html?e="&amp;$A46)</f>
-      </c>
-      <c r="Y46" s="1">
-        <f>IF($A46="","","https://momentedit.kr/i-family/family-"&amp;$H46&amp;".html?e="&amp;$A46)</f>
+      <c r="AA46" s="1">
+        <f>IF($A46="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H46,2)&amp;".html?e="&amp;$A46)</f>
+      </c>
+      <c r="AB46" s="1">
+        <f>IF($A46="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H46,2)&amp;".html?e="&amp;$A46)</f>
       </c>
     </row>
     <row r="47">
-      <c r="X47" s="1">
-        <f>IF($A47="","","https://momentedit.kr/i/cover-"&amp;$H47&amp;".html?e="&amp;$A47)</f>
-      </c>
-      <c r="Y47" s="1">
-        <f>IF($A47="","","https://momentedit.kr/i-family/family-"&amp;$H47&amp;".html?e="&amp;$A47)</f>
+      <c r="AA47" s="1">
+        <f>IF($A47="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H47,2)&amp;".html?e="&amp;$A47)</f>
+      </c>
+      <c r="AB47" s="1">
+        <f>IF($A47="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H47,2)&amp;".html?e="&amp;$A47)</f>
       </c>
     </row>
     <row r="48">
-      <c r="X48" s="1">
-        <f>IF($A48="","","https://momentedit.kr/i/cover-"&amp;$H48&amp;".html?e="&amp;$A48)</f>
-      </c>
-      <c r="Y48" s="1">
-        <f>IF($A48="","","https://momentedit.kr/i-family/family-"&amp;$H48&amp;".html?e="&amp;$A48)</f>
+      <c r="AA48" s="1">
+        <f>IF($A48="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H48,2)&amp;".html?e="&amp;$A48)</f>
+      </c>
+      <c r="AB48" s="1">
+        <f>IF($A48="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H48,2)&amp;".html?e="&amp;$A48)</f>
       </c>
     </row>
     <row r="49">
-      <c r="X49" s="1">
-        <f>IF($A49="","","https://momentedit.kr/i/cover-"&amp;$H49&amp;".html?e="&amp;$A49)</f>
-      </c>
-      <c r="Y49" s="1">
-        <f>IF($A49="","","https://momentedit.kr/i-family/family-"&amp;$H49&amp;".html?e="&amp;$A49)</f>
+      <c r="AA49" s="1">
+        <f>IF($A49="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H49,2)&amp;".html?e="&amp;$A49)</f>
+      </c>
+      <c r="AB49" s="1">
+        <f>IF($A49="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H49,2)&amp;".html?e="&amp;$A49)</f>
       </c>
     </row>
     <row r="50">
-      <c r="X50" s="1">
-        <f>IF($A50="","","https://momentedit.kr/i/cover-"&amp;$H50&amp;".html?e="&amp;$A50)</f>
-      </c>
-      <c r="Y50" s="1">
-        <f>IF($A50="","","https://momentedit.kr/i-family/family-"&amp;$H50&amp;".html?e="&amp;$A50)</f>
+      <c r="AA50" s="1">
+        <f>IF($A50="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H50,2)&amp;".html?e="&amp;$A50)</f>
+      </c>
+      <c r="AB50" s="1">
+        <f>IF($A50="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H50,2)&amp;".html?e="&amp;$A50)</f>
       </c>
     </row>
     <row r="51">
-      <c r="X51" s="1">
-        <f>IF($A51="","","https://momentedit.kr/i/cover-"&amp;$H51&amp;".html?e="&amp;$A51)</f>
-      </c>
-      <c r="Y51" s="1">
-        <f>IF($A51="","","https://momentedit.kr/i-family/family-"&amp;$H51&amp;".html?e="&amp;$A51)</f>
+      <c r="AA51" s="1">
+        <f>IF($A51="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H51,2)&amp;".html?e="&amp;$A51)</f>
+      </c>
+      <c r="AB51" s="1">
+        <f>IF($A51="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H51,2)&amp;".html?e="&amp;$A51)</f>
       </c>
     </row>
     <row r="52">
-      <c r="X52" s="1">
-        <f>IF($A52="","","https://momentedit.kr/i/cover-"&amp;$H52&amp;".html?e="&amp;$A52)</f>
-      </c>
-      <c r="Y52" s="1">
-        <f>IF($A52="","","https://momentedit.kr/i-family/family-"&amp;$H52&amp;".html?e="&amp;$A52)</f>
+      <c r="AA52" s="1">
+        <f>IF($A52="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H52,2)&amp;".html?e="&amp;$A52)</f>
+      </c>
+      <c r="AB52" s="1">
+        <f>IF($A52="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H52,2)&amp;".html?e="&amp;$A52)</f>
       </c>
     </row>
     <row r="53">
-      <c r="X53" s="1">
-        <f>IF($A53="","","https://momentedit.kr/i/cover-"&amp;$H53&amp;".html?e="&amp;$A53)</f>
-      </c>
-      <c r="Y53" s="1">
-        <f>IF($A53="","","https://momentedit.kr/i-family/family-"&amp;$H53&amp;".html?e="&amp;$A53)</f>
+      <c r="AA53" s="1">
+        <f>IF($A53="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H53,2)&amp;".html?e="&amp;$A53)</f>
+      </c>
+      <c r="AB53" s="1">
+        <f>IF($A53="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H53,2)&amp;".html?e="&amp;$A53)</f>
       </c>
     </row>
     <row r="54">
-      <c r="X54" s="1">
-        <f>IF($A54="","","https://momentedit.kr/i/cover-"&amp;$H54&amp;".html?e="&amp;$A54)</f>
-      </c>
-      <c r="Y54" s="1">
-        <f>IF($A54="","","https://momentedit.kr/i-family/family-"&amp;$H54&amp;".html?e="&amp;$A54)</f>
+      <c r="AA54" s="1">
+        <f>IF($A54="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H54,2)&amp;".html?e="&amp;$A54)</f>
+      </c>
+      <c r="AB54" s="1">
+        <f>IF($A54="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H54,2)&amp;".html?e="&amp;$A54)</f>
       </c>
     </row>
     <row r="55">
-      <c r="X55" s="1">
-        <f>IF($A55="","","https://momentedit.kr/i/cover-"&amp;$H55&amp;".html?e="&amp;$A55)</f>
-      </c>
-      <c r="Y55" s="1">
-        <f>IF($A55="","","https://momentedit.kr/i-family/family-"&amp;$H55&amp;".html?e="&amp;$A55)</f>
+      <c r="AA55" s="1">
+        <f>IF($A55="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H55,2)&amp;".html?e="&amp;$A55)</f>
+      </c>
+      <c r="AB55" s="1">
+        <f>IF($A55="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H55,2)&amp;".html?e="&amp;$A55)</f>
       </c>
     </row>
     <row r="56">
-      <c r="X56" s="1">
-        <f>IF($A56="","","https://momentedit.kr/i/cover-"&amp;$H56&amp;".html?e="&amp;$A56)</f>
-      </c>
-      <c r="Y56" s="1">
-        <f>IF($A56="","","https://momentedit.kr/i-family/family-"&amp;$H56&amp;".html?e="&amp;$A56)</f>
+      <c r="AA56" s="1">
+        <f>IF($A56="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H56,2)&amp;".html?e="&amp;$A56)</f>
+      </c>
+      <c r="AB56" s="1">
+        <f>IF($A56="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H56,2)&amp;".html?e="&amp;$A56)</f>
       </c>
     </row>
     <row r="57">
-      <c r="X57" s="1">
-        <f>IF($A57="","","https://momentedit.kr/i/cover-"&amp;$H57&amp;".html?e="&amp;$A57)</f>
-      </c>
-      <c r="Y57" s="1">
-        <f>IF($A57="","","https://momentedit.kr/i-family/family-"&amp;$H57&amp;".html?e="&amp;$A57)</f>
+      <c r="AA57" s="1">
+        <f>IF($A57="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H57,2)&amp;".html?e="&amp;$A57)</f>
+      </c>
+      <c r="AB57" s="1">
+        <f>IF($A57="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H57,2)&amp;".html?e="&amp;$A57)</f>
       </c>
     </row>
     <row r="58">
-      <c r="X58" s="1">
-        <f>IF($A58="","","https://momentedit.kr/i/cover-"&amp;$H58&amp;".html?e="&amp;$A58)</f>
-      </c>
-      <c r="Y58" s="1">
-        <f>IF($A58="","","https://momentedit.kr/i-family/family-"&amp;$H58&amp;".html?e="&amp;$A58)</f>
+      <c r="AA58" s="1">
+        <f>IF($A58="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H58,2)&amp;".html?e="&amp;$A58)</f>
+      </c>
+      <c r="AB58" s="1">
+        <f>IF($A58="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H58,2)&amp;".html?e="&amp;$A58)</f>
       </c>
     </row>
     <row r="59">
-      <c r="X59" s="1">
-        <f>IF($A59="","","https://momentedit.kr/i/cover-"&amp;$H59&amp;".html?e="&amp;$A59)</f>
-      </c>
-      <c r="Y59" s="1">
-        <f>IF($A59="","","https://momentedit.kr/i-family/family-"&amp;$H59&amp;".html?e="&amp;$A59)</f>
+      <c r="AA59" s="1">
+        <f>IF($A59="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H59,2)&amp;".html?e="&amp;$A59)</f>
+      </c>
+      <c r="AB59" s="1">
+        <f>IF($A59="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H59,2)&amp;".html?e="&amp;$A59)</f>
       </c>
     </row>
     <row r="60">
-      <c r="X60" s="1">
-        <f>IF($A60="","","https://momentedit.kr/i/cover-"&amp;$H60&amp;".html?e="&amp;$A60)</f>
-      </c>
-      <c r="Y60" s="1">
-        <f>IF($A60="","","https://momentedit.kr/i-family/family-"&amp;$H60&amp;".html?e="&amp;$A60)</f>
+      <c r="AA60" s="1">
+        <f>IF($A60="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H60,2)&amp;".html?e="&amp;$A60)</f>
+      </c>
+      <c r="AB60" s="1">
+        <f>IF($A60="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H60,2)&amp;".html?e="&amp;$A60)</f>
       </c>
     </row>
     <row r="61">
-      <c r="X61" s="1">
-        <f>IF($A61="","","https://momentedit.kr/i/cover-"&amp;$H61&amp;".html?e="&amp;$A61)</f>
-      </c>
-      <c r="Y61" s="1">
-        <f>IF($A61="","","https://momentedit.kr/i-family/family-"&amp;$H61&amp;".html?e="&amp;$A61)</f>
+      <c r="AA61" s="1">
+        <f>IF($A61="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H61,2)&amp;".html?e="&amp;$A61)</f>
+      </c>
+      <c r="AB61" s="1">
+        <f>IF($A61="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H61,2)&amp;".html?e="&amp;$A61)</f>
       </c>
     </row>
     <row r="62">
-      <c r="X62" s="1">
-        <f>IF($A62="","","https://momentedit.kr/i/cover-"&amp;$H62&amp;".html?e="&amp;$A62)</f>
-      </c>
-      <c r="Y62" s="1">
-        <f>IF($A62="","","https://momentedit.kr/i-family/family-"&amp;$H62&amp;".html?e="&amp;$A62)</f>
+      <c r="AA62" s="1">
+        <f>IF($A62="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H62,2)&amp;".html?e="&amp;$A62)</f>
+      </c>
+      <c r="AB62" s="1">
+        <f>IF($A62="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H62,2)&amp;".html?e="&amp;$A62)</f>
       </c>
     </row>
     <row r="63">
-      <c r="X63" s="1">
-        <f>IF($A63="","","https://momentedit.kr/i/cover-"&amp;$H63&amp;".html?e="&amp;$A63)</f>
-      </c>
-      <c r="Y63" s="1">
-        <f>IF($A63="","","https://momentedit.kr/i-family/family-"&amp;$H63&amp;".html?e="&amp;$A63)</f>
+      <c r="AA63" s="1">
+        <f>IF($A63="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H63,2)&amp;".html?e="&amp;$A63)</f>
+      </c>
+      <c r="AB63" s="1">
+        <f>IF($A63="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H63,2)&amp;".html?e="&amp;$A63)</f>
       </c>
     </row>
     <row r="64">
-      <c r="X64" s="1">
-        <f>IF($A64="","","https://momentedit.kr/i/cover-"&amp;$H64&amp;".html?e="&amp;$A64)</f>
-      </c>
-      <c r="Y64" s="1">
-        <f>IF($A64="","","https://momentedit.kr/i-family/family-"&amp;$H64&amp;".html?e="&amp;$A64)</f>
+      <c r="AA64" s="1">
+        <f>IF($A64="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H64,2)&amp;".html?e="&amp;$A64)</f>
+      </c>
+      <c r="AB64" s="1">
+        <f>IF($A64="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H64,2)&amp;".html?e="&amp;$A64)</f>
       </c>
     </row>
     <row r="65">
-      <c r="X65" s="1">
-        <f>IF($A65="","","https://momentedit.kr/i/cover-"&amp;$H65&amp;".html?e="&amp;$A65)</f>
-      </c>
-      <c r="Y65" s="1">
-        <f>IF($A65="","","https://momentedit.kr/i-family/family-"&amp;$H65&amp;".html?e="&amp;$A65)</f>
+      <c r="AA65" s="1">
+        <f>IF($A65="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H65,2)&amp;".html?e="&amp;$A65)</f>
+      </c>
+      <c r="AB65" s="1">
+        <f>IF($A65="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H65,2)&amp;".html?e="&amp;$A65)</f>
       </c>
     </row>
     <row r="66">
-      <c r="X66" s="1">
-        <f>IF($A66="","","https://momentedit.kr/i/cover-"&amp;$H66&amp;".html?e="&amp;$A66)</f>
-      </c>
-      <c r="Y66" s="1">
-        <f>IF($A66="","","https://momentedit.kr/i-family/family-"&amp;$H66&amp;".html?e="&amp;$A66)</f>
+      <c r="AA66" s="1">
+        <f>IF($A66="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H66,2)&amp;".html?e="&amp;$A66)</f>
+      </c>
+      <c r="AB66" s="1">
+        <f>IF($A66="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H66,2)&amp;".html?e="&amp;$A66)</f>
       </c>
     </row>
     <row r="67">
-      <c r="X67" s="1">
-        <f>IF($A67="","","https://momentedit.kr/i/cover-"&amp;$H67&amp;".html?e="&amp;$A67)</f>
-      </c>
-      <c r="Y67" s="1">
-        <f>IF($A67="","","https://momentedit.kr/i-family/family-"&amp;$H67&amp;".html?e="&amp;$A67)</f>
+      <c r="AA67" s="1">
+        <f>IF($A67="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H67,2)&amp;".html?e="&amp;$A67)</f>
+      </c>
+      <c r="AB67" s="1">
+        <f>IF($A67="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H67,2)&amp;".html?e="&amp;$A67)</f>
       </c>
     </row>
     <row r="68">
-      <c r="X68" s="1">
-        <f>IF($A68="","","https://momentedit.kr/i/cover-"&amp;$H68&amp;".html?e="&amp;$A68)</f>
-      </c>
-      <c r="Y68" s="1">
-        <f>IF($A68="","","https://momentedit.kr/i-family/family-"&amp;$H68&amp;".html?e="&amp;$A68)</f>
+      <c r="AA68" s="1">
+        <f>IF($A68="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H68,2)&amp;".html?e="&amp;$A68)</f>
+      </c>
+      <c r="AB68" s="1">
+        <f>IF($A68="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H68,2)&amp;".html?e="&amp;$A68)</f>
       </c>
     </row>
     <row r="69">
-      <c r="X69" s="1">
-        <f>IF($A69="","","https://momentedit.kr/i/cover-"&amp;$H69&amp;".html?e="&amp;$A69)</f>
-      </c>
-      <c r="Y69" s="1">
-        <f>IF($A69="","","https://momentedit.kr/i-family/family-"&amp;$H69&amp;".html?e="&amp;$A69)</f>
+      <c r="AA69" s="1">
+        <f>IF($A69="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H69,2)&amp;".html?e="&amp;$A69)</f>
+      </c>
+      <c r="AB69" s="1">
+        <f>IF($A69="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H69,2)&amp;".html?e="&amp;$A69)</f>
       </c>
     </row>
     <row r="70">
-      <c r="X70" s="1">
-        <f>IF($A70="","","https://momentedit.kr/i/cover-"&amp;$H70&amp;".html?e="&amp;$A70)</f>
-      </c>
-      <c r="Y70" s="1">
-        <f>IF($A70="","","https://momentedit.kr/i-family/family-"&amp;$H70&amp;".html?e="&amp;$A70)</f>
+      <c r="AA70" s="1">
+        <f>IF($A70="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H70,2)&amp;".html?e="&amp;$A70)</f>
+      </c>
+      <c r="AB70" s="1">
+        <f>IF($A70="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H70,2)&amp;".html?e="&amp;$A70)</f>
       </c>
     </row>
     <row r="71">
-      <c r="X71" s="1">
-        <f>IF($A71="","","https://momentedit.kr/i/cover-"&amp;$H71&amp;".html?e="&amp;$A71)</f>
-      </c>
-      <c r="Y71" s="1">
-        <f>IF($A71="","","https://momentedit.kr/i-family/family-"&amp;$H71&amp;".html?e="&amp;$A71)</f>
+      <c r="AA71" s="1">
+        <f>IF($A71="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H71,2)&amp;".html?e="&amp;$A71)</f>
+      </c>
+      <c r="AB71" s="1">
+        <f>IF($A71="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H71,2)&amp;".html?e="&amp;$A71)</f>
       </c>
     </row>
     <row r="72">
-      <c r="X72" s="1">
-        <f>IF($A72="","","https://momentedit.kr/i/cover-"&amp;$H72&amp;".html?e="&amp;$A72)</f>
-      </c>
-      <c r="Y72" s="1">
-        <f>IF($A72="","","https://momentedit.kr/i-family/family-"&amp;$H72&amp;".html?e="&amp;$A72)</f>
+      <c r="AA72" s="1">
+        <f>IF($A72="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H72,2)&amp;".html?e="&amp;$A72)</f>
+      </c>
+      <c r="AB72" s="1">
+        <f>IF($A72="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H72,2)&amp;".html?e="&amp;$A72)</f>
       </c>
     </row>
     <row r="73">
-      <c r="X73" s="1">
-        <f>IF($A73="","","https://momentedit.kr/i/cover-"&amp;$H73&amp;".html?e="&amp;$A73)</f>
-      </c>
-      <c r="Y73" s="1">
-        <f>IF($A73="","","https://momentedit.kr/i-family/family-"&amp;$H73&amp;".html?e="&amp;$A73)</f>
+      <c r="AA73" s="1">
+        <f>IF($A73="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H73,2)&amp;".html?e="&amp;$A73)</f>
+      </c>
+      <c r="AB73" s="1">
+        <f>IF($A73="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H73,2)&amp;".html?e="&amp;$A73)</f>
       </c>
     </row>
     <row r="74">
-      <c r="X74" s="1">
-        <f>IF($A74="","","https://momentedit.kr/i/cover-"&amp;$H74&amp;".html?e="&amp;$A74)</f>
-      </c>
-      <c r="Y74" s="1">
-        <f>IF($A74="","","https://momentedit.kr/i-family/family-"&amp;$H74&amp;".html?e="&amp;$A74)</f>
+      <c r="AA74" s="1">
+        <f>IF($A74="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H74,2)&amp;".html?e="&amp;$A74)</f>
+      </c>
+      <c r="AB74" s="1">
+        <f>IF($A74="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H74,2)&amp;".html?e="&amp;$A74)</f>
       </c>
     </row>
     <row r="75">
-      <c r="X75" s="1">
-        <f>IF($A75="","","https://momentedit.kr/i/cover-"&amp;$H75&amp;".html?e="&amp;$A75)</f>
-      </c>
-      <c r="Y75" s="1">
-        <f>IF($A75="","","https://momentedit.kr/i-family/family-"&amp;$H75&amp;".html?e="&amp;$A75)</f>
+      <c r="AA75" s="1">
+        <f>IF($A75="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H75,2)&amp;".html?e="&amp;$A75)</f>
+      </c>
+      <c r="AB75" s="1">
+        <f>IF($A75="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H75,2)&amp;".html?e="&amp;$A75)</f>
       </c>
     </row>
     <row r="76">
-      <c r="X76" s="1">
-        <f>IF($A76="","","https://momentedit.kr/i/cover-"&amp;$H76&amp;".html?e="&amp;$A76)</f>
-      </c>
-      <c r="Y76" s="1">
-        <f>IF($A76="","","https://momentedit.kr/i-family/family-"&amp;$H76&amp;".html?e="&amp;$A76)</f>
+      <c r="AA76" s="1">
+        <f>IF($A76="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H76,2)&amp;".html?e="&amp;$A76)</f>
+      </c>
+      <c r="AB76" s="1">
+        <f>IF($A76="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H76,2)&amp;".html?e="&amp;$A76)</f>
       </c>
     </row>
     <row r="77">
-      <c r="X77" s="1">
-        <f>IF($A77="","","https://momentedit.kr/i/cover-"&amp;$H77&amp;".html?e="&amp;$A77)</f>
-      </c>
-      <c r="Y77" s="1">
-        <f>IF($A77="","","https://momentedit.kr/i-family/family-"&amp;$H77&amp;".html?e="&amp;$A77)</f>
+      <c r="AA77" s="1">
+        <f>IF($A77="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H77,2)&amp;".html?e="&amp;$A77)</f>
+      </c>
+      <c r="AB77" s="1">
+        <f>IF($A77="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H77,2)&amp;".html?e="&amp;$A77)</f>
       </c>
     </row>
     <row r="78">
-      <c r="X78" s="1">
-        <f>IF($A78="","","https://momentedit.kr/i/cover-"&amp;$H78&amp;".html?e="&amp;$A78)</f>
-      </c>
-      <c r="Y78" s="1">
-        <f>IF($A78="","","https://momentedit.kr/i-family/family-"&amp;$H78&amp;".html?e="&amp;$A78)</f>
+      <c r="AA78" s="1">
+        <f>IF($A78="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H78,2)&amp;".html?e="&amp;$A78)</f>
+      </c>
+      <c r="AB78" s="1">
+        <f>IF($A78="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H78,2)&amp;".html?e="&amp;$A78)</f>
       </c>
     </row>
     <row r="79">
-      <c r="X79" s="1">
-        <f>IF($A79="","","https://momentedit.kr/i/cover-"&amp;$H79&amp;".html?e="&amp;$A79)</f>
-      </c>
-      <c r="Y79" s="1">
-        <f>IF($A79="","","https://momentedit.kr/i-family/family-"&amp;$H79&amp;".html?e="&amp;$A79)</f>
+      <c r="AA79" s="1">
+        <f>IF($A79="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H79,2)&amp;".html?e="&amp;$A79)</f>
+      </c>
+      <c r="AB79" s="1">
+        <f>IF($A79="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H79,2)&amp;".html?e="&amp;$A79)</f>
       </c>
     </row>
     <row r="80">
-      <c r="X80" s="1">
-        <f>IF($A80="","","https://momentedit.kr/i/cover-"&amp;$H80&amp;".html?e="&amp;$A80)</f>
-      </c>
-      <c r="Y80" s="1">
-        <f>IF($A80="","","https://momentedit.kr/i-family/family-"&amp;$H80&amp;".html?e="&amp;$A80)</f>
+      <c r="AA80" s="1">
+        <f>IF($A80="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H80,2)&amp;".html?e="&amp;$A80)</f>
+      </c>
+      <c r="AB80" s="1">
+        <f>IF($A80="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H80,2)&amp;".html?e="&amp;$A80)</f>
       </c>
     </row>
     <row r="81">
-      <c r="X81" s="1">
-        <f>IF($A81="","","https://momentedit.kr/i/cover-"&amp;$H81&amp;".html?e="&amp;$A81)</f>
-      </c>
-      <c r="Y81" s="1">
-        <f>IF($A81="","","https://momentedit.kr/i-family/family-"&amp;$H81&amp;".html?e="&amp;$A81)</f>
+      <c r="AA81" s="1">
+        <f>IF($A81="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H81,2)&amp;".html?e="&amp;$A81)</f>
+      </c>
+      <c r="AB81" s="1">
+        <f>IF($A81="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H81,2)&amp;".html?e="&amp;$A81)</f>
       </c>
     </row>
     <row r="82">
-      <c r="X82" s="1">
-        <f>IF($A82="","","https://momentedit.kr/i/cover-"&amp;$H82&amp;".html?e="&amp;$A82)</f>
-      </c>
-      <c r="Y82" s="1">
-        <f>IF($A82="","","https://momentedit.kr/i-family/family-"&amp;$H82&amp;".html?e="&amp;$A82)</f>
+      <c r="AA82" s="1">
+        <f>IF($A82="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H82,2)&amp;".html?e="&amp;$A82)</f>
+      </c>
+      <c r="AB82" s="1">
+        <f>IF($A82="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H82,2)&amp;".html?e="&amp;$A82)</f>
       </c>
     </row>
     <row r="83">
-      <c r="X83" s="1">
-        <f>IF($A83="","","https://momentedit.kr/i/cover-"&amp;$H83&amp;".html?e="&amp;$A83)</f>
-      </c>
-      <c r="Y83" s="1">
-        <f>IF($A83="","","https://momentedit.kr/i-family/family-"&amp;$H83&amp;".html?e="&amp;$A83)</f>
+      <c r="AA83" s="1">
+        <f>IF($A83="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H83,2)&amp;".html?e="&amp;$A83)</f>
+      </c>
+      <c r="AB83" s="1">
+        <f>IF($A83="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H83,2)&amp;".html?e="&amp;$A83)</f>
       </c>
     </row>
     <row r="84">
-      <c r="X84" s="1">
-        <f>IF($A84="","","https://momentedit.kr/i/cover-"&amp;$H84&amp;".html?e="&amp;$A84)</f>
-      </c>
-      <c r="Y84" s="1">
-        <f>IF($A84="","","https://momentedit.kr/i-family/family-"&amp;$H84&amp;".html?e="&amp;$A84)</f>
+      <c r="AA84" s="1">
+        <f>IF($A84="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H84,2)&amp;".html?e="&amp;$A84)</f>
+      </c>
+      <c r="AB84" s="1">
+        <f>IF($A84="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H84,2)&amp;".html?e="&amp;$A84)</f>
       </c>
     </row>
     <row r="85">
-      <c r="X85" s="1">
-        <f>IF($A85="","","https://momentedit.kr/i/cover-"&amp;$H85&amp;".html?e="&amp;$A85)</f>
-      </c>
-      <c r="Y85" s="1">
-        <f>IF($A85="","","https://momentedit.kr/i-family/family-"&amp;$H85&amp;".html?e="&amp;$A85)</f>
+      <c r="AA85" s="1">
+        <f>IF($A85="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H85,2)&amp;".html?e="&amp;$A85)</f>
+      </c>
+      <c r="AB85" s="1">
+        <f>IF($A85="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H85,2)&amp;".html?e="&amp;$A85)</f>
       </c>
     </row>
     <row r="86">
-      <c r="X86" s="1">
-        <f>IF($A86="","","https://momentedit.kr/i/cover-"&amp;$H86&amp;".html?e="&amp;$A86)</f>
-      </c>
-      <c r="Y86" s="1">
-        <f>IF($A86="","","https://momentedit.kr/i-family/family-"&amp;$H86&amp;".html?e="&amp;$A86)</f>
+      <c r="AA86" s="1">
+        <f>IF($A86="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H86,2)&amp;".html?e="&amp;$A86)</f>
+      </c>
+      <c r="AB86" s="1">
+        <f>IF($A86="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H86,2)&amp;".html?e="&amp;$A86)</f>
       </c>
     </row>
     <row r="87">
-      <c r="X87" s="1">
-        <f>IF($A87="","","https://momentedit.kr/i/cover-"&amp;$H87&amp;".html?e="&amp;$A87)</f>
-      </c>
-      <c r="Y87" s="1">
-        <f>IF($A87="","","https://momentedit.kr/i-family/family-"&amp;$H87&amp;".html?e="&amp;$A87)</f>
+      <c r="AA87" s="1">
+        <f>IF($A87="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H87,2)&amp;".html?e="&amp;$A87)</f>
+      </c>
+      <c r="AB87" s="1">
+        <f>IF($A87="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H87,2)&amp;".html?e="&amp;$A87)</f>
       </c>
     </row>
     <row r="88">
-      <c r="X88" s="1">
-        <f>IF($A88="","","https://momentedit.kr/i/cover-"&amp;$H88&amp;".html?e="&amp;$A88)</f>
-      </c>
-      <c r="Y88" s="1">
-        <f>IF($A88="","","https://momentedit.kr/i-family/family-"&amp;$H88&amp;".html?e="&amp;$A88)</f>
+      <c r="AA88" s="1">
+        <f>IF($A88="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H88,2)&amp;".html?e="&amp;$A88)</f>
+      </c>
+      <c r="AB88" s="1">
+        <f>IF($A88="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H88,2)&amp;".html?e="&amp;$A88)</f>
       </c>
     </row>
     <row r="89">
-      <c r="X89" s="1">
-        <f>IF($A89="","","https://momentedit.kr/i/cover-"&amp;$H89&amp;".html?e="&amp;$A89)</f>
-      </c>
-      <c r="Y89" s="1">
-        <f>IF($A89="","","https://momentedit.kr/i-family/family-"&amp;$H89&amp;".html?e="&amp;$A89)</f>
+      <c r="AA89" s="1">
+        <f>IF($A89="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H89,2)&amp;".html?e="&amp;$A89)</f>
+      </c>
+      <c r="AB89" s="1">
+        <f>IF($A89="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H89,2)&amp;".html?e="&amp;$A89)</f>
       </c>
     </row>
     <row r="90">
-      <c r="X90" s="1">
-        <f>IF($A90="","","https://momentedit.kr/i/cover-"&amp;$H90&amp;".html?e="&amp;$A90)</f>
-      </c>
-      <c r="Y90" s="1">
-        <f>IF($A90="","","https://momentedit.kr/i-family/family-"&amp;$H90&amp;".html?e="&amp;$A90)</f>
+      <c r="AA90" s="1">
+        <f>IF($A90="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H90,2)&amp;".html?e="&amp;$A90)</f>
+      </c>
+      <c r="AB90" s="1">
+        <f>IF($A90="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H90,2)&amp;".html?e="&amp;$A90)</f>
       </c>
     </row>
     <row r="91">
-      <c r="X91" s="1">
-        <f>IF($A91="","","https://momentedit.kr/i/cover-"&amp;$H91&amp;".html?e="&amp;$A91)</f>
-      </c>
-      <c r="Y91" s="1">
-        <f>IF($A91="","","https://momentedit.kr/i-family/family-"&amp;$H91&amp;".html?e="&amp;$A91)</f>
+      <c r="AA91" s="1">
+        <f>IF($A91="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H91,2)&amp;".html?e="&amp;$A91)</f>
+      </c>
+      <c r="AB91" s="1">
+        <f>IF($A91="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H91,2)&amp;".html?e="&amp;$A91)</f>
       </c>
     </row>
     <row r="92">
-      <c r="X92" s="1">
-        <f>IF($A92="","","https://momentedit.kr/i/cover-"&amp;$H92&amp;".html?e="&amp;$A92)</f>
-      </c>
-      <c r="Y92" s="1">
-        <f>IF($A92="","","https://momentedit.kr/i-family/family-"&amp;$H92&amp;".html?e="&amp;$A92)</f>
+      <c r="AA92" s="1">
+        <f>IF($A92="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H92,2)&amp;".html?e="&amp;$A92)</f>
+      </c>
+      <c r="AB92" s="1">
+        <f>IF($A92="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H92,2)&amp;".html?e="&amp;$A92)</f>
       </c>
     </row>
     <row r="93">
-      <c r="X93" s="1">
-        <f>IF($A93="","","https://momentedit.kr/i/cover-"&amp;$H93&amp;".html?e="&amp;$A93)</f>
-      </c>
-      <c r="Y93" s="1">
-        <f>IF($A93="","","https://momentedit.kr/i-family/family-"&amp;$H93&amp;".html?e="&amp;$A93)</f>
+      <c r="AA93" s="1">
+        <f>IF($A93="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H93,2)&amp;".html?e="&amp;$A93)</f>
+      </c>
+      <c r="AB93" s="1">
+        <f>IF($A93="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H93,2)&amp;".html?e="&amp;$A93)</f>
       </c>
     </row>
     <row r="94">
-      <c r="X94" s="1">
-        <f>IF($A94="","","https://momentedit.kr/i/cover-"&amp;$H94&amp;".html?e="&amp;$A94)</f>
-      </c>
-      <c r="Y94" s="1">
-        <f>IF($A94="","","https://momentedit.kr/i-family/family-"&amp;$H94&amp;".html?e="&amp;$A94)</f>
+      <c r="AA94" s="1">
+        <f>IF($A94="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H94,2)&amp;".html?e="&amp;$A94)</f>
+      </c>
+      <c r="AB94" s="1">
+        <f>IF($A94="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H94,2)&amp;".html?e="&amp;$A94)</f>
       </c>
     </row>
     <row r="95">
-      <c r="X95" s="1">
-        <f>IF($A95="","","https://momentedit.kr/i/cover-"&amp;$H95&amp;".html?e="&amp;$A95)</f>
-      </c>
-      <c r="Y95" s="1">
-        <f>IF($A95="","","https://momentedit.kr/i-family/family-"&amp;$H95&amp;".html?e="&amp;$A95)</f>
+      <c r="AA95" s="1">
+        <f>IF($A95="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H95,2)&amp;".html?e="&amp;$A95)</f>
+      </c>
+      <c r="AB95" s="1">
+        <f>IF($A95="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H95,2)&amp;".html?e="&amp;$A95)</f>
       </c>
     </row>
     <row r="96">
-      <c r="X96" s="1">
-        <f>IF($A96="","","https://momentedit.kr/i/cover-"&amp;$H96&amp;".html?e="&amp;$A96)</f>
-      </c>
-      <c r="Y96" s="1">
-        <f>IF($A96="","","https://momentedit.kr/i-family/family-"&amp;$H96&amp;".html?e="&amp;$A96)</f>
+      <c r="AA96" s="1">
+        <f>IF($A96="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H96,2)&amp;".html?e="&amp;$A96)</f>
+      </c>
+      <c r="AB96" s="1">
+        <f>IF($A96="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H96,2)&amp;".html?e="&amp;$A96)</f>
       </c>
     </row>
     <row r="97">
-      <c r="X97" s="1">
-        <f>IF($A97="","","https://momentedit.kr/i/cover-"&amp;$H97&amp;".html?e="&amp;$A97)</f>
-      </c>
-      <c r="Y97" s="1">
-        <f>IF($A97="","","https://momentedit.kr/i-family/family-"&amp;$H97&amp;".html?e="&amp;$A97)</f>
+      <c r="AA97" s="1">
+        <f>IF($A97="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H97,2)&amp;".html?e="&amp;$A97)</f>
+      </c>
+      <c r="AB97" s="1">
+        <f>IF($A97="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H97,2)&amp;".html?e="&amp;$A97)</f>
       </c>
     </row>
     <row r="98">
-      <c r="X98" s="1">
-        <f>IF($A98="","","https://momentedit.kr/i/cover-"&amp;$H98&amp;".html?e="&amp;$A98)</f>
-      </c>
-      <c r="Y98" s="1">
-        <f>IF($A98="","","https://momentedit.kr/i-family/family-"&amp;$H98&amp;".html?e="&amp;$A98)</f>
+      <c r="AA98" s="1">
+        <f>IF($A98="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H98,2)&amp;".html?e="&amp;$A98)</f>
+      </c>
+      <c r="AB98" s="1">
+        <f>IF($A98="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H98,2)&amp;".html?e="&amp;$A98)</f>
       </c>
     </row>
     <row r="99">
-      <c r="X99" s="1">
-        <f>IF($A99="","","https://momentedit.kr/i/cover-"&amp;$H99&amp;".html?e="&amp;$A99)</f>
-      </c>
-      <c r="Y99" s="1">
-        <f>IF($A99="","","https://momentedit.kr/i-family/family-"&amp;$H99&amp;".html?e="&amp;$A99)</f>
+      <c r="AA99" s="1">
+        <f>IF($A99="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H99,2)&amp;".html?e="&amp;$A99)</f>
+      </c>
+      <c r="AB99" s="1">
+        <f>IF($A99="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H99,2)&amp;".html?e="&amp;$A99)</f>
       </c>
     </row>
     <row r="100">
-      <c r="X100" s="1">
-        <f>IF($A100="","","https://momentedit.kr/i/cover-"&amp;$H100&amp;".html?e="&amp;$A100)</f>
-      </c>
-      <c r="Y100" s="1">
-        <f>IF($A100="","","https://momentedit.kr/i-family/family-"&amp;$H100&amp;".html?e="&amp;$A100)</f>
+      <c r="AA100" s="1">
+        <f>IF($A100="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H100,2)&amp;".html?e="&amp;$A100)</f>
+      </c>
+      <c r="AB100" s="1">
+        <f>IF($A100="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H100,2)&amp;".html?e="&amp;$A100)</f>
       </c>
     </row>
     <row r="101">
-      <c r="X101" s="1">
-        <f>IF($A101="","","https://momentedit.kr/i/cover-"&amp;$H101&amp;".html?e="&amp;$A101)</f>
-      </c>
-      <c r="Y101" s="1">
-        <f>IF($A101="","","https://momentedit.kr/i-family/family-"&amp;$H101&amp;".html?e="&amp;$A101)</f>
+      <c r="AA101" s="1">
+        <f>IF($A101="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H101,2)&amp;".html?e="&amp;$A101)</f>
+      </c>
+      <c r="AB101" s="1">
+        <f>IF($A101="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H101,2)&amp;".html?e="&amp;$A101)</f>
       </c>
     </row>
     <row r="102">
-      <c r="X102" s="1">
-        <f>IF($A102="","","https://momentedit.kr/i/cover-"&amp;$H102&amp;".html?e="&amp;$A102)</f>
-      </c>
-      <c r="Y102" s="1">
-        <f>IF($A102="","","https://momentedit.kr/i-family/family-"&amp;$H102&amp;".html?e="&amp;$A102)</f>
+      <c r="AA102" s="1">
+        <f>IF($A102="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H102,2)&amp;".html?e="&amp;$A102)</f>
+      </c>
+      <c r="AB102" s="1">
+        <f>IF($A102="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H102,2)&amp;".html?e="&amp;$A102)</f>
       </c>
     </row>
     <row r="103">
-      <c r="X103" s="1">
-        <f>IF($A103="","","https://momentedit.kr/i/cover-"&amp;$H103&amp;".html?e="&amp;$A103)</f>
-      </c>
-      <c r="Y103" s="1">
-        <f>IF($A103="","","https://momentedit.kr/i-family/family-"&amp;$H103&amp;".html?e="&amp;$A103)</f>
+      <c r="AA103" s="1">
+        <f>IF($A103="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H103,2)&amp;".html?e="&amp;$A103)</f>
+      </c>
+      <c r="AB103" s="1">
+        <f>IF($A103="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H103,2)&amp;".html?e="&amp;$A103)</f>
       </c>
     </row>
     <row r="104">
-      <c r="X104" s="1">
-        <f>IF($A104="","","https://momentedit.kr/i/cover-"&amp;$H104&amp;".html?e="&amp;$A104)</f>
-      </c>
-      <c r="Y104" s="1">
-        <f>IF($A104="","","https://momentedit.kr/i-family/family-"&amp;$H104&amp;".html?e="&amp;$A104)</f>
+      <c r="AA104" s="1">
+        <f>IF($A104="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H104,2)&amp;".html?e="&amp;$A104)</f>
+      </c>
+      <c r="AB104" s="1">
+        <f>IF($A104="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H104,2)&amp;".html?e="&amp;$A104)</f>
       </c>
     </row>
     <row r="105">
-      <c r="X105" s="1">
-        <f>IF($A105="","","https://momentedit.kr/i/cover-"&amp;$H105&amp;".html?e="&amp;$A105)</f>
-      </c>
-      <c r="Y105" s="1">
-        <f>IF($A105="","","https://momentedit.kr/i-family/family-"&amp;$H105&amp;".html?e="&amp;$A105)</f>
+      <c r="AA105" s="1">
+        <f>IF($A105="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H105,2)&amp;".html?e="&amp;$A105)</f>
+      </c>
+      <c r="AB105" s="1">
+        <f>IF($A105="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H105,2)&amp;".html?e="&amp;$A105)</f>
       </c>
     </row>
     <row r="106">
-      <c r="X106" s="1">
-        <f>IF($A106="","","https://momentedit.kr/i/cover-"&amp;$H106&amp;".html?e="&amp;$A106)</f>
-      </c>
-      <c r="Y106" s="1">
-        <f>IF($A106="","","https://momentedit.kr/i-family/family-"&amp;$H106&amp;".html?e="&amp;$A106)</f>
+      <c r="AA106" s="1">
+        <f>IF($A106="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H106,2)&amp;".html?e="&amp;$A106)</f>
+      </c>
+      <c r="AB106" s="1">
+        <f>IF($A106="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H106,2)&amp;".html?e="&amp;$A106)</f>
       </c>
     </row>
     <row r="107">
-      <c r="X107" s="1">
-        <f>IF($A107="","","https://momentedit.kr/i/cover-"&amp;$H107&amp;".html?e="&amp;$A107)</f>
-      </c>
-      <c r="Y107" s="1">
-        <f>IF($A107="","","https://momentedit.kr/i-family/family-"&amp;$H107&amp;".html?e="&amp;$A107)</f>
+      <c r="AA107" s="1">
+        <f>IF($A107="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H107,2)&amp;".html?e="&amp;$A107)</f>
+      </c>
+      <c r="AB107" s="1">
+        <f>IF($A107="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H107,2)&amp;".html?e="&amp;$A107)</f>
       </c>
     </row>
     <row r="108">
-      <c r="X108" s="1">
-        <f>IF($A108="","","https://momentedit.kr/i/cover-"&amp;$H108&amp;".html?e="&amp;$A108)</f>
-      </c>
-      <c r="Y108" s="1">
-        <f>IF($A108="","","https://momentedit.kr/i-family/family-"&amp;$H108&amp;".html?e="&amp;$A108)</f>
+      <c r="AA108" s="1">
+        <f>IF($A108="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H108,2)&amp;".html?e="&amp;$A108)</f>
+      </c>
+      <c r="AB108" s="1">
+        <f>IF($A108="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H108,2)&amp;".html?e="&amp;$A108)</f>
       </c>
     </row>
     <row r="109">
-      <c r="X109" s="1">
-        <f>IF($A109="","","https://momentedit.kr/i/cover-"&amp;$H109&amp;".html?e="&amp;$A109)</f>
-      </c>
-      <c r="Y109" s="1">
-        <f>IF($A109="","","https://momentedit.kr/i-family/family-"&amp;$H109&amp;".html?e="&amp;$A109)</f>
+      <c r="AA109" s="1">
+        <f>IF($A109="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H109,2)&amp;".html?e="&amp;$A109)</f>
+      </c>
+      <c r="AB109" s="1">
+        <f>IF($A109="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H109,2)&amp;".html?e="&amp;$A109)</f>
       </c>
     </row>
     <row r="110">
-      <c r="X110" s="1">
-        <f>IF($A110="","","https://momentedit.kr/i/cover-"&amp;$H110&amp;".html?e="&amp;$A110)</f>
-      </c>
-      <c r="Y110" s="1">
-        <f>IF($A110="","","https://momentedit.kr/i-family/family-"&amp;$H110&amp;".html?e="&amp;$A110)</f>
+      <c r="AA110" s="1">
+        <f>IF($A110="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H110,2)&amp;".html?e="&amp;$A110)</f>
+      </c>
+      <c r="AB110" s="1">
+        <f>IF($A110="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H110,2)&amp;".html?e="&amp;$A110)</f>
       </c>
     </row>
     <row r="111">
-      <c r="X111" s="1">
-        <f>IF($A111="","","https://momentedit.kr/i/cover-"&amp;$H111&amp;".html?e="&amp;$A111)</f>
-      </c>
-      <c r="Y111" s="1">
-        <f>IF($A111="","","https://momentedit.kr/i-family/family-"&amp;$H111&amp;".html?e="&amp;$A111)</f>
+      <c r="AA111" s="1">
+        <f>IF($A111="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H111,2)&amp;".html?e="&amp;$A111)</f>
+      </c>
+      <c r="AB111" s="1">
+        <f>IF($A111="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H111,2)&amp;".html?e="&amp;$A111)</f>
       </c>
     </row>
     <row r="112">
-      <c r="X112" s="1">
-        <f>IF($A112="","","https://momentedit.kr/i/cover-"&amp;$H112&amp;".html?e="&amp;$A112)</f>
-      </c>
-      <c r="Y112" s="1">
-        <f>IF($A112="","","https://momentedit.kr/i-family/family-"&amp;$H112&amp;".html?e="&amp;$A112)</f>
+      <c r="AA112" s="1">
+        <f>IF($A112="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H112,2)&amp;".html?e="&amp;$A112)</f>
+      </c>
+      <c r="AB112" s="1">
+        <f>IF($A112="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H112,2)&amp;".html?e="&amp;$A112)</f>
       </c>
     </row>
     <row r="113">
-      <c r="X113" s="1">
-        <f>IF($A113="","","https://momentedit.kr/i/cover-"&amp;$H113&amp;".html?e="&amp;$A113)</f>
-      </c>
-      <c r="Y113" s="1">
-        <f>IF($A113="","","https://momentedit.kr/i-family/family-"&amp;$H113&amp;".html?e="&amp;$A113)</f>
+      <c r="AA113" s="1">
+        <f>IF($A113="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H113,2)&amp;".html?e="&amp;$A113)</f>
+      </c>
+      <c r="AB113" s="1">
+        <f>IF($A113="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H113,2)&amp;".html?e="&amp;$A113)</f>
       </c>
     </row>
     <row r="114">
-      <c r="X114" s="1">
-        <f>IF($A114="","","https://momentedit.kr/i/cover-"&amp;$H114&amp;".html?e="&amp;$A114)</f>
-      </c>
-      <c r="Y114" s="1">
-        <f>IF($A114="","","https://momentedit.kr/i-family/family-"&amp;$H114&amp;".html?e="&amp;$A114)</f>
+      <c r="AA114" s="1">
+        <f>IF($A114="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H114,2)&amp;".html?e="&amp;$A114)</f>
+      </c>
+      <c r="AB114" s="1">
+        <f>IF($A114="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H114,2)&amp;".html?e="&amp;$A114)</f>
       </c>
     </row>
     <row r="115">
-      <c r="X115" s="1">
-        <f>IF($A115="","","https://momentedit.kr/i/cover-"&amp;$H115&amp;".html?e="&amp;$A115)</f>
-      </c>
-      <c r="Y115" s="1">
-        <f>IF($A115="","","https://momentedit.kr/i-family/family-"&amp;$H115&amp;".html?e="&amp;$A115)</f>
+      <c r="AA115" s="1">
+        <f>IF($A115="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H115,2)&amp;".html?e="&amp;$A115)</f>
+      </c>
+      <c r="AB115" s="1">
+        <f>IF($A115="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H115,2)&amp;".html?e="&amp;$A115)</f>
       </c>
     </row>
     <row r="116">
-      <c r="X116" s="1">
-        <f>IF($A116="","","https://momentedit.kr/i/cover-"&amp;$H116&amp;".html?e="&amp;$A116)</f>
-      </c>
-      <c r="Y116" s="1">
-        <f>IF($A116="","","https://momentedit.kr/i-family/family-"&amp;$H116&amp;".html?e="&amp;$A116)</f>
+      <c r="AA116" s="1">
+        <f>IF($A116="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H116,2)&amp;".html?e="&amp;$A116)</f>
+      </c>
+      <c r="AB116" s="1">
+        <f>IF($A116="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H116,2)&amp;".html?e="&amp;$A116)</f>
       </c>
     </row>
     <row r="117">
-      <c r="X117" s="1">
-        <f>IF($A117="","","https://momentedit.kr/i/cover-"&amp;$H117&amp;".html?e="&amp;$A117)</f>
-      </c>
-      <c r="Y117" s="1">
-        <f>IF($A117="","","https://momentedit.kr/i-family/family-"&amp;$H117&amp;".html?e="&amp;$A117)</f>
+      <c r="AA117" s="1">
+        <f>IF($A117="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H117,2)&amp;".html?e="&amp;$A117)</f>
+      </c>
+      <c r="AB117" s="1">
+        <f>IF($A117="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H117,2)&amp;".html?e="&amp;$A117)</f>
       </c>
     </row>
     <row r="118">
-      <c r="X118" s="1">
-        <f>IF($A118="","","https://momentedit.kr/i/cover-"&amp;$H118&amp;".html?e="&amp;$A118)</f>
-      </c>
-      <c r="Y118" s="1">
-        <f>IF($A118="","","https://momentedit.kr/i-family/family-"&amp;$H118&amp;".html?e="&amp;$A118)</f>
+      <c r="AA118" s="1">
+        <f>IF($A118="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H118,2)&amp;".html?e="&amp;$A118)</f>
+      </c>
+      <c r="AB118" s="1">
+        <f>IF($A118="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H118,2)&amp;".html?e="&amp;$A118)</f>
       </c>
     </row>
     <row r="119">
-      <c r="X119" s="1">
-        <f>IF($A119="","","https://momentedit.kr/i/cover-"&amp;$H119&amp;".html?e="&amp;$A119)</f>
-      </c>
-      <c r="Y119" s="1">
-        <f>IF($A119="","","https://momentedit.kr/i-family/family-"&amp;$H119&amp;".html?e="&amp;$A119)</f>
+      <c r="AA119" s="1">
+        <f>IF($A119="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H119,2)&amp;".html?e="&amp;$A119)</f>
+      </c>
+      <c r="AB119" s="1">
+        <f>IF($A119="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H119,2)&amp;".html?e="&amp;$A119)</f>
       </c>
     </row>
     <row r="120">
-      <c r="X120" s="1">
-        <f>IF($A120="","","https://momentedit.kr/i/cover-"&amp;$H120&amp;".html?e="&amp;$A120)</f>
-      </c>
-      <c r="Y120" s="1">
-        <f>IF($A120="","","https://momentedit.kr/i-family/family-"&amp;$H120&amp;".html?e="&amp;$A120)</f>
+      <c r="AA120" s="1">
+        <f>IF($A120="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H120,2)&amp;".html?e="&amp;$A120)</f>
+      </c>
+      <c r="AB120" s="1">
+        <f>IF($A120="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H120,2)&amp;".html?e="&amp;$A120)</f>
       </c>
     </row>
     <row r="121">
-      <c r="X121" s="1">
-        <f>IF($A121="","","https://momentedit.kr/i/cover-"&amp;$H121&amp;".html?e="&amp;$A121)</f>
-      </c>
-      <c r="Y121" s="1">
-        <f>IF($A121="","","https://momentedit.kr/i-family/family-"&amp;$H121&amp;".html?e="&amp;$A121)</f>
+      <c r="AA121" s="1">
+        <f>IF($A121="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H121,2)&amp;".html?e="&amp;$A121)</f>
+      </c>
+      <c r="AB121" s="1">
+        <f>IF($A121="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H121,2)&amp;".html?e="&amp;$A121)</f>
       </c>
     </row>
     <row r="122">
-      <c r="X122" s="1">
-        <f>IF($A122="","","https://momentedit.kr/i/cover-"&amp;$H122&amp;".html?e="&amp;$A122)</f>
-      </c>
-      <c r="Y122" s="1">
-        <f>IF($A122="","","https://momentedit.kr/i-family/family-"&amp;$H122&amp;".html?e="&amp;$A122)</f>
+      <c r="AA122" s="1">
+        <f>IF($A122="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H122,2)&amp;".html?e="&amp;$A122)</f>
+      </c>
+      <c r="AB122" s="1">
+        <f>IF($A122="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H122,2)&amp;".html?e="&amp;$A122)</f>
       </c>
     </row>
     <row r="123">
-      <c r="X123" s="1">
-        <f>IF($A123="","","https://momentedit.kr/i/cover-"&amp;$H123&amp;".html?e="&amp;$A123)</f>
-      </c>
-      <c r="Y123" s="1">
-        <f>IF($A123="","","https://momentedit.kr/i-family/family-"&amp;$H123&amp;".html?e="&amp;$A123)</f>
+      <c r="AA123" s="1">
+        <f>IF($A123="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H123,2)&amp;".html?e="&amp;$A123)</f>
+      </c>
+      <c r="AB123" s="1">
+        <f>IF($A123="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H123,2)&amp;".html?e="&amp;$A123)</f>
       </c>
     </row>
     <row r="124">
-      <c r="X124" s="1">
-        <f>IF($A124="","","https://momentedit.kr/i/cover-"&amp;$H124&amp;".html?e="&amp;$A124)</f>
-      </c>
-      <c r="Y124" s="1">
-        <f>IF($A124="","","https://momentedit.kr/i-family/family-"&amp;$H124&amp;".html?e="&amp;$A124)</f>
+      <c r="AA124" s="1">
+        <f>IF($A124="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H124,2)&amp;".html?e="&amp;$A124)</f>
+      </c>
+      <c r="AB124" s="1">
+        <f>IF($A124="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H124,2)&amp;".html?e="&amp;$A124)</f>
       </c>
     </row>
     <row r="125">
-      <c r="X125" s="1">
-        <f>IF($A125="","","https://momentedit.kr/i/cover-"&amp;$H125&amp;".html?e="&amp;$A125)</f>
-      </c>
-      <c r="Y125" s="1">
-        <f>IF($A125="","","https://momentedit.kr/i-family/family-"&amp;$H125&amp;".html?e="&amp;$A125)</f>
+      <c r="AA125" s="1">
+        <f>IF($A125="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H125,2)&amp;".html?e="&amp;$A125)</f>
+      </c>
+      <c r="AB125" s="1">
+        <f>IF($A125="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H125,2)&amp;".html?e="&amp;$A125)</f>
       </c>
     </row>
     <row r="126">
-      <c r="X126" s="1">
-        <f>IF($A126="","","https://momentedit.kr/i/cover-"&amp;$H126&amp;".html?e="&amp;$A126)</f>
-      </c>
-      <c r="Y126" s="1">
-        <f>IF($A126="","","https://momentedit.kr/i-family/family-"&amp;$H126&amp;".html?e="&amp;$A126)</f>
+      <c r="AA126" s="1">
+        <f>IF($A126="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H126,2)&amp;".html?e="&amp;$A126)</f>
+      </c>
+      <c r="AB126" s="1">
+        <f>IF($A126="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H126,2)&amp;".html?e="&amp;$A126)</f>
       </c>
     </row>
     <row r="127">
-      <c r="X127" s="1">
-        <f>IF($A127="","","https://momentedit.kr/i/cover-"&amp;$H127&amp;".html?e="&amp;$A127)</f>
-      </c>
-      <c r="Y127" s="1">
-        <f>IF($A127="","","https://momentedit.kr/i-family/family-"&amp;$H127&amp;".html?e="&amp;$A127)</f>
+      <c r="AA127" s="1">
+        <f>IF($A127="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H127,2)&amp;".html?e="&amp;$A127)</f>
+      </c>
+      <c r="AB127" s="1">
+        <f>IF($A127="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H127,2)&amp;".html?e="&amp;$A127)</f>
       </c>
     </row>
     <row r="128">
-      <c r="X128" s="1">
-        <f>IF($A128="","","https://momentedit.kr/i/cover-"&amp;$H128&amp;".html?e="&amp;$A128)</f>
-      </c>
-      <c r="Y128" s="1">
-        <f>IF($A128="","","https://momentedit.kr/i-family/family-"&amp;$H128&amp;".html?e="&amp;$A128)</f>
+      <c r="AA128" s="1">
+        <f>IF($A128="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H128,2)&amp;".html?e="&amp;$A128)</f>
+      </c>
+      <c r="AB128" s="1">
+        <f>IF($A128="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H128,2)&amp;".html?e="&amp;$A128)</f>
       </c>
     </row>
     <row r="129">
-      <c r="X129" s="1">
-        <f>IF($A129="","","https://momentedit.kr/i/cover-"&amp;$H129&amp;".html?e="&amp;$A129)</f>
-      </c>
-      <c r="Y129" s="1">
-        <f>IF($A129="","","https://momentedit.kr/i-family/family-"&amp;$H129&amp;".html?e="&amp;$A129)</f>
+      <c r="AA129" s="1">
+        <f>IF($A129="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H129,2)&amp;".html?e="&amp;$A129)</f>
+      </c>
+      <c r="AB129" s="1">
+        <f>IF($A129="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H129,2)&amp;".html?e="&amp;$A129)</f>
       </c>
     </row>
     <row r="130">
-      <c r="X130" s="1">
-        <f>IF($A130="","","https://momentedit.kr/i/cover-"&amp;$H130&amp;".html?e="&amp;$A130)</f>
-      </c>
-      <c r="Y130" s="1">
-        <f>IF($A130="","","https://momentedit.kr/i-family/family-"&amp;$H130&amp;".html?e="&amp;$A130)</f>
+      <c r="AA130" s="1">
+        <f>IF($A130="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H130,2)&amp;".html?e="&amp;$A130)</f>
+      </c>
+      <c r="AB130" s="1">
+        <f>IF($A130="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H130,2)&amp;".html?e="&amp;$A130)</f>
       </c>
     </row>
     <row r="131">
-      <c r="X131" s="1">
-        <f>IF($A131="","","https://momentedit.kr/i/cover-"&amp;$H131&amp;".html?e="&amp;$A131)</f>
-      </c>
-      <c r="Y131" s="1">
-        <f>IF($A131="","","https://momentedit.kr/i-family/family-"&amp;$H131&amp;".html?e="&amp;$A131)</f>
+      <c r="AA131" s="1">
+        <f>IF($A131="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H131,2)&amp;".html?e="&amp;$A131)</f>
+      </c>
+      <c r="AB131" s="1">
+        <f>IF($A131="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H131,2)&amp;".html?e="&amp;$A131)</f>
       </c>
     </row>
     <row r="132">
-      <c r="X132" s="1">
-        <f>IF($A132="","","https://momentedit.kr/i/cover-"&amp;$H132&amp;".html?e="&amp;$A132)</f>
-      </c>
-      <c r="Y132" s="1">
-        <f>IF($A132="","","https://momentedit.kr/i-family/family-"&amp;$H132&amp;".html?e="&amp;$A132)</f>
+      <c r="AA132" s="1">
+        <f>IF($A132="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H132,2)&amp;".html?e="&amp;$A132)</f>
+      </c>
+      <c r="AB132" s="1">
+        <f>IF($A132="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H132,2)&amp;".html?e="&amp;$A132)</f>
       </c>
     </row>
     <row r="133">
-      <c r="X133" s="1">
-        <f>IF($A133="","","https://momentedit.kr/i/cover-"&amp;$H133&amp;".html?e="&amp;$A133)</f>
-      </c>
-      <c r="Y133" s="1">
-        <f>IF($A133="","","https://momentedit.kr/i-family/family-"&amp;$H133&amp;".html?e="&amp;$A133)</f>
+      <c r="AA133" s="1">
+        <f>IF($A133="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H133,2)&amp;".html?e="&amp;$A133)</f>
+      </c>
+      <c r="AB133" s="1">
+        <f>IF($A133="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H133,2)&amp;".html?e="&amp;$A133)</f>
       </c>
     </row>
     <row r="134">
-      <c r="X134" s="1">
-        <f>IF($A134="","","https://momentedit.kr/i/cover-"&amp;$H134&amp;".html?e="&amp;$A134)</f>
-      </c>
-      <c r="Y134" s="1">
-        <f>IF($A134="","","https://momentedit.kr/i-family/family-"&amp;$H134&amp;".html?e="&amp;$A134)</f>
+      <c r="AA134" s="1">
+        <f>IF($A134="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H134,2)&amp;".html?e="&amp;$A134)</f>
+      </c>
+      <c r="AB134" s="1">
+        <f>IF($A134="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H134,2)&amp;".html?e="&amp;$A134)</f>
       </c>
     </row>
     <row r="135">
-      <c r="X135" s="1">
-        <f>IF($A135="","","https://momentedit.kr/i/cover-"&amp;$H135&amp;".html?e="&amp;$A135)</f>
-      </c>
-      <c r="Y135" s="1">
-        <f>IF($A135="","","https://momentedit.kr/i-family/family-"&amp;$H135&amp;".html?e="&amp;$A135)</f>
+      <c r="AA135" s="1">
+        <f>IF($A135="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H135,2)&amp;".html?e="&amp;$A135)</f>
+      </c>
+      <c r="AB135" s="1">
+        <f>IF($A135="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H135,2)&amp;".html?e="&amp;$A135)</f>
       </c>
     </row>
     <row r="136">
-      <c r="X136" s="1">
-        <f>IF($A136="","","https://momentedit.kr/i/cover-"&amp;$H136&amp;".html?e="&amp;$A136)</f>
-      </c>
-      <c r="Y136" s="1">
-        <f>IF($A136="","","https://momentedit.kr/i-family/family-"&amp;$H136&amp;".html?e="&amp;$A136)</f>
+      <c r="AA136" s="1">
+        <f>IF($A136="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H136,2)&amp;".html?e="&amp;$A136)</f>
+      </c>
+      <c r="AB136" s="1">
+        <f>IF($A136="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H136,2)&amp;".html?e="&amp;$A136)</f>
       </c>
     </row>
     <row r="137">
-      <c r="X137" s="1">
-        <f>IF($A137="","","https://momentedit.kr/i/cover-"&amp;$H137&amp;".html?e="&amp;$A137)</f>
-      </c>
-      <c r="Y137" s="1">
-        <f>IF($A137="","","https://momentedit.kr/i-family/family-"&amp;$H137&amp;".html?e="&amp;$A137)</f>
+      <c r="AA137" s="1">
+        <f>IF($A137="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H137,2)&amp;".html?e="&amp;$A137)</f>
+      </c>
+      <c r="AB137" s="1">
+        <f>IF($A137="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H137,2)&amp;".html?e="&amp;$A137)</f>
       </c>
     </row>
     <row r="138">
-      <c r="X138" s="1">
-        <f>IF($A138="","","https://momentedit.kr/i/cover-"&amp;$H138&amp;".html?e="&amp;$A138)</f>
-      </c>
-      <c r="Y138" s="1">
-        <f>IF($A138="","","https://momentedit.kr/i-family/family-"&amp;$H138&amp;".html?e="&amp;$A138)</f>
+      <c r="AA138" s="1">
+        <f>IF($A138="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H138,2)&amp;".html?e="&amp;$A138)</f>
+      </c>
+      <c r="AB138" s="1">
+        <f>IF($A138="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H138,2)&amp;".html?e="&amp;$A138)</f>
       </c>
     </row>
     <row r="139">
-      <c r="X139" s="1">
-        <f>IF($A139="","","https://momentedit.kr/i/cover-"&amp;$H139&amp;".html?e="&amp;$A139)</f>
-      </c>
-      <c r="Y139" s="1">
-        <f>IF($A139="","","https://momentedit.kr/i-family/family-"&amp;$H139&amp;".html?e="&amp;$A139)</f>
+      <c r="AA139" s="1">
+        <f>IF($A139="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H139,2)&amp;".html?e="&amp;$A139)</f>
+      </c>
+      <c r="AB139" s="1">
+        <f>IF($A139="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H139,2)&amp;".html?e="&amp;$A139)</f>
       </c>
     </row>
     <row r="140">
-      <c r="X140" s="1">
-        <f>IF($A140="","","https://momentedit.kr/i/cover-"&amp;$H140&amp;".html?e="&amp;$A140)</f>
-      </c>
-      <c r="Y140" s="1">
-        <f>IF($A140="","","https://momentedit.kr/i-family/family-"&amp;$H140&amp;".html?e="&amp;$A140)</f>
+      <c r="AA140" s="1">
+        <f>IF($A140="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H140,2)&amp;".html?e="&amp;$A140)</f>
+      </c>
+      <c r="AB140" s="1">
+        <f>IF($A140="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H140,2)&amp;".html?e="&amp;$A140)</f>
       </c>
     </row>
     <row r="141">
-      <c r="X141" s="1">
-        <f>IF($A141="","","https://momentedit.kr/i/cover-"&amp;$H141&amp;".html?e="&amp;$A141)</f>
-      </c>
-      <c r="Y141" s="1">
-        <f>IF($A141="","","https://momentedit.kr/i-family/family-"&amp;$H141&amp;".html?e="&amp;$A141)</f>
+      <c r="AA141" s="1">
+        <f>IF($A141="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H141,2)&amp;".html?e="&amp;$A141)</f>
+      </c>
+      <c r="AB141" s="1">
+        <f>IF($A141="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H141,2)&amp;".html?e="&amp;$A141)</f>
       </c>
     </row>
     <row r="142">
-      <c r="X142" s="1">
-        <f>IF($A142="","","https://momentedit.kr/i/cover-"&amp;$H142&amp;".html?e="&amp;$A142)</f>
-      </c>
-      <c r="Y142" s="1">
-        <f>IF($A142="","","https://momentedit.kr/i-family/family-"&amp;$H142&amp;".html?e="&amp;$A142)</f>
+      <c r="AA142" s="1">
+        <f>IF($A142="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H142,2)&amp;".html?e="&amp;$A142)</f>
+      </c>
+      <c r="AB142" s="1">
+        <f>IF($A142="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H142,2)&amp;".html?e="&amp;$A142)</f>
       </c>
     </row>
     <row r="143">
-      <c r="X143" s="1">
-        <f>IF($A143="","","https://momentedit.kr/i/cover-"&amp;$H143&amp;".html?e="&amp;$A143)</f>
-      </c>
-      <c r="Y143" s="1">
-        <f>IF($A143="","","https://momentedit.kr/i-family/family-"&amp;$H143&amp;".html?e="&amp;$A143)</f>
+      <c r="AA143" s="1">
+        <f>IF($A143="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H143,2)&amp;".html?e="&amp;$A143)</f>
+      </c>
+      <c r="AB143" s="1">
+        <f>IF($A143="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H143,2)&amp;".html?e="&amp;$A143)</f>
       </c>
     </row>
     <row r="144">
-      <c r="X144" s="1">
-        <f>IF($A144="","","https://momentedit.kr/i/cover-"&amp;$H144&amp;".html?e="&amp;$A144)</f>
-      </c>
-      <c r="Y144" s="1">
-        <f>IF($A144="","","https://momentedit.kr/i-family/family-"&amp;$H144&amp;".html?e="&amp;$A144)</f>
+      <c r="AA144" s="1">
+        <f>IF($A144="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H144,2)&amp;".html?e="&amp;$A144)</f>
+      </c>
+      <c r="AB144" s="1">
+        <f>IF($A144="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H144,2)&amp;".html?e="&amp;$A144)</f>
       </c>
     </row>
     <row r="145">
-      <c r="X145" s="1">
-        <f>IF($A145="","","https://momentedit.kr/i/cover-"&amp;$H145&amp;".html?e="&amp;$A145)</f>
-      </c>
-      <c r="Y145" s="1">
-        <f>IF($A145="","","https://momentedit.kr/i-family/family-"&amp;$H145&amp;".html?e="&amp;$A145)</f>
+      <c r="AA145" s="1">
+        <f>IF($A145="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H145,2)&amp;".html?e="&amp;$A145)</f>
+      </c>
+      <c r="AB145" s="1">
+        <f>IF($A145="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H145,2)&amp;".html?e="&amp;$A145)</f>
       </c>
     </row>
     <row r="146">
-      <c r="X146" s="1">
-        <f>IF($A146="","","https://momentedit.kr/i/cover-"&amp;$H146&amp;".html?e="&amp;$A146)</f>
-      </c>
-      <c r="Y146" s="1">
-        <f>IF($A146="","","https://momentedit.kr/i-family/family-"&amp;$H146&amp;".html?e="&amp;$A146)</f>
+      <c r="AA146" s="1">
+        <f>IF($A146="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H146,2)&amp;".html?e="&amp;$A146)</f>
+      </c>
+      <c r="AB146" s="1">
+        <f>IF($A146="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H146,2)&amp;".html?e="&amp;$A146)</f>
       </c>
     </row>
     <row r="147">
-      <c r="X147" s="1">
-        <f>IF($A147="","","https://momentedit.kr/i/cover-"&amp;$H147&amp;".html?e="&amp;$A147)</f>
-      </c>
-      <c r="Y147" s="1">
-        <f>IF($A147="","","https://momentedit.kr/i-family/family-"&amp;$H147&amp;".html?e="&amp;$A147)</f>
+      <c r="AA147" s="1">
+        <f>IF($A147="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H147,2)&amp;".html?e="&amp;$A147)</f>
+      </c>
+      <c r="AB147" s="1">
+        <f>IF($A147="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H147,2)&amp;".html?e="&amp;$A147)</f>
       </c>
     </row>
     <row r="148">
-      <c r="X148" s="1">
-        <f>IF($A148="","","https://momentedit.kr/i/cover-"&amp;$H148&amp;".html?e="&amp;$A148)</f>
-      </c>
-      <c r="Y148" s="1">
-        <f>IF($A148="","","https://momentedit.kr/i-family/family-"&amp;$H148&amp;".html?e="&amp;$A148)</f>
+      <c r="AA148" s="1">
+        <f>IF($A148="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H148,2)&amp;".html?e="&amp;$A148)</f>
+      </c>
+      <c r="AB148" s="1">
+        <f>IF($A148="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H148,2)&amp;".html?e="&amp;$A148)</f>
       </c>
     </row>
     <row r="149">
-      <c r="X149" s="1">
-        <f>IF($A149="","","https://momentedit.kr/i/cover-"&amp;$H149&amp;".html?e="&amp;$A149)</f>
-      </c>
-      <c r="Y149" s="1">
-        <f>IF($A149="","","https://momentedit.kr/i-family/family-"&amp;$H149&amp;".html?e="&amp;$A149)</f>
+      <c r="AA149" s="1">
+        <f>IF($A149="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H149,2)&amp;".html?e="&amp;$A149)</f>
+      </c>
+      <c r="AB149" s="1">
+        <f>IF($A149="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H149,2)&amp;".html?e="&amp;$A149)</f>
       </c>
     </row>
     <row r="150">
-      <c r="X150" s="1">
-        <f>IF($A150="","","https://momentedit.kr/i/cover-"&amp;$H150&amp;".html?e="&amp;$A150)</f>
-      </c>
-      <c r="Y150" s="1">
-        <f>IF($A150="","","https://momentedit.kr/i-family/family-"&amp;$H150&amp;".html?e="&amp;$A150)</f>
+      <c r="AA150" s="1">
+        <f>IF($A150="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H150,2)&amp;".html?e="&amp;$A150)</f>
+      </c>
+      <c r="AB150" s="1">
+        <f>IF($A150="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H150,2)&amp;".html?e="&amp;$A150)</f>
       </c>
     </row>
     <row r="151">
-      <c r="X151" s="1">
-        <f>IF($A151="","","https://momentedit.kr/i/cover-"&amp;$H151&amp;".html?e="&amp;$A151)</f>
-      </c>
-      <c r="Y151" s="1">
-        <f>IF($A151="","","https://momentedit.kr/i-family/family-"&amp;$H151&amp;".html?e="&amp;$A151)</f>
+      <c r="AA151" s="1">
+        <f>IF($A151="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H151,2)&amp;".html?e="&amp;$A151)</f>
+      </c>
+      <c r="AB151" s="1">
+        <f>IF($A151="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H151,2)&amp;".html?e="&amp;$A151)</f>
       </c>
     </row>
     <row r="152">
-      <c r="X152" s="1">
-        <f>IF($A152="","","https://momentedit.kr/i/cover-"&amp;$H152&amp;".html?e="&amp;$A152)</f>
-      </c>
-      <c r="Y152" s="1">
-        <f>IF($A152="","","https://momentedit.kr/i-family/family-"&amp;$H152&amp;".html?e="&amp;$A152)</f>
+      <c r="AA152" s="1">
+        <f>IF($A152="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H152,2)&amp;".html?e="&amp;$A152)</f>
+      </c>
+      <c r="AB152" s="1">
+        <f>IF($A152="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H152,2)&amp;".html?e="&amp;$A152)</f>
       </c>
     </row>
     <row r="153">
-      <c r="X153" s="1">
-        <f>IF($A153="","","https://momentedit.kr/i/cover-"&amp;$H153&amp;".html?e="&amp;$A153)</f>
-      </c>
-      <c r="Y153" s="1">
-        <f>IF($A153="","","https://momentedit.kr/i-family/family-"&amp;$H153&amp;".html?e="&amp;$A153)</f>
+      <c r="AA153" s="1">
+        <f>IF($A153="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H153,2)&amp;".html?e="&amp;$A153)</f>
+      </c>
+      <c r="AB153" s="1">
+        <f>IF($A153="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H153,2)&amp;".html?e="&amp;$A153)</f>
       </c>
     </row>
     <row r="154">
-      <c r="X154" s="1">
-        <f>IF($A154="","","https://momentedit.kr/i/cover-"&amp;$H154&amp;".html?e="&amp;$A154)</f>
-      </c>
-      <c r="Y154" s="1">
-        <f>IF($A154="","","https://momentedit.kr/i-family/family-"&amp;$H154&amp;".html?e="&amp;$A154)</f>
+      <c r="AA154" s="1">
+        <f>IF($A154="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H154,2)&amp;".html?e="&amp;$A154)</f>
+      </c>
+      <c r="AB154" s="1">
+        <f>IF($A154="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H154,2)&amp;".html?e="&amp;$A154)</f>
       </c>
     </row>
     <row r="155">
-      <c r="X155" s="1">
-        <f>IF($A155="","","https://momentedit.kr/i/cover-"&amp;$H155&amp;".html?e="&amp;$A155)</f>
-      </c>
-      <c r="Y155" s="1">
-        <f>IF($A155="","","https://momentedit.kr/i-family/family-"&amp;$H155&amp;".html?e="&amp;$A155)</f>
+      <c r="AA155" s="1">
+        <f>IF($A155="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H155,2)&amp;".html?e="&amp;$A155)</f>
+      </c>
+      <c r="AB155" s="1">
+        <f>IF($A155="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H155,2)&amp;".html?e="&amp;$A155)</f>
       </c>
     </row>
     <row r="156">
-      <c r="X156" s="1">
-        <f>IF($A156="","","https://momentedit.kr/i/cover-"&amp;$H156&amp;".html?e="&amp;$A156)</f>
-      </c>
-      <c r="Y156" s="1">
-        <f>IF($A156="","","https://momentedit.kr/i-family/family-"&amp;$H156&amp;".html?e="&amp;$A156)</f>
+      <c r="AA156" s="1">
+        <f>IF($A156="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H156,2)&amp;".html?e="&amp;$A156)</f>
+      </c>
+      <c r="AB156" s="1">
+        <f>IF($A156="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H156,2)&amp;".html?e="&amp;$A156)</f>
       </c>
     </row>
     <row r="157">
-      <c r="X157" s="1">
-        <f>IF($A157="","","https://momentedit.kr/i/cover-"&amp;$H157&amp;".html?e="&amp;$A157)</f>
-      </c>
-      <c r="Y157" s="1">
-        <f>IF($A157="","","https://momentedit.kr/i-family/family-"&amp;$H157&amp;".html?e="&amp;$A157)</f>
+      <c r="AA157" s="1">
+        <f>IF($A157="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H157,2)&amp;".html?e="&amp;$A157)</f>
+      </c>
+      <c r="AB157" s="1">
+        <f>IF($A157="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H157,2)&amp;".html?e="&amp;$A157)</f>
       </c>
     </row>
     <row r="158">
-      <c r="X158" s="1">
-        <f>IF($A158="","","https://momentedit.kr/i/cover-"&amp;$H158&amp;".html?e="&amp;$A158)</f>
-      </c>
-      <c r="Y158" s="1">
-        <f>IF($A158="","","https://momentedit.kr/i-family/family-"&amp;$H158&amp;".html?e="&amp;$A158)</f>
+      <c r="AA158" s="1">
+        <f>IF($A158="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H158,2)&amp;".html?e="&amp;$A158)</f>
+      </c>
+      <c r="AB158" s="1">
+        <f>IF($A158="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H158,2)&amp;".html?e="&amp;$A158)</f>
       </c>
     </row>
     <row r="159">
-      <c r="X159" s="1">
-        <f>IF($A159="","","https://momentedit.kr/i/cover-"&amp;$H159&amp;".html?e="&amp;$A159)</f>
-      </c>
-      <c r="Y159" s="1">
-        <f>IF($A159="","","https://momentedit.kr/i-family/family-"&amp;$H159&amp;".html?e="&amp;$A159)</f>
+      <c r="AA159" s="1">
+        <f>IF($A159="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H159,2)&amp;".html?e="&amp;$A159)</f>
+      </c>
+      <c r="AB159" s="1">
+        <f>IF($A159="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H159,2)&amp;".html?e="&amp;$A159)</f>
       </c>
     </row>
     <row r="160">
-      <c r="X160" s="1">
-        <f>IF($A160="","","https://momentedit.kr/i/cover-"&amp;$H160&amp;".html?e="&amp;$A160)</f>
-      </c>
-      <c r="Y160" s="1">
-        <f>IF($A160="","","https://momentedit.kr/i-family/family-"&amp;$H160&amp;".html?e="&amp;$A160)</f>
+      <c r="AA160" s="1">
+        <f>IF($A160="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H160,2)&amp;".html?e="&amp;$A160)</f>
+      </c>
+      <c r="AB160" s="1">
+        <f>IF($A160="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H160,2)&amp;".html?e="&amp;$A160)</f>
       </c>
     </row>
     <row r="161">
-      <c r="X161" s="1">
-        <f>IF($A161="","","https://momentedit.kr/i/cover-"&amp;$H161&amp;".html?e="&amp;$A161)</f>
-      </c>
-      <c r="Y161" s="1">
-        <f>IF($A161="","","https://momentedit.kr/i-family/family-"&amp;$H161&amp;".html?e="&amp;$A161)</f>
+      <c r="AA161" s="1">
+        <f>IF($A161="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H161,2)&amp;".html?e="&amp;$A161)</f>
+      </c>
+      <c r="AB161" s="1">
+        <f>IF($A161="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H161,2)&amp;".html?e="&amp;$A161)</f>
       </c>
     </row>
     <row r="162">
-      <c r="X162" s="1">
-        <f>IF($A162="","","https://momentedit.kr/i/cover-"&amp;$H162&amp;".html?e="&amp;$A162)</f>
-      </c>
-      <c r="Y162" s="1">
-        <f>IF($A162="","","https://momentedit.kr/i-family/family-"&amp;$H162&amp;".html?e="&amp;$A162)</f>
+      <c r="AA162" s="1">
+        <f>IF($A162="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H162,2)&amp;".html?e="&amp;$A162)</f>
+      </c>
+      <c r="AB162" s="1">
+        <f>IF($A162="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H162,2)&amp;".html?e="&amp;$A162)</f>
       </c>
     </row>
     <row r="163">
-      <c r="X163" s="1">
-        <f>IF($A163="","","https://momentedit.kr/i/cover-"&amp;$H163&amp;".html?e="&amp;$A163)</f>
-      </c>
-      <c r="Y163" s="1">
-        <f>IF($A163="","","https://momentedit.kr/i-family/family-"&amp;$H163&amp;".html?e="&amp;$A163)</f>
+      <c r="AA163" s="1">
+        <f>IF($A163="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H163,2)&amp;".html?e="&amp;$A163)</f>
+      </c>
+      <c r="AB163" s="1">
+        <f>IF($A163="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H163,2)&amp;".html?e="&amp;$A163)</f>
       </c>
     </row>
     <row r="164">
-      <c r="X164" s="1">
-        <f>IF($A164="","","https://momentedit.kr/i/cover-"&amp;$H164&amp;".html?e="&amp;$A164)</f>
-      </c>
-      <c r="Y164" s="1">
-        <f>IF($A164="","","https://momentedit.kr/i-family/family-"&amp;$H164&amp;".html?e="&amp;$A164)</f>
+      <c r="AA164" s="1">
+        <f>IF($A164="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H164,2)&amp;".html?e="&amp;$A164)</f>
+      </c>
+      <c r="AB164" s="1">
+        <f>IF($A164="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H164,2)&amp;".html?e="&amp;$A164)</f>
       </c>
     </row>
     <row r="165">
-      <c r="X165" s="1">
-        <f>IF($A165="","","https://momentedit.kr/i/cover-"&amp;$H165&amp;".html?e="&amp;$A165)</f>
-      </c>
-      <c r="Y165" s="1">
-        <f>IF($A165="","","https://momentedit.kr/i-family/family-"&amp;$H165&amp;".html?e="&amp;$A165)</f>
+      <c r="AA165" s="1">
+        <f>IF($A165="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H165,2)&amp;".html?e="&amp;$A165)</f>
+      </c>
+      <c r="AB165" s="1">
+        <f>IF($A165="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H165,2)&amp;".html?e="&amp;$A165)</f>
       </c>
     </row>
     <row r="166">
-      <c r="X166" s="1">
-        <f>IF($A166="","","https://momentedit.kr/i/cover-"&amp;$H166&amp;".html?e="&amp;$A166)</f>
-      </c>
-      <c r="Y166" s="1">
-        <f>IF($A166="","","https://momentedit.kr/i-family/family-"&amp;$H166&amp;".html?e="&amp;$A166)</f>
+      <c r="AA166" s="1">
+        <f>IF($A166="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H166,2)&amp;".html?e="&amp;$A166)</f>
+      </c>
+      <c r="AB166" s="1">
+        <f>IF($A166="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H166,2)&amp;".html?e="&amp;$A166)</f>
       </c>
     </row>
     <row r="167">
-      <c r="X167" s="1">
-        <f>IF($A167="","","https://momentedit.kr/i/cover-"&amp;$H167&amp;".html?e="&amp;$A167)</f>
-      </c>
-      <c r="Y167" s="1">
-        <f>IF($A167="","","https://momentedit.kr/i-family/family-"&amp;$H167&amp;".html?e="&amp;$A167)</f>
+      <c r="AA167" s="1">
+        <f>IF($A167="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H167,2)&amp;".html?e="&amp;$A167)</f>
+      </c>
+      <c r="AB167" s="1">
+        <f>IF($A167="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H167,2)&amp;".html?e="&amp;$A167)</f>
       </c>
     </row>
     <row r="168">
-      <c r="X168" s="1">
-        <f>IF($A168="","","https://momentedit.kr/i/cover-"&amp;$H168&amp;".html?e="&amp;$A168)</f>
-      </c>
-      <c r="Y168" s="1">
-        <f>IF($A168="","","https://momentedit.kr/i-family/family-"&amp;$H168&amp;".html?e="&amp;$A168)</f>
+      <c r="AA168" s="1">
+        <f>IF($A168="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H168,2)&amp;".html?e="&amp;$A168)</f>
+      </c>
+      <c r="AB168" s="1">
+        <f>IF($A168="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H168,2)&amp;".html?e="&amp;$A168)</f>
       </c>
     </row>
     <row r="169">
-      <c r="X169" s="1">
-        <f>IF($A169="","","https://momentedit.kr/i/cover-"&amp;$H169&amp;".html?e="&amp;$A169)</f>
-      </c>
-      <c r="Y169" s="1">
-        <f>IF($A169="","","https://momentedit.kr/i-family/family-"&amp;$H169&amp;".html?e="&amp;$A169)</f>
+      <c r="AA169" s="1">
+        <f>IF($A169="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H169,2)&amp;".html?e="&amp;$A169)</f>
+      </c>
+      <c r="AB169" s="1">
+        <f>IF($A169="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H169,2)&amp;".html?e="&amp;$A169)</f>
       </c>
     </row>
     <row r="170">
-      <c r="X170" s="1">
-        <f>IF($A170="","","https://momentedit.kr/i/cover-"&amp;$H170&amp;".html?e="&amp;$A170)</f>
-      </c>
-      <c r="Y170" s="1">
-        <f>IF($A170="","","https://momentedit.kr/i-family/family-"&amp;$H170&amp;".html?e="&amp;$A170)</f>
+      <c r="AA170" s="1">
+        <f>IF($A170="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H170,2)&amp;".html?e="&amp;$A170)</f>
+      </c>
+      <c r="AB170" s="1">
+        <f>IF($A170="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H170,2)&amp;".html?e="&amp;$A170)</f>
       </c>
     </row>
     <row r="171">
-      <c r="X171" s="1">
-        <f>IF($A171="","","https://momentedit.kr/i/cover-"&amp;$H171&amp;".html?e="&amp;$A171)</f>
-      </c>
-      <c r="Y171" s="1">
-        <f>IF($A171="","","https://momentedit.kr/i-family/family-"&amp;$H171&amp;".html?e="&amp;$A171)</f>
+      <c r="AA171" s="1">
+        <f>IF($A171="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H171,2)&amp;".html?e="&amp;$A171)</f>
+      </c>
+      <c r="AB171" s="1">
+        <f>IF($A171="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H171,2)&amp;".html?e="&amp;$A171)</f>
       </c>
     </row>
     <row r="172">
-      <c r="X172" s="1">
-        <f>IF($A172="","","https://momentedit.kr/i/cover-"&amp;$H172&amp;".html?e="&amp;$A172)</f>
-      </c>
-      <c r="Y172" s="1">
-        <f>IF($A172="","","https://momentedit.kr/i-family/family-"&amp;$H172&amp;".html?e="&amp;$A172)</f>
+      <c r="AA172" s="1">
+        <f>IF($A172="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H172,2)&amp;".html?e="&amp;$A172)</f>
+      </c>
+      <c r="AB172" s="1">
+        <f>IF($A172="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H172,2)&amp;".html?e="&amp;$A172)</f>
       </c>
     </row>
     <row r="173">
-      <c r="X173" s="1">
-        <f>IF($A173="","","https://momentedit.kr/i/cover-"&amp;$H173&amp;".html?e="&amp;$A173)</f>
-      </c>
-      <c r="Y173" s="1">
-        <f>IF($A173="","","https://momentedit.kr/i-family/family-"&amp;$H173&amp;".html?e="&amp;$A173)</f>
+      <c r="AA173" s="1">
+        <f>IF($A173="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H173,2)&amp;".html?e="&amp;$A173)</f>
+      </c>
+      <c r="AB173" s="1">
+        <f>IF($A173="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H173,2)&amp;".html?e="&amp;$A173)</f>
       </c>
     </row>
     <row r="174">
-      <c r="X174" s="1">
-        <f>IF($A174="","","https://momentedit.kr/i/cover-"&amp;$H174&amp;".html?e="&amp;$A174)</f>
-      </c>
-      <c r="Y174" s="1">
-        <f>IF($A174="","","https://momentedit.kr/i-family/family-"&amp;$H174&amp;".html?e="&amp;$A174)</f>
+      <c r="AA174" s="1">
+        <f>IF($A174="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H174,2)&amp;".html?e="&amp;$A174)</f>
+      </c>
+      <c r="AB174" s="1">
+        <f>IF($A174="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H174,2)&amp;".html?e="&amp;$A174)</f>
       </c>
     </row>
     <row r="175">
-      <c r="X175" s="1">
-        <f>IF($A175="","","https://momentedit.kr/i/cover-"&amp;$H175&amp;".html?e="&amp;$A175)</f>
-      </c>
-      <c r="Y175" s="1">
-        <f>IF($A175="","","https://momentedit.kr/i-family/family-"&amp;$H175&amp;".html?e="&amp;$A175)</f>
+      <c r="AA175" s="1">
+        <f>IF($A175="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H175,2)&amp;".html?e="&amp;$A175)</f>
+      </c>
+      <c r="AB175" s="1">
+        <f>IF($A175="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H175,2)&amp;".html?e="&amp;$A175)</f>
       </c>
     </row>
     <row r="176">
-      <c r="X176" s="1">
-        <f>IF($A176="","","https://momentedit.kr/i/cover-"&amp;$H176&amp;".html?e="&amp;$A176)</f>
-      </c>
-      <c r="Y176" s="1">
-        <f>IF($A176="","","https://momentedit.kr/i-family/family-"&amp;$H176&amp;".html?e="&amp;$A176)</f>
+      <c r="AA176" s="1">
+        <f>IF($A176="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H176,2)&amp;".html?e="&amp;$A176)</f>
+      </c>
+      <c r="AB176" s="1">
+        <f>IF($A176="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H176,2)&amp;".html?e="&amp;$A176)</f>
       </c>
     </row>
     <row r="177">
-      <c r="X177" s="1">
-        <f>IF($A177="","","https://momentedit.kr/i/cover-"&amp;$H177&amp;".html?e="&amp;$A177)</f>
-      </c>
-      <c r="Y177" s="1">
-        <f>IF($A177="","","https://momentedit.kr/i-family/family-"&amp;$H177&amp;".html?e="&amp;$A177)</f>
+      <c r="AA177" s="1">
+        <f>IF($A177="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H177,2)&amp;".html?e="&amp;$A177)</f>
+      </c>
+      <c r="AB177" s="1">
+        <f>IF($A177="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H177,2)&amp;".html?e="&amp;$A177)</f>
       </c>
     </row>
     <row r="178">
-      <c r="X178" s="1">
-        <f>IF($A178="","","https://momentedit.kr/i/cover-"&amp;$H178&amp;".html?e="&amp;$A178)</f>
-      </c>
-      <c r="Y178" s="1">
-        <f>IF($A178="","","https://momentedit.kr/i-family/family-"&amp;$H178&amp;".html?e="&amp;$A178)</f>
+      <c r="AA178" s="1">
+        <f>IF($A178="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H178,2)&amp;".html?e="&amp;$A178)</f>
+      </c>
+      <c r="AB178" s="1">
+        <f>IF($A178="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H178,2)&amp;".html?e="&amp;$A178)</f>
       </c>
     </row>
     <row r="179">
-      <c r="X179" s="1">
-        <f>IF($A179="","","https://momentedit.kr/i/cover-"&amp;$H179&amp;".html?e="&amp;$A179)</f>
-      </c>
-      <c r="Y179" s="1">
-        <f>IF($A179="","","https://momentedit.kr/i-family/family-"&amp;$H179&amp;".html?e="&amp;$A179)</f>
+      <c r="AA179" s="1">
+        <f>IF($A179="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H179,2)&amp;".html?e="&amp;$A179)</f>
+      </c>
+      <c r="AB179" s="1">
+        <f>IF($A179="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H179,2)&amp;".html?e="&amp;$A179)</f>
       </c>
     </row>
     <row r="180">
-      <c r="X180" s="1">
-        <f>IF($A180="","","https://momentedit.kr/i/cover-"&amp;$H180&amp;".html?e="&amp;$A180)</f>
-      </c>
-      <c r="Y180" s="1">
-        <f>IF($A180="","","https://momentedit.kr/i-family/family-"&amp;$H180&amp;".html?e="&amp;$A180)</f>
+      <c r="AA180" s="1">
+        <f>IF($A180="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H180,2)&amp;".html?e="&amp;$A180)</f>
+      </c>
+      <c r="AB180" s="1">
+        <f>IF($A180="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H180,2)&amp;".html?e="&amp;$A180)</f>
       </c>
     </row>
     <row r="181">
-      <c r="X181" s="1">
-        <f>IF($A181="","","https://momentedit.kr/i/cover-"&amp;$H181&amp;".html?e="&amp;$A181)</f>
-      </c>
-      <c r="Y181" s="1">
-        <f>IF($A181="","","https://momentedit.kr/i-family/family-"&amp;$H181&amp;".html?e="&amp;$A181)</f>
+      <c r="AA181" s="1">
+        <f>IF($A181="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H181,2)&amp;".html?e="&amp;$A181)</f>
+      </c>
+      <c r="AB181" s="1">
+        <f>IF($A181="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H181,2)&amp;".html?e="&amp;$A181)</f>
       </c>
     </row>
     <row r="182">
-      <c r="X182" s="1">
-        <f>IF($A182="","","https://momentedit.kr/i/cover-"&amp;$H182&amp;".html?e="&amp;$A182)</f>
-      </c>
-      <c r="Y182" s="1">
-        <f>IF($A182="","","https://momentedit.kr/i-family/family-"&amp;$H182&amp;".html?e="&amp;$A182)</f>
+      <c r="AA182" s="1">
+        <f>IF($A182="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H182,2)&amp;".html?e="&amp;$A182)</f>
+      </c>
+      <c r="AB182" s="1">
+        <f>IF($A182="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H182,2)&amp;".html?e="&amp;$A182)</f>
       </c>
     </row>
     <row r="183">
-      <c r="X183" s="1">
-        <f>IF($A183="","","https://momentedit.kr/i/cover-"&amp;$H183&amp;".html?e="&amp;$A183)</f>
-      </c>
-      <c r="Y183" s="1">
-        <f>IF($A183="","","https://momentedit.kr/i-family/family-"&amp;$H183&amp;".html?e="&amp;$A183)</f>
+      <c r="AA183" s="1">
+        <f>IF($A183="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H183,2)&amp;".html?e="&amp;$A183)</f>
+      </c>
+      <c r="AB183" s="1">
+        <f>IF($A183="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H183,2)&amp;".html?e="&amp;$A183)</f>
       </c>
     </row>
     <row r="184">
-      <c r="X184" s="1">
-        <f>IF($A184="","","https://momentedit.kr/i/cover-"&amp;$H184&amp;".html?e="&amp;$A184)</f>
-      </c>
-      <c r="Y184" s="1">
-        <f>IF($A184="","","https://momentedit.kr/i-family/family-"&amp;$H184&amp;".html?e="&amp;$A184)</f>
+      <c r="AA184" s="1">
+        <f>IF($A184="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H184,2)&amp;".html?e="&amp;$A184)</f>
+      </c>
+      <c r="AB184" s="1">
+        <f>IF($A184="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H184,2)&amp;".html?e="&amp;$A184)</f>
       </c>
     </row>
     <row r="185">
-      <c r="X185" s="1">
-        <f>IF($A185="","","https://momentedit.kr/i/cover-"&amp;$H185&amp;".html?e="&amp;$A185)</f>
-      </c>
-      <c r="Y185" s="1">
-        <f>IF($A185="","","https://momentedit.kr/i-family/family-"&amp;$H185&amp;".html?e="&amp;$A185)</f>
+      <c r="AA185" s="1">
+        <f>IF($A185="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H185,2)&amp;".html?e="&amp;$A185)</f>
+      </c>
+      <c r="AB185" s="1">
+        <f>IF($A185="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H185,2)&amp;".html?e="&amp;$A185)</f>
       </c>
     </row>
     <row r="186">
-      <c r="X186" s="1">
-        <f>IF($A186="","","https://momentedit.kr/i/cover-"&amp;$H186&amp;".html?e="&amp;$A186)</f>
-      </c>
-      <c r="Y186" s="1">
-        <f>IF($A186="","","https://momentedit.kr/i-family/family-"&amp;$H186&amp;".html?e="&amp;$A186)</f>
+      <c r="AA186" s="1">
+        <f>IF($A186="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H186,2)&amp;".html?e="&amp;$A186)</f>
+      </c>
+      <c r="AB186" s="1">
+        <f>IF($A186="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H186,2)&amp;".html?e="&amp;$A186)</f>
       </c>
     </row>
     <row r="187">
-      <c r="X187" s="1">
-        <f>IF($A187="","","https://momentedit.kr/i/cover-"&amp;$H187&amp;".html?e="&amp;$A187)</f>
-      </c>
-      <c r="Y187" s="1">
-        <f>IF($A187="","","https://momentedit.kr/i-family/family-"&amp;$H187&amp;".html?e="&amp;$A187)</f>
+      <c r="AA187" s="1">
+        <f>IF($A187="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H187,2)&amp;".html?e="&amp;$A187)</f>
+      </c>
+      <c r="AB187" s="1">
+        <f>IF($A187="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H187,2)&amp;".html?e="&amp;$A187)</f>
       </c>
     </row>
     <row r="188">
-      <c r="X188" s="1">
-        <f>IF($A188="","","https://momentedit.kr/i/cover-"&amp;$H188&amp;".html?e="&amp;$A188)</f>
-      </c>
-      <c r="Y188" s="1">
-        <f>IF($A188="","","https://momentedit.kr/i-family/family-"&amp;$H188&amp;".html?e="&amp;$A188)</f>
+      <c r="AA188" s="1">
+        <f>IF($A188="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H188,2)&amp;".html?e="&amp;$A188)</f>
+      </c>
+      <c r="AB188" s="1">
+        <f>IF($A188="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H188,2)&amp;".html?e="&amp;$A188)</f>
       </c>
     </row>
     <row r="189">
-      <c r="X189" s="1">
-        <f>IF($A189="","","https://momentedit.kr/i/cover-"&amp;$H189&amp;".html?e="&amp;$A189)</f>
-      </c>
-      <c r="Y189" s="1">
-        <f>IF($A189="","","https://momentedit.kr/i-family/family-"&amp;$H189&amp;".html?e="&amp;$A189)</f>
+      <c r="AA189" s="1">
+        <f>IF($A189="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H189,2)&amp;".html?e="&amp;$A189)</f>
+      </c>
+      <c r="AB189" s="1">
+        <f>IF($A189="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H189,2)&amp;".html?e="&amp;$A189)</f>
       </c>
     </row>
     <row r="190">
-      <c r="X190" s="1">
-        <f>IF($A190="","","https://momentedit.kr/i/cover-"&amp;$H190&amp;".html?e="&amp;$A190)</f>
-      </c>
-      <c r="Y190" s="1">
-        <f>IF($A190="","","https://momentedit.kr/i-family/family-"&amp;$H190&amp;".html?e="&amp;$A190)</f>
+      <c r="AA190" s="1">
+        <f>IF($A190="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H190,2)&amp;".html?e="&amp;$A190)</f>
+      </c>
+      <c r="AB190" s="1">
+        <f>IF($A190="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H190,2)&amp;".html?e="&amp;$A190)</f>
       </c>
     </row>
     <row r="191">
-      <c r="X191" s="1">
-        <f>IF($A191="","","https://momentedit.kr/i/cover-"&amp;$H191&amp;".html?e="&amp;$A191)</f>
-      </c>
-      <c r="Y191" s="1">
-        <f>IF($A191="","","https://momentedit.kr/i-family/family-"&amp;$H191&amp;".html?e="&amp;$A191)</f>
+      <c r="AA191" s="1">
+        <f>IF($A191="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H191,2)&amp;".html?e="&amp;$A191)</f>
+      </c>
+      <c r="AB191" s="1">
+        <f>IF($A191="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H191,2)&amp;".html?e="&amp;$A191)</f>
       </c>
     </row>
     <row r="192">
-      <c r="X192" s="1">
-        <f>IF($A192="","","https://momentedit.kr/i/cover-"&amp;$H192&amp;".html?e="&amp;$A192)</f>
-      </c>
-      <c r="Y192" s="1">
-        <f>IF($A192="","","https://momentedit.kr/i-family/family-"&amp;$H192&amp;".html?e="&amp;$A192)</f>
+      <c r="AA192" s="1">
+        <f>IF($A192="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H192,2)&amp;".html?e="&amp;$A192)</f>
+      </c>
+      <c r="AB192" s="1">
+        <f>IF($A192="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H192,2)&amp;".html?e="&amp;$A192)</f>
       </c>
     </row>
     <row r="193">
-      <c r="X193" s="1">
-        <f>IF($A193="","","https://momentedit.kr/i/cover-"&amp;$H193&amp;".html?e="&amp;$A193)</f>
-      </c>
-      <c r="Y193" s="1">
-        <f>IF($A193="","","https://momentedit.kr/i-family/family-"&amp;$H193&amp;".html?e="&amp;$A193)</f>
+      <c r="AA193" s="1">
+        <f>IF($A193="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H193,2)&amp;".html?e="&amp;$A193)</f>
+      </c>
+      <c r="AB193" s="1">
+        <f>IF($A193="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H193,2)&amp;".html?e="&amp;$A193)</f>
       </c>
     </row>
     <row r="194">
-      <c r="X194" s="1">
-        <f>IF($A194="","","https://momentedit.kr/i/cover-"&amp;$H194&amp;".html?e="&amp;$A194)</f>
-      </c>
-      <c r="Y194" s="1">
-        <f>IF($A194="","","https://momentedit.kr/i-family/family-"&amp;$H194&amp;".html?e="&amp;$A194)</f>
+      <c r="AA194" s="1">
+        <f>IF($A194="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H194,2)&amp;".html?e="&amp;$A194)</f>
+      </c>
+      <c r="AB194" s="1">
+        <f>IF($A194="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H194,2)&amp;".html?e="&amp;$A194)</f>
       </c>
     </row>
     <row r="195">
-      <c r="X195" s="1">
-        <f>IF($A195="","","https://momentedit.kr/i/cover-"&amp;$H195&amp;".html?e="&amp;$A195)</f>
-      </c>
-      <c r="Y195" s="1">
-        <f>IF($A195="","","https://momentedit.kr/i-family/family-"&amp;$H195&amp;".html?e="&amp;$A195)</f>
+      <c r="AA195" s="1">
+        <f>IF($A195="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H195,2)&amp;".html?e="&amp;$A195)</f>
+      </c>
+      <c r="AB195" s="1">
+        <f>IF($A195="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H195,2)&amp;".html?e="&amp;$A195)</f>
       </c>
     </row>
     <row r="196">
-      <c r="X196" s="1">
-        <f>IF($A196="","","https://momentedit.kr/i/cover-"&amp;$H196&amp;".html?e="&amp;$A196)</f>
-      </c>
-      <c r="Y196" s="1">
-        <f>IF($A196="","","https://momentedit.kr/i-family/family-"&amp;$H196&amp;".html?e="&amp;$A196)</f>
+      <c r="AA196" s="1">
+        <f>IF($A196="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H196,2)&amp;".html?e="&amp;$A196)</f>
+      </c>
+      <c r="AB196" s="1">
+        <f>IF($A196="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H196,2)&amp;".html?e="&amp;$A196)</f>
       </c>
     </row>
     <row r="197">
-      <c r="X197" s="1">
-        <f>IF($A197="","","https://momentedit.kr/i/cover-"&amp;$H197&amp;".html?e="&amp;$A197)</f>
-      </c>
-      <c r="Y197" s="1">
-        <f>IF($A197="","","https://momentedit.kr/i-family/family-"&amp;$H197&amp;".html?e="&amp;$A197)</f>
+      <c r="AA197" s="1">
+        <f>IF($A197="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H197,2)&amp;".html?e="&amp;$A197)</f>
+      </c>
+      <c r="AB197" s="1">
+        <f>IF($A197="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H197,2)&amp;".html?e="&amp;$A197)</f>
       </c>
     </row>
     <row r="198">
-      <c r="X198" s="1">
-        <f>IF($A198="","","https://momentedit.kr/i/cover-"&amp;$H198&amp;".html?e="&amp;$A198)</f>
-      </c>
-      <c r="Y198" s="1">
-        <f>IF($A198="","","https://momentedit.kr/i-family/family-"&amp;$H198&amp;".html?e="&amp;$A198)</f>
+      <c r="AA198" s="1">
+        <f>IF($A198="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H198,2)&amp;".html?e="&amp;$A198)</f>
+      </c>
+      <c r="AB198" s="1">
+        <f>IF($A198="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H198,2)&amp;".html?e="&amp;$A198)</f>
       </c>
     </row>
     <row r="199">
-      <c r="X199" s="1">
-        <f>IF($A199="","","https://momentedit.kr/i/cover-"&amp;$H199&amp;".html?e="&amp;$A199)</f>
-      </c>
-      <c r="Y199" s="1">
-        <f>IF($A199="","","https://momentedit.kr/i-family/family-"&amp;$H199&amp;".html?e="&amp;$A199)</f>
+      <c r="AA199" s="1">
+        <f>IF($A199="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H199,2)&amp;".html?e="&amp;$A199)</f>
+      </c>
+      <c r="AB199" s="1">
+        <f>IF($A199="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H199,2)&amp;".html?e="&amp;$A199)</f>
       </c>
     </row>
     <row r="200">
-      <c r="X200" s="1">
-        <f>IF($A200="","","https://momentedit.kr/i/cover-"&amp;$H200&amp;".html?e="&amp;$A200)</f>
-      </c>
-      <c r="Y200" s="1">
-        <f>IF($A200="","","https://momentedit.kr/i-family/family-"&amp;$H200&amp;".html?e="&amp;$A200)</f>
+      <c r="AA200" s="1">
+        <f>IF($A200="","","https://momentedit.kr/i/cover-"&amp;RIGHT("0"&amp;$H200,2)&amp;".html?e="&amp;$A200)</f>
+      </c>
+      <c r="AB200" s="1">
+        <f>IF($A200="","","https://momentedit.kr/i-family/family-"&amp;RIGHT("0"&amp;$H200,2)&amp;".html?e="&amp;$A200)</f>
       </c>
     </row>
   </sheetData>

--- a/청첩장/Moment Edit · Letter System (개선).xlsx
+++ b/청첩장/Moment Edit · Letter System (개선).xlsx
@@ -1976,16 +1976,8 @@
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
